--- a/MBF04S.xlsx
+++ b/MBF04S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1122" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1098" uniqueCount="399">
   <si>
     <t/>
   </si>
@@ -31,375 +31,357 @@
     <t>RT,(E-2B)</t>
   </si>
   <si>
-    <t>10004950</t>
-  </si>
-  <si>
-    <t>CERELAC KCNG HJU 120</t>
+    <t>20004385</t>
+  </si>
+  <si>
+    <t>NESTLE BR PSG&amp;SUS120</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>10003111</t>
+  </si>
+  <si>
+    <t>PROMINA BB MARI S150</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>20034046</t>
+  </si>
+  <si>
+    <t>SUN MARIE BISC BLT80</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>20134698</t>
+  </si>
+  <si>
+    <t>SUN MARIE BISC KJU80</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>20032058</t>
+  </si>
+  <si>
+    <t>FF KENTAL MANIS 6X37</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>10015124</t>
+  </si>
+  <si>
+    <t>FF SKM COKLAT 6X37</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>20013433</t>
+  </si>
+  <si>
+    <t>INDOMILK SKM PTH6X37</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>10000724</t>
+  </si>
+  <si>
+    <t>SUN BBR SS BRS/M 120</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>20004385</t>
-  </si>
-  <si>
-    <t>NESTLE BR PSG&amp;SUS120</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>10003111</t>
-  </si>
-  <si>
-    <t>PROMINA BB MARI S150</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>20034046</t>
-  </si>
-  <si>
-    <t>SUN MARIE BISC BLT80</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20134698</t>
-  </si>
-  <si>
-    <t>SUN MARIE BISC KJU80</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>20032058</t>
-  </si>
-  <si>
-    <t>FF KENTAL MANIS 6X37</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>10015124</t>
-  </si>
-  <si>
-    <t>FF SKM COKLAT 6X37</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>20013435</t>
-  </si>
-  <si>
-    <t>ENAK K/MNS PUTIH 6'S</t>
+    <t>10031256</t>
+  </si>
+  <si>
+    <t>SUN BBR SS AYM&amp;B 120</t>
+  </si>
+  <si>
+    <t>20073496</t>
+  </si>
+  <si>
+    <t>SUN BBR SS UBI/U120G</t>
+  </si>
+  <si>
+    <t>10022197</t>
+  </si>
+  <si>
+    <t>SUN BBR.PISANG SC120</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>10000146</t>
+  </si>
+  <si>
+    <t>SUN KC HIJAU EKO 120</t>
+  </si>
+  <si>
+    <t>10000143</t>
+  </si>
+  <si>
+    <t>SUN BRS MERAH EKO120</t>
+  </si>
+  <si>
+    <t>20001705</t>
+  </si>
+  <si>
+    <t>MILNA BISC.6+ PSG110</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20001701</t>
+  </si>
+  <si>
+    <t>MILNA BISC.6+ ORG110</t>
+  </si>
+  <si>
+    <t>10010825</t>
+  </si>
+  <si>
+    <t>MLNA WGAN AYM+KP 120</t>
+  </si>
+  <si>
+    <t>10000720</t>
+  </si>
+  <si>
+    <t>PROMINA TIM SP&amp;WR120</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>10003707</t>
+  </si>
+  <si>
+    <t>PROMINA C.CHKN BR120</t>
+  </si>
+  <si>
+    <t>10021949</t>
+  </si>
+  <si>
+    <t>PROMINA DGNG&amp;BRO 100</t>
+  </si>
+  <si>
+    <t>20012830</t>
+  </si>
+  <si>
+    <t>PRMNA TIM AYM KP 100</t>
+  </si>
+  <si>
+    <t>20002201</t>
+  </si>
+  <si>
+    <t>PROMINA AYM,T,W 100G</t>
+  </si>
+  <si>
+    <t>20012831</t>
+  </si>
+  <si>
+    <t>PROMINA TIM SLMON100</t>
+  </si>
+  <si>
+    <t>10033560</t>
+  </si>
+  <si>
+    <t>PROMINA CHO.AVCD 100</t>
+  </si>
+  <si>
+    <t>20139959</t>
+  </si>
+  <si>
+    <t>PRMN SALMON LM 120G</t>
+  </si>
+  <si>
+    <t>20100805</t>
+  </si>
+  <si>
+    <t>PRMNA PUDNG CHO 4X25</t>
+  </si>
+  <si>
+    <t>20067680</t>
+  </si>
+  <si>
+    <t>PRMNA PUDNG STRW 100</t>
+  </si>
+  <si>
+    <t>20113322</t>
+  </si>
+  <si>
+    <t>PROMINA PASTA M&amp;C 70</t>
+  </si>
+  <si>
+    <t>20126004</t>
+  </si>
+  <si>
+    <t>PROMINA PASTA CCS 60</t>
+  </si>
+  <si>
+    <t>20126003</t>
+  </si>
+  <si>
+    <t>PRMNA MI BT AYM KP75</t>
+  </si>
+  <si>
+    <t>20135120</t>
+  </si>
+  <si>
+    <t>PRMNA SFTCRN BUTER15</t>
+  </si>
+  <si>
+    <t>10025325</t>
+  </si>
+  <si>
+    <t>PRMNA SUPMI AYM SY81</t>
+  </si>
+  <si>
+    <t>10025326</t>
+  </si>
+  <si>
+    <t>PRMN SUPMI DG&amp;SYR 84</t>
+  </si>
+  <si>
+    <t>20094437</t>
+  </si>
+  <si>
+    <t>PROMINA CRUNCHIES 20</t>
+  </si>
+  <si>
+    <t>20129287</t>
+  </si>
+  <si>
+    <t>PRMINA CRN SEAWED 20</t>
+  </si>
+  <si>
+    <t>20129288</t>
+  </si>
+  <si>
+    <t>PRMINA CRN CHKN.BR20</t>
+  </si>
+  <si>
+    <t>20136087</t>
+  </si>
+  <si>
+    <t>PRMNA SFTCRN STRWB15</t>
+  </si>
+  <si>
+    <t>20141387</t>
+  </si>
+  <si>
+    <t>PROMINA MC CHO.AL 42</t>
+  </si>
+  <si>
+    <t>20141376</t>
+  </si>
+  <si>
+    <t>PROMINA MC BL.CHS 42</t>
+  </si>
+  <si>
+    <t>20133324</t>
+  </si>
+  <si>
+    <t>PRMINA CRCKR BRCLI20</t>
+  </si>
+  <si>
+    <t>20134695</t>
+  </si>
+  <si>
+    <t>PRMNA CRCKR BRRIES20</t>
+  </si>
+  <si>
+    <t>20077368</t>
+  </si>
+  <si>
+    <t>PRMINA PUFF BNANA 15</t>
+  </si>
+  <si>
+    <t>20077369</t>
+  </si>
+  <si>
+    <t>PRMINA PUFF BLUBR 15</t>
+  </si>
+  <si>
+    <t>20092042</t>
+  </si>
+  <si>
+    <t>PRMINA PUFF STRWAP15</t>
+  </si>
+  <si>
+    <t>20139421</t>
+  </si>
+  <si>
+    <t>PRMINA YGR MLT SRW 8</t>
+  </si>
+  <si>
+    <t>20139431</t>
+  </si>
+  <si>
+    <t>PRMINA YGR MLT MLK 8</t>
+  </si>
+  <si>
+    <t>20109115</t>
+  </si>
+  <si>
+    <t>MLNA PUFFS ORG BNN15</t>
+  </si>
+  <si>
+    <t>20103062</t>
+  </si>
+  <si>
+    <t>MLNA PUFFS ORG AMB15</t>
+  </si>
+  <si>
+    <t>20103061</t>
+  </si>
+  <si>
+    <t>MLNA PUFFS ORG CHS15</t>
+  </si>
+  <si>
+    <t>20027865</t>
+  </si>
+  <si>
+    <t>MILNA SUP AYM JG 100</t>
+  </si>
+  <si>
+    <t>20027867</t>
+  </si>
+  <si>
+    <t>MILNA ATI AYM BYM120</t>
   </si>
   <si>
     <t>10</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20013434</t>
-  </si>
-  <si>
-    <t>INDOMILK SKM CKT6X37</t>
+    <t>20122054</t>
+  </si>
+  <si>
+    <t>MLNA BBR SLMN CB 100</t>
   </si>
   <si>
     <t>11</t>
   </si>
   <si>
-    <t>20013433</t>
-  </si>
-  <si>
-    <t>INDOMILK SKM PTH6X37</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>10000724</t>
-  </si>
-  <si>
-    <t>SUN BBR SS BRS/M 120</t>
-  </si>
-  <si>
-    <t>10031256</t>
-  </si>
-  <si>
-    <t>SUN BBR SS AYM&amp;B 120</t>
-  </si>
-  <si>
-    <t>20073496</t>
-  </si>
-  <si>
-    <t>SUN BBR SS UBI/U120G</t>
-  </si>
-  <si>
-    <t>10022197</t>
-  </si>
-  <si>
-    <t>SUN BBR.PISANG SC120</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>10000146</t>
-  </si>
-  <si>
-    <t>SUN KC HIJAU EKO 120</t>
-  </si>
-  <si>
-    <t>10000143</t>
-  </si>
-  <si>
-    <t>SUN BRS MERAH EKO120</t>
-  </si>
-  <si>
-    <t>20001705</t>
-  </si>
-  <si>
-    <t>MILNA BISC.6+ PSG110</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20001701</t>
-  </si>
-  <si>
-    <t>MILNA BISC.6+ ORG110</t>
-  </si>
-  <si>
-    <t>10010825</t>
-  </si>
-  <si>
-    <t>MLNA WGAN AYM+KP 120</t>
-  </si>
-  <si>
-    <t>10000720</t>
-  </si>
-  <si>
-    <t>PROMINA TIM SP&amp;WR120</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>10003707</t>
-  </si>
-  <si>
-    <t>PROMINA C.CHKN BR120</t>
-  </si>
-  <si>
-    <t>10021949</t>
-  </si>
-  <si>
-    <t>PROMINA DGNG&amp;BRO 100</t>
-  </si>
-  <si>
-    <t>20012830</t>
-  </si>
-  <si>
-    <t>PRMNA TIM AYM KP 100</t>
-  </si>
-  <si>
-    <t>20002201</t>
-  </si>
-  <si>
-    <t>PROMINA AYM,T,W 100G</t>
-  </si>
-  <si>
-    <t>20012831</t>
-  </si>
-  <si>
-    <t>PROMINA TIM SLMON100</t>
-  </si>
-  <si>
-    <t>10033560</t>
-  </si>
-  <si>
-    <t>PROMINA CHO.AVCD 100</t>
-  </si>
-  <si>
-    <t>20139959</t>
-  </si>
-  <si>
-    <t>PRMN SALMON LM 120G</t>
-  </si>
-  <si>
-    <t>20100805</t>
-  </si>
-  <si>
-    <t>PRMNA PUDNG CHO 4X25</t>
-  </si>
-  <si>
-    <t>20067680</t>
-  </si>
-  <si>
-    <t>PRMNA PUDNG STRW 100</t>
-  </si>
-  <si>
-    <t>20113322</t>
-  </si>
-  <si>
-    <t>PROMINA PASTA M&amp;C 70</t>
-  </si>
-  <si>
-    <t>20126004</t>
-  </si>
-  <si>
-    <t>PROMINA PASTA CCS 60</t>
-  </si>
-  <si>
-    <t>20126003</t>
-  </si>
-  <si>
-    <t>PRMNA MI BT AYM KP75</t>
-  </si>
-  <si>
-    <t>20135120</t>
-  </si>
-  <si>
-    <t>PRMNA SFTCRN BUTER15</t>
-  </si>
-  <si>
-    <t>10025325</t>
-  </si>
-  <si>
-    <t>PRMNA SUPMI AYM SY81</t>
-  </si>
-  <si>
-    <t>10025326</t>
-  </si>
-  <si>
-    <t>PRMN SUPMI DG&amp;SYR 84</t>
-  </si>
-  <si>
-    <t>20094437</t>
-  </si>
-  <si>
-    <t>PROMINA CRUNCHIES 20</t>
-  </si>
-  <si>
-    <t>20129287</t>
-  </si>
-  <si>
-    <t>PRMINA CRN SEAWED 20</t>
-  </si>
-  <si>
-    <t>20129288</t>
-  </si>
-  <si>
-    <t>PRMINA CRN CHKN.BR20</t>
-  </si>
-  <si>
-    <t>20136087</t>
-  </si>
-  <si>
-    <t>PRMNA SFTCRN STRWB15</t>
-  </si>
-  <si>
-    <t>20141387</t>
-  </si>
-  <si>
-    <t>PROMINA MC CHO.AL 42</t>
-  </si>
-  <si>
-    <t>20141376</t>
-  </si>
-  <si>
-    <t>PROMINA MC BL.CHS 42</t>
-  </si>
-  <si>
-    <t>20133324</t>
-  </si>
-  <si>
-    <t>PRMINA CRCKR BRCLI20</t>
-  </si>
-  <si>
-    <t>20134695</t>
-  </si>
-  <si>
-    <t>PRMNA CRCKR BRRIES20</t>
-  </si>
-  <si>
-    <t>20077368</t>
-  </si>
-  <si>
-    <t>PRMINA PUFF BNANA 15</t>
-  </si>
-  <si>
-    <t>20077369</t>
-  </si>
-  <si>
-    <t>PRMINA PUFF BLUBR 15</t>
-  </si>
-  <si>
-    <t>20092042</t>
-  </si>
-  <si>
-    <t>PRMINA PUFF STRWAP15</t>
-  </si>
-  <si>
-    <t>20139421</t>
-  </si>
-  <si>
-    <t>PRMINA YGR MLT SRW 8</t>
-  </si>
-  <si>
-    <t>20139431</t>
-  </si>
-  <si>
-    <t>PRMINA YGR MLT MLK 8</t>
-  </si>
-  <si>
-    <t>20109115</t>
-  </si>
-  <si>
-    <t>MLNA PUFFS ORG BNN15</t>
-  </si>
-  <si>
-    <t>20103062</t>
-  </si>
-  <si>
-    <t>MLNA PUFFS ORG AMB15</t>
-  </si>
-  <si>
-    <t>20103061</t>
-  </si>
-  <si>
-    <t>MLNA PUFFS ORG CHS15</t>
-  </si>
-  <si>
-    <t>20027865</t>
-  </si>
-  <si>
-    <t>MILNA SUP AYM JG 100</t>
-  </si>
-  <si>
-    <t>20027867</t>
-  </si>
-  <si>
-    <t>MILNA ATI AYM BYM120</t>
-  </si>
-  <si>
-    <t>20122054</t>
-  </si>
-  <si>
-    <t>MLNA BBR SLMN CB 100</t>
-  </si>
-  <si>
     <t>20138171</t>
   </si>
   <si>
@@ -550,12 +532,6 @@
     <t>INDOMLK KM DURIAN370</t>
   </si>
   <si>
-    <t>10031572</t>
-  </si>
-  <si>
-    <t>ENAK K/MNS COKLT370G</t>
-  </si>
-  <si>
     <t>10000021</t>
   </si>
   <si>
@@ -625,13 +601,13 @@
     <t>20135200</t>
   </si>
   <si>
-    <t>VIDORAN BABY0-6 575G</t>
+    <t>VIDORAN BABY0-6 550G</t>
   </si>
   <si>
     <t>20129773</t>
   </si>
   <si>
-    <t>VDORAN BABY6-12 575G</t>
+    <t>VDORAN BABY6-12 550G</t>
   </si>
   <si>
     <t>20117983</t>
@@ -1624,7 +1600,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F187"/>
+  <dimension ref="A1:F183"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1771,15 +1747,15 @@
         <v>20</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -1788,10 +1764,10 @@
         <v>4</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1811,27 +1787,27 @@
         <v>27</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="F10" s="1" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1845,50 +1821,50 @@
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>5</v>
@@ -1896,19 +1872,19 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>5</v>
@@ -1916,19 +1892,19 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>5</v>
@@ -1936,70 +1912,70 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="C16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>5</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>52</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
@@ -2008,18 +1984,18 @@
         <v>8</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>55</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
@@ -2028,18 +2004,18 @@
         <v>8</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>57</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
@@ -2048,47 +2024,47 @@
         <v>8</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>59</v>
-      </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>5</v>
@@ -2096,19 +2072,19 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>5</v>
@@ -2116,39 +2092,39 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>5</v>
@@ -2156,19 +2132,19 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>5</v>
@@ -2176,39 +2152,39 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>60</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>5</v>
@@ -2216,19 +2192,19 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>5</v>
@@ -2236,59 +2212,59 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>5</v>
@@ -2296,190 +2272,190 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E40" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E40" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="F40" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
@@ -2488,18 +2464,18 @@
         <v>14</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
@@ -2508,18 +2484,18 @@
         <v>14</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
@@ -2528,170 +2504,170 @@
         <v>14</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E49" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E49" s="1" t="s">
-        <v>46</v>
-      </c>
       <c r="F49" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E52" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B52" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="F52" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="C53" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E53" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="C53" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="F53" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -2705,13 +2681,13 @@
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>27</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -2728,10 +2704,10 @@
         <v>17</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -2748,10 +2724,10 @@
         <v>17</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -2768,10 +2744,10 @@
         <v>17</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -2785,13 +2761,13 @@
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -2805,13 +2781,13 @@
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -2825,13 +2801,13 @@
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -2845,13 +2821,13 @@
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>60</v>
+        <v>28</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -2865,13 +2841,13 @@
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E62" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E62" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="F62" s="1" t="s">
-        <v>60</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -2888,10 +2864,10 @@
         <v>20</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -2908,10 +2884,10 @@
         <v>20</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -2928,10 +2904,10 @@
         <v>20</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -2945,13 +2921,13 @@
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -2965,13 +2941,13 @@
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -2985,13 +2961,13 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -3005,13 +2981,13 @@
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -3025,13 +3001,13 @@
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -3045,13 +3021,13 @@
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -3065,13 +3041,13 @@
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>20</v>
+        <v>119</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -3085,13 +3061,13 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>23</v>
+        <v>122</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -3105,13 +3081,13 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -3125,13 +3101,13 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -3145,13 +3121,13 @@
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>60</v>
+        <v>21</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -3165,13 +3141,13 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -3185,13 +3161,13 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -3205,13 +3181,13 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -3225,13 +3201,13 @@
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -3245,13 +3221,13 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>14</v>
+        <v>119</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -3265,13 +3241,13 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>17</v>
+        <v>122</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -3285,13 +3261,13 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>27</v>
+        <v>119</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -3305,13 +3281,13 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>27</v>
+        <v>119</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>5</v>
+        <v>45</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -3325,13 +3301,13 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>27</v>
+        <v>119</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -3345,13 +3321,13 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>27</v>
+        <v>119</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -3365,13 +3341,13 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>30</v>
+        <v>119</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -3385,13 +3361,13 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>30</v>
+        <v>122</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -3405,13 +3381,13 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>30</v>
+        <v>122</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -3425,13 +3401,13 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>30</v>
+        <v>122</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -3445,13 +3421,13 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>30</v>
+        <v>122</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -3465,10 +3441,10 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>34</v>
+        <v>122</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>5</v>
@@ -3485,13 +3461,13 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>60</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -3505,13 +3481,13 @@
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>60</v>
+        <v>5</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -3525,13 +3501,13 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>60</v>
+        <v>5</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -3545,10 +3521,10 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>5</v>
@@ -3565,10 +3541,10 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>5</v>
@@ -3585,10 +3561,10 @@
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>37</v>
+        <v>213</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>5</v>
@@ -3596,19 +3572,19 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D99" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="B99" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="E99" s="1" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>5</v>
@@ -3616,19 +3592,19 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>37</v>
+        <v>213</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>5</v>
@@ -3636,19 +3612,19 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>37</v>
+        <v>213</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>5</v>
@@ -3656,59 +3632,59 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E102" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D103" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B103" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="C103" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>221</v>
-      </c>
       <c r="E103" s="1" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -3716,19 +3692,19 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>5</v>
@@ -3736,79 +3712,79 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E106" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D107" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="B107" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="C107" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D107" s="1" t="s">
-        <v>230</v>
-      </c>
       <c r="E107" s="1" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -3816,22 +3792,22 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>5</v>
+        <v>45</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -3845,93 +3821,93 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D112" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="B112" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C112" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>239</v>
-      </c>
       <c r="E112" s="1" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>5</v>
+        <v>45</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -3945,13 +3921,13 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -3965,90 +3941,90 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D118" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="B118" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="C118" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D118" s="1" t="s">
-        <v>250</v>
-      </c>
       <c r="E118" s="1" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>5</v>
@@ -4065,10 +4041,10 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>5</v>
@@ -4085,10 +4061,10 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>5</v>
@@ -4105,10 +4081,10 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>46</v>
+        <v>4</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>5</v>
@@ -4116,19 +4092,19 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D125" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="B125" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="C125" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D125" s="1" t="s">
-        <v>263</v>
-      </c>
       <c r="E125" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>5</v>
@@ -4136,19 +4112,19 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>5</v>
@@ -4156,19 +4132,19 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>5</v>
@@ -4176,19 +4152,19 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>5</v>
@@ -4205,10 +4181,10 @@
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>5</v>
@@ -4225,10 +4201,10 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>5</v>
@@ -4236,19 +4212,19 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D131" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="B131" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="C131" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>278</v>
-      </c>
       <c r="E131" s="1" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>5</v>
@@ -4256,19 +4232,19 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>5</v>
@@ -4276,19 +4252,19 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>5</v>
@@ -4296,19 +4272,19 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>5</v>
@@ -4325,10 +4301,10 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>5</v>
@@ -4336,19 +4312,19 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D136" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="B136" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="C136" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D136" s="1" t="s">
-        <v>291</v>
-      </c>
       <c r="E136" s="1" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>5</v>
@@ -4356,19 +4332,19 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>5</v>
@@ -4376,19 +4352,19 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>5</v>
@@ -4396,22 +4372,22 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>5</v>
+        <v>45</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
@@ -4425,10 +4401,10 @@
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>5</v>
@@ -4436,19 +4412,19 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D141" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="B141" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="C141" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D141" s="1" t="s">
-        <v>302</v>
-      </c>
       <c r="E141" s="1" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>5</v>
@@ -4456,59 +4432,59 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>5</v>
+        <v>45</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>5</v>
@@ -4525,50 +4501,50 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>5</v>
+        <v>45</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D146" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="B146" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="C146" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D146" s="1" t="s">
-        <v>313</v>
-      </c>
       <c r="E146" s="1" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>5</v>
@@ -4576,19 +4552,19 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>5</v>
@@ -4596,22 +4572,22 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -4625,13 +4601,13 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>60</v>
+        <v>5</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
@@ -4645,10 +4621,10 @@
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>5</v>
@@ -4656,19 +4632,19 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D152" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="B152" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="C152" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D152" s="1" t="s">
-        <v>324</v>
-      </c>
       <c r="E152" s="1" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>5</v>
@@ -4676,19 +4652,19 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>5</v>
@@ -4696,19 +4672,19 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>5</v>
@@ -4716,19 +4692,19 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>5</v>
@@ -4745,10 +4721,10 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>5</v>
@@ -4756,19 +4732,19 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D157" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="B157" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="C157" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D157" s="1" t="s">
-        <v>337</v>
-      </c>
       <c r="E157" s="1" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>5</v>
@@ -4776,19 +4752,19 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>5</v>
@@ -4796,19 +4772,19 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>5</v>
@@ -4816,19 +4792,19 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>5</v>
@@ -4845,10 +4821,10 @@
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>5</v>
@@ -4865,10 +4841,10 @@
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>5</v>
@@ -4885,10 +4861,10 @@
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>46</v>
+        <v>4</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>5</v>
@@ -4896,19 +4872,19 @@
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D164" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="B164" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="C164" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D164" s="1" t="s">
-        <v>348</v>
-      </c>
       <c r="E164" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>5</v>
@@ -4916,19 +4892,19 @@
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>5</v>
@@ -4936,19 +4912,19 @@
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>5</v>
@@ -4956,19 +4932,19 @@
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>5</v>
@@ -4985,10 +4961,10 @@
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>5</v>
@@ -5005,10 +4981,10 @@
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>5</v>
@@ -5016,19 +4992,19 @@
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D170" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="B170" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="C170" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D170" s="1" t="s">
-        <v>363</v>
-      </c>
       <c r="E170" s="1" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>5</v>
@@ -5036,19 +5012,19 @@
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>5</v>
@@ -5056,19 +5032,19 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>5</v>
@@ -5076,16 +5052,16 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E173" s="1" t="s">
         <v>4</v>
@@ -5096,19 +5072,19 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="B174" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="C174" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D174" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="B174" s="1" t="s">
-        <v>378</v>
-      </c>
-      <c r="C174" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D174" s="1" t="s">
-        <v>376</v>
-      </c>
       <c r="E174" s="1" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>5</v>
@@ -5116,19 +5092,19 @@
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>5</v>
@@ -5136,19 +5112,19 @@
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>5</v>
@@ -5156,19 +5132,19 @@
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>5</v>
@@ -5185,10 +5161,10 @@
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>5</v>
@@ -5205,10 +5181,10 @@
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>5</v>
@@ -5216,59 +5192,59 @@
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="B180" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="C180" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D180" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="B180" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="C180" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D180" s="1" t="s">
-        <v>385</v>
-      </c>
       <c r="E180" s="1" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>5</v>
@@ -5276,101 +5252,21 @@
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A184" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="B184" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="C184" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D184" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="E184" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F184" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A185" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="B185" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="C185" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D185" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="E185" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F185" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A186" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="B186" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="C186" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D186" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="E186" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F186" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A187" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="B187" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="C187" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D187" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="E187" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F187" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/MBF04S.xlsx
+++ b/MBF04S.xlsx
@@ -46,346 +46,346 @@
     <t>PROMINA BB MARI S150</t>
   </si>
   <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>20034046</t>
+  </si>
+  <si>
+    <t>SUN MARIE BISC BLT80</t>
+  </si>
+  <si>
     <t>5</t>
   </si>
   <si>
-    <t>20034046</t>
-  </si>
-  <si>
-    <t>SUN MARIE BISC BLT80</t>
+    <t>20134698</t>
+  </si>
+  <si>
+    <t>SUN MARIE BISC KJU80</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>20134698</t>
-  </si>
-  <si>
-    <t>SUN MARIE BISC KJU80</t>
+    <t>20032058</t>
+  </si>
+  <si>
+    <t>FF KENTAL MANIS 6X37</t>
   </si>
   <si>
     <t>7</t>
   </si>
   <si>
-    <t>20032058</t>
-  </si>
-  <si>
-    <t>FF KENTAL MANIS 6X37</t>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>10015124</t>
+  </si>
+  <si>
+    <t>FF SKM COKLAT 6X37</t>
   </si>
   <si>
     <t>8</t>
   </si>
   <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>10015124</t>
-  </si>
-  <si>
-    <t>FF SKM COKLAT 6X37</t>
+    <t>20013433</t>
+  </si>
+  <si>
+    <t>INDOMILK SKM PTH6X37</t>
   </si>
   <si>
     <t>9</t>
   </si>
   <si>
-    <t>20013433</t>
-  </si>
-  <si>
-    <t>INDOMILK SKM PTH6X37</t>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>10000724</t>
+  </si>
+  <si>
+    <t>SUN BBR SS BRS/M 120</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>10031256</t>
+  </si>
+  <si>
+    <t>SUN BBR SS AYM&amp;B 120</t>
+  </si>
+  <si>
+    <t>20073496</t>
+  </si>
+  <si>
+    <t>SUN BBR SS UBI/U120G</t>
+  </si>
+  <si>
+    <t>10022197</t>
+  </si>
+  <si>
+    <t>SUN BBR.PISANG SC120</t>
+  </si>
+  <si>
+    <t>10000146</t>
+  </si>
+  <si>
+    <t>SUN KC HIJAU EKO 120</t>
+  </si>
+  <si>
+    <t>10000143</t>
+  </si>
+  <si>
+    <t>SUN BRS MERAH EKO120</t>
+  </si>
+  <si>
+    <t>20001705</t>
+  </si>
+  <si>
+    <t>MILNA BISC.6+ PSG110</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20001701</t>
+  </si>
+  <si>
+    <t>MILNA BISC.6+ ORG110</t>
+  </si>
+  <si>
+    <t>10010825</t>
+  </si>
+  <si>
+    <t>MLNA WGAN AYM+KP 120</t>
+  </si>
+  <si>
+    <t>10000720</t>
+  </si>
+  <si>
+    <t>PROMINA TIM SP&amp;WR120</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>10003707</t>
+  </si>
+  <si>
+    <t>PROMINA C.CHKN BR120</t>
+  </si>
+  <si>
+    <t>10021949</t>
+  </si>
+  <si>
+    <t>PROMINA DGNG&amp;BRO 100</t>
+  </si>
+  <si>
+    <t>20012830</t>
+  </si>
+  <si>
+    <t>PRMNA TIM AYM KP 100</t>
+  </si>
+  <si>
+    <t>20002201</t>
+  </si>
+  <si>
+    <t>PROMINA AYM,T,W 100G</t>
+  </si>
+  <si>
+    <t>20012831</t>
+  </si>
+  <si>
+    <t>PROMINA TIM SLMON100</t>
+  </si>
+  <si>
+    <t>10033560</t>
+  </si>
+  <si>
+    <t>PROMINA CHO.AVCD 100</t>
+  </si>
+  <si>
+    <t>20139959</t>
+  </si>
+  <si>
+    <t>PRMN SALMON LM 120G</t>
+  </si>
+  <si>
+    <t>20100805</t>
+  </si>
+  <si>
+    <t>PRMNA PUDNG CHO 4X25</t>
+  </si>
+  <si>
+    <t>20067680</t>
+  </si>
+  <si>
+    <t>PRMNA PUDNG STRW 100</t>
+  </si>
+  <si>
+    <t>20113322</t>
+  </si>
+  <si>
+    <t>PROMINA PASTA M&amp;C 70</t>
+  </si>
+  <si>
+    <t>20126004</t>
+  </si>
+  <si>
+    <t>PROMINA PASTA CCS 60</t>
+  </si>
+  <si>
+    <t>20126003</t>
+  </si>
+  <si>
+    <t>PRMNA MI BT AYM KP75</t>
+  </si>
+  <si>
+    <t>20135120</t>
+  </si>
+  <si>
+    <t>PRMNA SFTCRN BUTER15</t>
+  </si>
+  <si>
+    <t>10025325</t>
+  </si>
+  <si>
+    <t>PRMNA SUPMI AYM SY81</t>
+  </si>
+  <si>
+    <t>10025326</t>
+  </si>
+  <si>
+    <t>PRMN SUPMI DG&amp;SYR 84</t>
+  </si>
+  <si>
+    <t>20094437</t>
+  </si>
+  <si>
+    <t>PROMINA CRUNCHIES 20</t>
+  </si>
+  <si>
+    <t>20129287</t>
+  </si>
+  <si>
+    <t>PRMINA CRN SEAWED 20</t>
+  </si>
+  <si>
+    <t>20129288</t>
+  </si>
+  <si>
+    <t>PRMINA CRN CHKN.BR20</t>
+  </si>
+  <si>
+    <t>20136087</t>
+  </si>
+  <si>
+    <t>PRMNA SFTCRN STRWB15</t>
+  </si>
+  <si>
+    <t>20141387</t>
+  </si>
+  <si>
+    <t>PROMINA MC CHO.AL 42</t>
+  </si>
+  <si>
+    <t>20141376</t>
+  </si>
+  <si>
+    <t>PROMINA MC BL.CHS 42</t>
+  </si>
+  <si>
+    <t>20133324</t>
+  </si>
+  <si>
+    <t>PRMINA CRCKR BRCLI20</t>
+  </si>
+  <si>
+    <t>20134695</t>
+  </si>
+  <si>
+    <t>PRMNA CRCKR BRRIES20</t>
+  </si>
+  <si>
+    <t>20077368</t>
+  </si>
+  <si>
+    <t>PRMINA PUFF BNANA 15</t>
+  </si>
+  <si>
+    <t>20077369</t>
+  </si>
+  <si>
+    <t>PRMINA PUFF BLUBR 15</t>
+  </si>
+  <si>
+    <t>20092042</t>
+  </si>
+  <si>
+    <t>PRMINA PUFF STRWAP15</t>
+  </si>
+  <si>
+    <t>20139421</t>
+  </si>
+  <si>
+    <t>PRMINA YGR MLT SRW 8</t>
+  </si>
+  <si>
+    <t>20139431</t>
+  </si>
+  <si>
+    <t>PRMINA YGR MLT MLK 8</t>
+  </si>
+  <si>
+    <t>20109115</t>
+  </si>
+  <si>
+    <t>MLNA PUFFS ORG BNN15</t>
+  </si>
+  <si>
+    <t>20103062</t>
+  </si>
+  <si>
+    <t>MLNA PUFFS ORG AMB15</t>
+  </si>
+  <si>
+    <t>20103061</t>
+  </si>
+  <si>
+    <t>MLNA PUFFS ORG CHS15</t>
+  </si>
+  <si>
+    <t>20027865</t>
+  </si>
+  <si>
+    <t>MILNA SUP AYM JG 100</t>
+  </si>
+  <si>
+    <t>20027867</t>
+  </si>
+  <si>
+    <t>MILNA ATI AYM BYM120</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>20122054</t>
+  </si>
+  <si>
+    <t>MLNA BBR SLMN CB 100</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>20138171</t>
+  </si>
+  <si>
+    <t>PRMN MELTY B.STRW 42</t>
   </si>
   <si>
     <t>12</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>10000724</t>
-  </si>
-  <si>
-    <t>SUN BBR SS BRS/M 120</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>10031256</t>
-  </si>
-  <si>
-    <t>SUN BBR SS AYM&amp;B 120</t>
-  </si>
-  <si>
-    <t>20073496</t>
-  </si>
-  <si>
-    <t>SUN BBR SS UBI/U120G</t>
-  </si>
-  <si>
-    <t>10022197</t>
-  </si>
-  <si>
-    <t>SUN BBR.PISANG SC120</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>10000146</t>
-  </si>
-  <si>
-    <t>SUN KC HIJAU EKO 120</t>
-  </si>
-  <si>
-    <t>10000143</t>
-  </si>
-  <si>
-    <t>SUN BRS MERAH EKO120</t>
-  </si>
-  <si>
-    <t>20001705</t>
-  </si>
-  <si>
-    <t>MILNA BISC.6+ PSG110</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20001701</t>
-  </si>
-  <si>
-    <t>MILNA BISC.6+ ORG110</t>
-  </si>
-  <si>
-    <t>10010825</t>
-  </si>
-  <si>
-    <t>MLNA WGAN AYM+KP 120</t>
-  </si>
-  <si>
-    <t>10000720</t>
-  </si>
-  <si>
-    <t>PROMINA TIM SP&amp;WR120</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>10003707</t>
-  </si>
-  <si>
-    <t>PROMINA C.CHKN BR120</t>
-  </si>
-  <si>
-    <t>10021949</t>
-  </si>
-  <si>
-    <t>PROMINA DGNG&amp;BRO 100</t>
-  </si>
-  <si>
-    <t>20012830</t>
-  </si>
-  <si>
-    <t>PRMNA TIM AYM KP 100</t>
-  </si>
-  <si>
-    <t>20002201</t>
-  </si>
-  <si>
-    <t>PROMINA AYM,T,W 100G</t>
-  </si>
-  <si>
-    <t>20012831</t>
-  </si>
-  <si>
-    <t>PROMINA TIM SLMON100</t>
-  </si>
-  <si>
-    <t>10033560</t>
-  </si>
-  <si>
-    <t>PROMINA CHO.AVCD 100</t>
-  </si>
-  <si>
-    <t>20139959</t>
-  </si>
-  <si>
-    <t>PRMN SALMON LM 120G</t>
-  </si>
-  <si>
-    <t>20100805</t>
-  </si>
-  <si>
-    <t>PRMNA PUDNG CHO 4X25</t>
-  </si>
-  <si>
-    <t>20067680</t>
-  </si>
-  <si>
-    <t>PRMNA PUDNG STRW 100</t>
-  </si>
-  <si>
-    <t>20113322</t>
-  </si>
-  <si>
-    <t>PROMINA PASTA M&amp;C 70</t>
-  </si>
-  <si>
-    <t>20126004</t>
-  </si>
-  <si>
-    <t>PROMINA PASTA CCS 60</t>
-  </si>
-  <si>
-    <t>20126003</t>
-  </si>
-  <si>
-    <t>PRMNA MI BT AYM KP75</t>
-  </si>
-  <si>
-    <t>20135120</t>
-  </si>
-  <si>
-    <t>PRMNA SFTCRN BUTER15</t>
-  </si>
-  <si>
-    <t>10025325</t>
-  </si>
-  <si>
-    <t>PRMNA SUPMI AYM SY81</t>
-  </si>
-  <si>
-    <t>10025326</t>
-  </si>
-  <si>
-    <t>PRMN SUPMI DG&amp;SYR 84</t>
-  </si>
-  <si>
-    <t>20094437</t>
-  </si>
-  <si>
-    <t>PROMINA CRUNCHIES 20</t>
-  </si>
-  <si>
-    <t>20129287</t>
-  </si>
-  <si>
-    <t>PRMINA CRN SEAWED 20</t>
-  </si>
-  <si>
-    <t>20129288</t>
-  </si>
-  <si>
-    <t>PRMINA CRN CHKN.BR20</t>
-  </si>
-  <si>
-    <t>20136087</t>
-  </si>
-  <si>
-    <t>PRMNA SFTCRN STRWB15</t>
-  </si>
-  <si>
-    <t>20141387</t>
-  </si>
-  <si>
-    <t>PROMINA MC CHO.AL 42</t>
-  </si>
-  <si>
-    <t>20141376</t>
-  </si>
-  <si>
-    <t>PROMINA MC BL.CHS 42</t>
-  </si>
-  <si>
-    <t>20133324</t>
-  </si>
-  <si>
-    <t>PRMINA CRCKR BRCLI20</t>
-  </si>
-  <si>
-    <t>20134695</t>
-  </si>
-  <si>
-    <t>PRMNA CRCKR BRRIES20</t>
-  </si>
-  <si>
-    <t>20077368</t>
-  </si>
-  <si>
-    <t>PRMINA PUFF BNANA 15</t>
-  </si>
-  <si>
-    <t>20077369</t>
-  </si>
-  <si>
-    <t>PRMINA PUFF BLUBR 15</t>
-  </si>
-  <si>
-    <t>20092042</t>
-  </si>
-  <si>
-    <t>PRMINA PUFF STRWAP15</t>
-  </si>
-  <si>
-    <t>20139421</t>
-  </si>
-  <si>
-    <t>PRMINA YGR MLT SRW 8</t>
-  </si>
-  <si>
-    <t>20139431</t>
-  </si>
-  <si>
-    <t>PRMINA YGR MLT MLK 8</t>
-  </si>
-  <si>
-    <t>20109115</t>
-  </si>
-  <si>
-    <t>MLNA PUFFS ORG BNN15</t>
-  </si>
-  <si>
-    <t>20103062</t>
-  </si>
-  <si>
-    <t>MLNA PUFFS ORG AMB15</t>
-  </si>
-  <si>
-    <t>20103061</t>
-  </si>
-  <si>
-    <t>MLNA PUFFS ORG CHS15</t>
-  </si>
-  <si>
-    <t>20027865</t>
-  </si>
-  <si>
-    <t>MILNA SUP AYM JG 100</t>
-  </si>
-  <si>
-    <t>20027867</t>
-  </si>
-  <si>
-    <t>MILNA ATI AYM BYM120</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>20122054</t>
-  </si>
-  <si>
-    <t>MLNA BBR SLMN CB 100</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>20138171</t>
-  </si>
-  <si>
-    <t>PRMN MELTY B.STRW 42</t>
   </si>
   <si>
     <t>20137013</t>
@@ -1864,7 +1864,7 @@
         <v>31</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>5</v>
@@ -1872,10 +1872,10 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
@@ -1884,7 +1884,7 @@
         <v>31</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>5</v>
@@ -1892,10 +1892,10 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>42</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
@@ -1904,7 +1904,7 @@
         <v>31</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>5</v>
@@ -1912,10 +1912,10 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>44</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
@@ -1924,18 +1924,18 @@
         <v>31</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>47</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
@@ -1944,7 +1944,7 @@
         <v>31</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>28</v>
@@ -1952,10 +1952,10 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>49</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
@@ -1964,18 +1964,18 @@
         <v>31</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>50</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>51</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
@@ -1987,15 +1987,15 @@
         <v>4</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>54</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
@@ -2012,10 +2012,10 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
@@ -2032,10 +2032,10 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>57</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>58</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
@@ -2044,18 +2044,18 @@
         <v>8</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>60</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
@@ -2064,7 +2064,7 @@
         <v>8</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>5</v>
@@ -2072,10 +2072,10 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>62</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
@@ -2084,7 +2084,7 @@
         <v>8</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>5</v>
@@ -2092,10 +2092,10 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>64</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
@@ -2104,18 +2104,18 @@
         <v>8</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
@@ -2124,7 +2124,7 @@
         <v>8</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>5</v>
@@ -2132,16 +2132,16 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>68</v>
-      </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>4</v>
@@ -2152,16 +2152,16 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>70</v>
-      </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>31</v>
@@ -2172,16 +2172,16 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>8</v>
@@ -2192,19 +2192,19 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B30" s="1" t="s">
-        <v>74</v>
-      </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>5</v>
@@ -2212,19 +2212,19 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B31" s="1" t="s">
-        <v>76</v>
-      </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>28</v>
@@ -2232,19 +2232,19 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B32" s="1" t="s">
-        <v>78</v>
-      </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>28</v>
@@ -2252,19 +2252,19 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B33" s="1" t="s">
-        <v>80</v>
-      </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>5</v>
@@ -2272,19 +2272,19 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B34" s="1" t="s">
-        <v>82</v>
-      </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>5</v>
@@ -2292,16 +2292,16 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B35" s="1" t="s">
-        <v>84</v>
-      </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>4</v>
@@ -2312,16 +2312,16 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B36" s="1" t="s">
-        <v>86</v>
-      </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>31</v>
@@ -2332,16 +2332,16 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B37" s="1" t="s">
-        <v>88</v>
-      </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>8</v>
@@ -2352,19 +2352,19 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B38" s="1" t="s">
-        <v>90</v>
-      </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E38" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>38</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>28</v>
@@ -2372,19 +2372,19 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B39" s="1" t="s">
-        <v>92</v>
-      </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>28</v>
@@ -2392,19 +2392,19 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B40" s="1" t="s">
-        <v>94</v>
-      </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>28</v>
@@ -2412,19 +2412,19 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B41" s="1" t="s">
-        <v>96</v>
-      </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>28</v>
@@ -2432,19 +2432,19 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B42" s="1" t="s">
-        <v>98</v>
-      </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>28</v>
@@ -2452,16 +2452,16 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B43" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B43" s="1" t="s">
-        <v>100</v>
-      </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>4</v>
@@ -2472,16 +2472,16 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B44" s="1" t="s">
-        <v>102</v>
-      </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>31</v>
@@ -2492,16 +2492,16 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B45" s="1" t="s">
-        <v>104</v>
-      </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>8</v>
@@ -2512,19 +2512,19 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B46" s="1" t="s">
-        <v>106</v>
-      </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>28</v>
@@ -2532,19 +2532,19 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B47" s="1" t="s">
-        <v>108</v>
-      </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E47" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>28</v>
@@ -2552,19 +2552,19 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B48" s="1" t="s">
-        <v>110</v>
-      </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>28</v>
@@ -2572,19 +2572,19 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B49" s="1" t="s">
-        <v>112</v>
-      </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>28</v>
@@ -2592,19 +2592,19 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B50" s="1" t="s">
-        <v>114</v>
-      </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>28</v>
@@ -2612,19 +2612,19 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B51" s="1" t="s">
-        <v>116</v>
-      </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>28</v>
@@ -2632,19 +2632,19 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="C52" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E52" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>119</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>28</v>
@@ -2652,19 +2652,19 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="C53" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E53" s="1" t="s">
         <v>121</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>122</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>28</v>
@@ -2672,19 +2672,19 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="C54" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E54" s="1" t="s">
         <v>124</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>28</v>
@@ -2701,7 +2701,7 @@
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>4</v>
@@ -2721,7 +2721,7 @@
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>31</v>
@@ -2741,7 +2741,7 @@
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>8</v>
@@ -2761,13 +2761,13 @@
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -2781,13 +2781,13 @@
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -2801,10 +2801,10 @@
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E60" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>28</v>
@@ -2821,10 +2821,10 @@
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>28</v>
@@ -2841,10 +2841,10 @@
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>5</v>
@@ -2861,7 +2861,7 @@
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>4</v>
@@ -2881,7 +2881,7 @@
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>31</v>
@@ -2901,7 +2901,7 @@
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>8</v>
@@ -2921,10 +2921,10 @@
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>21</v>
@@ -2941,10 +2941,10 @@
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>21</v>
@@ -2961,10 +2961,10 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>28</v>
@@ -2981,10 +2981,10 @@
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E69" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>28</v>
@@ -3001,10 +3001,10 @@
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>28</v>
@@ -3021,10 +3021,10 @@
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>21</v>
@@ -3041,10 +3041,10 @@
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>28</v>
@@ -3061,13 +3061,13 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -3081,7 +3081,7 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>4</v>
@@ -3101,7 +3101,7 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>31</v>
@@ -3121,7 +3121,7 @@
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>8</v>
@@ -3141,10 +3141,10 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>21</v>
@@ -3161,10 +3161,10 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>28</v>
@@ -3181,10 +3181,10 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>28</v>
@@ -3201,10 +3201,10 @@
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -3221,10 +3221,10 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>21</v>
@@ -3241,10 +3241,10 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>28</v>
@@ -3261,13 +3261,13 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -3281,13 +3281,13 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -3301,13 +3301,13 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -3321,13 +3321,13 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -3341,13 +3341,13 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -3361,7 +3361,7 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>4</v>
@@ -3381,13 +3381,13 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -3401,13 +3401,13 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -3421,13 +3421,13 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -3441,10 +3441,10 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>5</v>
@@ -3461,7 +3461,7 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>27</v>
+        <v>124</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>4</v>
@@ -3481,7 +3481,7 @@
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>27</v>
+        <v>124</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>31</v>
@@ -3501,7 +3501,7 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>27</v>
+        <v>124</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>8</v>
@@ -3521,10 +3521,10 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>27</v>
+        <v>124</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>5</v>
@@ -3541,10 +3541,10 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>27</v>
+        <v>124</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>5</v>
@@ -3624,7 +3624,7 @@
         <v>213</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>5</v>
@@ -3704,7 +3704,7 @@
         <v>222</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>5</v>
@@ -3784,7 +3784,7 @@
         <v>231</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -3804,10 +3804,10 @@
         <v>231</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -3827,7 +3827,7 @@
         <v>4</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -3847,7 +3847,7 @@
         <v>31</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -3867,7 +3867,7 @@
         <v>8</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -3884,10 +3884,10 @@
         <v>242</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -3904,7 +3904,7 @@
         <v>242</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>28</v>
@@ -3924,10 +3924,10 @@
         <v>242</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -4004,7 +4004,7 @@
         <v>255</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>5</v>
@@ -4024,7 +4024,7 @@
         <v>255</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>5</v>
@@ -4044,7 +4044,7 @@
         <v>255</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>5</v>
@@ -4064,7 +4064,7 @@
         <v>255</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>5</v>
@@ -4144,7 +4144,7 @@
         <v>270</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>5</v>
@@ -4164,7 +4164,7 @@
         <v>270</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>5</v>
@@ -4184,7 +4184,7 @@
         <v>270</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>5</v>
@@ -4264,7 +4264,7 @@
         <v>283</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>5</v>
@@ -4284,7 +4284,7 @@
         <v>283</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>5</v>
@@ -4364,7 +4364,7 @@
         <v>294</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>5</v>
@@ -4384,10 +4384,10 @@
         <v>294</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
@@ -4447,7 +4447,7 @@
         <v>8</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -4464,7 +4464,7 @@
         <v>305</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>5</v>
@@ -4484,7 +4484,7 @@
         <v>305</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>5</v>
@@ -4507,7 +4507,7 @@
         <v>4</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -4527,7 +4527,7 @@
         <v>31</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -4564,7 +4564,7 @@
         <v>316</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>5</v>
@@ -4584,7 +4584,7 @@
         <v>316</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>5</v>
@@ -4604,7 +4604,7 @@
         <v>316</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>5</v>
@@ -4684,7 +4684,7 @@
         <v>329</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>5</v>
@@ -4704,7 +4704,7 @@
         <v>329</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>5</v>
@@ -4784,7 +4784,7 @@
         <v>340</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>5</v>
@@ -4804,7 +4804,7 @@
         <v>340</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>5</v>
@@ -4824,7 +4824,7 @@
         <v>340</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>5</v>
@@ -4844,7 +4844,7 @@
         <v>340</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>5</v>
@@ -4924,7 +4924,7 @@
         <v>355</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>5</v>
@@ -4944,7 +4944,7 @@
         <v>355</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>5</v>
@@ -4964,7 +4964,7 @@
         <v>355</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>5</v>
@@ -5044,7 +5044,7 @@
         <v>368</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>5</v>
@@ -5124,7 +5124,7 @@
         <v>377</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>5</v>
@@ -5144,7 +5144,7 @@
         <v>377</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>5</v>
@@ -5164,7 +5164,7 @@
         <v>377</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>5</v>
@@ -5244,7 +5244,7 @@
         <v>390</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>5</v>
@@ -5264,7 +5264,7 @@
         <v>390</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>5</v>

--- a/MBF04S.xlsx
+++ b/MBF04S.xlsx
@@ -466,6 +466,12 @@
     <t>FF GOLD SKM PTH 240G</t>
   </si>
   <si>
+    <t>20142228</t>
+  </si>
+  <si>
+    <t>CAP ENAK CHOCO 535G</t>
+  </si>
+  <si>
     <t>20094283</t>
   </si>
   <si>
@@ -524,12 +530,6 @@
   </si>
   <si>
     <t>FF SKM CKLT KLG 370</t>
-  </si>
-  <si>
-    <t>20136704</t>
-  </si>
-  <si>
-    <t>INDOMLK KM DURIAN370</t>
   </si>
   <si>
     <t>10000021</t>
@@ -3027,7 +3027,7 @@
         <v>27</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -3047,7 +3047,7 @@
         <v>118</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -3067,7 +3067,7 @@
         <v>121</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -3081,13 +3081,13 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>4</v>
+        <v>124</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>21</v>
+        <v>51</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -3104,7 +3104,7 @@
         <v>27</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>21</v>
@@ -3124,7 +3124,7 @@
         <v>27</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>21</v>
@@ -3144,7 +3144,7 @@
         <v>27</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>21</v>
@@ -3164,10 +3164,10 @@
         <v>27</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">

--- a/MBF04S.xlsx
+++ b/MBF04S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1098" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1128" uniqueCount="409">
   <si>
     <t/>
   </si>
@@ -37,34 +37,697 @@
     <t>NESTLE BR PSG&amp;SUS120</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>20001705</t>
+  </si>
+  <si>
+    <t>MILNA BISC.6+ PSG110</t>
+  </si>
+  <si>
     <t>3</t>
   </si>
   <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20001701</t>
+  </si>
+  <si>
+    <t>MILNA BISC.6+ ORG110</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20068905</t>
+  </si>
+  <si>
+    <t>FF SKM PUTIH 535G</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20068906</t>
+  </si>
+  <si>
+    <t>FF SKM COKELAT 535G</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>20118115</t>
+  </si>
+  <si>
+    <t>FRISIAN FLAG PTH 240</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>20112945</t>
+  </si>
+  <si>
+    <t>FF SKM COKLAT 240G</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>20121733</t>
+  </si>
+  <si>
+    <t>FF GOLD SKM PTH 240G</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>20094283</t>
+  </si>
+  <si>
+    <t>INDOMILK KM PTH 535G</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>20120855</t>
+  </si>
+  <si>
+    <t>INDOMILK SWIS CHO535</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>10000724</t>
+  </si>
+  <si>
+    <t>SUN BBR SS BRS/M 120</t>
+  </si>
+  <si>
+    <t>10031256</t>
+  </si>
+  <si>
+    <t>SUN BBR SS AYM&amp;B 120</t>
+  </si>
+  <si>
+    <t>20073496</t>
+  </si>
+  <si>
+    <t>SUN BBR SS UBI/U120G</t>
+  </si>
+  <si>
+    <t>10022197</t>
+  </si>
+  <si>
+    <t>SUN BBR.PISANG SC120</t>
+  </si>
+  <si>
+    <t>10000146</t>
+  </si>
+  <si>
+    <t>SUN KC HIJAU EKO 120</t>
+  </si>
+  <si>
+    <t>10000143</t>
+  </si>
+  <si>
+    <t>SUN BRS MERAH EKO120</t>
+  </si>
+  <si>
     <t>10003111</t>
   </si>
   <si>
     <t>PROMINA BB MARI S150</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
     <t>20034046</t>
   </si>
   <si>
     <t>SUN MARIE BISC BLT80</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
     <t>20134698</t>
   </si>
   <si>
     <t>SUN MARIE BISC KJU80</t>
   </si>
   <si>
-    <t>6</t>
+    <t>20138171</t>
+  </si>
+  <si>
+    <t>PRMN MELTY B.STRW 42</t>
+  </si>
+  <si>
+    <t>10010825</t>
+  </si>
+  <si>
+    <t>MLNA WGAN AYM+KP 120</t>
+  </si>
+  <si>
+    <t>10000720</t>
+  </si>
+  <si>
+    <t>PROMINA TIM SP&amp;WR120</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>10003707</t>
+  </si>
+  <si>
+    <t>PROMINA C.CHKN BR120</t>
+  </si>
+  <si>
+    <t>10021949</t>
+  </si>
+  <si>
+    <t>PROMINA DGNG&amp;BRO 100</t>
+  </si>
+  <si>
+    <t>20012830</t>
+  </si>
+  <si>
+    <t>PRMNA TIM AYM KP 100</t>
+  </si>
+  <si>
+    <t>20002201</t>
+  </si>
+  <si>
+    <t>PROMINA AYM,T,W 100G</t>
+  </si>
+  <si>
+    <t>20012831</t>
+  </si>
+  <si>
+    <t>PROMINA TIM SLMON100</t>
+  </si>
+  <si>
+    <t>10033560</t>
+  </si>
+  <si>
+    <t>PROMINA CHO.AVCD 100</t>
+  </si>
+  <si>
+    <t>20141377</t>
+  </si>
+  <si>
+    <t>PROMNA PSTA BLOGNESE</t>
+  </si>
+  <si>
+    <t>20100805</t>
+  </si>
+  <si>
+    <t>PRMNA PUDNG CHO 4X25</t>
+  </si>
+  <si>
+    <t>20067680</t>
+  </si>
+  <si>
+    <t>PRMNA PUDNG STRW 100</t>
+  </si>
+  <si>
+    <t>20113322</t>
+  </si>
+  <si>
+    <t>PROMINA PASTA M&amp;C 70</t>
+  </si>
+  <si>
+    <t>20126004</t>
+  </si>
+  <si>
+    <t>PROMINA PASTA CCS 60</t>
+  </si>
+  <si>
+    <t>20126003</t>
+  </si>
+  <si>
+    <t>PRMNA MI BT AYM KP75</t>
+  </si>
+  <si>
+    <t>10025325</t>
+  </si>
+  <si>
+    <t>PRMNA SUPMI AYM SY81</t>
+  </si>
+  <si>
+    <t>10025326</t>
+  </si>
+  <si>
+    <t>PRMN SUPMI DG&amp;SYR 84</t>
+  </si>
+  <si>
+    <t>20135120</t>
+  </si>
+  <si>
+    <t>PRMNA SFTCRN BUTER15</t>
+  </si>
+  <si>
+    <t>20094437</t>
+  </si>
+  <si>
+    <t>PROMINA CRUNCHIES 20</t>
+  </si>
+  <si>
+    <t>20129287</t>
+  </si>
+  <si>
+    <t>PRMINA CRN SEAWED 20</t>
+  </si>
+  <si>
+    <t>20129288</t>
+  </si>
+  <si>
+    <t>PRMINA CRN CHKN.BR20</t>
+  </si>
+  <si>
+    <t>20136087</t>
+  </si>
+  <si>
+    <t>PRMNA SFTCRN STRWB15</t>
+  </si>
+  <si>
+    <t>20141387</t>
+  </si>
+  <si>
+    <t>PROMINA MC CHO.AL 42</t>
+  </si>
+  <si>
+    <t>20141376</t>
+  </si>
+  <si>
+    <t>PROMINA MC BL.CHS 42</t>
+  </si>
+  <si>
+    <t>20133324</t>
+  </si>
+  <si>
+    <t>PRMINA CRCKR BRCLI20</t>
+  </si>
+  <si>
+    <t>20134695</t>
+  </si>
+  <si>
+    <t>PRMNA CRCKR BRRIES20</t>
+  </si>
+  <si>
+    <t>20077368</t>
+  </si>
+  <si>
+    <t>PRMINA PUFF BNANA 15</t>
+  </si>
+  <si>
+    <t>20077369</t>
+  </si>
+  <si>
+    <t>PRMINA PUFF BLUBR 15</t>
+  </si>
+  <si>
+    <t>20092042</t>
+  </si>
+  <si>
+    <t>PRMINA PUFF STRWAP15</t>
+  </si>
+  <si>
+    <t>20138373</t>
+  </si>
+  <si>
+    <t>PROMINA PUFF WGYU 15</t>
+  </si>
+  <si>
+    <t>20139421</t>
+  </si>
+  <si>
+    <t>PRMINA YGR MLT SRW 8</t>
+  </si>
+  <si>
+    <t>20139431</t>
+  </si>
+  <si>
+    <t>PRMINA YGR MLT MLK 8</t>
+  </si>
+  <si>
+    <t>20138655</t>
+  </si>
+  <si>
+    <t>MILNA PUFFS SWEED 13</t>
+  </si>
+  <si>
+    <t>20109115</t>
+  </si>
+  <si>
+    <t>MLNA PUFFS ORG BNN15</t>
+  </si>
+  <si>
+    <t>20103062</t>
+  </si>
+  <si>
+    <t>MLNA PUFFS ORG AMB15</t>
+  </si>
+  <si>
+    <t>20103061</t>
+  </si>
+  <si>
+    <t>MLNA PUFFS ORG CHS15</t>
+  </si>
+  <si>
+    <t>20027865</t>
+  </si>
+  <si>
+    <t>MILNA SUP AYM JG 100</t>
+  </si>
+  <si>
+    <t>20027867</t>
+  </si>
+  <si>
+    <t>MILNA ATI AYM BYM120</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>20122054</t>
+  </si>
+  <si>
+    <t>MLNA BBR SLMN CB 100</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>20137013</t>
+  </si>
+  <si>
+    <t>MILNA CRNCH CHSE 20G</t>
+  </si>
+  <si>
+    <t>20138656</t>
+  </si>
+  <si>
+    <t>MILNA CRN BERIES 20</t>
+  </si>
+  <si>
+    <t>20115159</t>
+  </si>
+  <si>
+    <t>MLNA RC.CRAC BNANA20</t>
+  </si>
+  <si>
+    <t>20115158</t>
+  </si>
+  <si>
+    <t>MLNA RC.CRACK SPC 20</t>
+  </si>
+  <si>
+    <t>20092863</t>
+  </si>
+  <si>
+    <t>YB BABY CRCK STRW 25</t>
+  </si>
+  <si>
+    <t>20080924</t>
+  </si>
+  <si>
+    <t>YB BABY CRACK BNN 25</t>
+  </si>
+  <si>
+    <t>20138661</t>
+  </si>
+  <si>
+    <t>BROMON CKS MIX.F 100</t>
+  </si>
+  <si>
+    <t>20138660</t>
+  </si>
+  <si>
+    <t>BOROMON CKS MILK 100</t>
+  </si>
+  <si>
+    <t>20125783</t>
+  </si>
+  <si>
+    <t>CAP/ENAK KKM PTH 535</t>
+  </si>
+  <si>
+    <t>20142228</t>
+  </si>
+  <si>
+    <t>CAP ENAK CHOCO 535G</t>
+  </si>
+  <si>
+    <t>10005489</t>
+  </si>
+  <si>
+    <t>FF KENTAL MANIS 370G</t>
+  </si>
+  <si>
+    <t>10000255</t>
+  </si>
+  <si>
+    <t>FF GOLD SKM PTH 370G</t>
+  </si>
+  <si>
+    <t>20089819</t>
+  </si>
+  <si>
+    <t>FF KENTAL MANIS 490G</t>
+  </si>
+  <si>
+    <t>10000021</t>
+  </si>
+  <si>
+    <t>ENAK K/MNS PUTIH 370</t>
+  </si>
+  <si>
+    <t>20002313</t>
+  </si>
+  <si>
+    <t>FF KRM MNS OMELA 370</t>
+  </si>
+  <si>
+    <t>20054589</t>
+  </si>
+  <si>
+    <t>3SAPI KRIMER 490G</t>
+  </si>
+  <si>
+    <t>10036665</t>
+  </si>
+  <si>
+    <t>CARNATION KKM 365G</t>
+  </si>
+  <si>
+    <t>20105631</t>
+  </si>
+  <si>
+    <t>CARNATION KKM 405G</t>
+  </si>
+  <si>
+    <t>20101859</t>
+  </si>
+  <si>
+    <t>SUNBAY EVP.MILK 380G</t>
+  </si>
+  <si>
+    <t>20136510</t>
+  </si>
+  <si>
+    <t>MILO 3IN1 ACT-GO 400</t>
+  </si>
+  <si>
+    <t>20027850</t>
+  </si>
+  <si>
+    <t>ZEE VNILA TWST 340G</t>
+  </si>
+  <si>
+    <t>20027848</t>
+  </si>
+  <si>
+    <t>ZEE SWIZZ CHO 340G</t>
+  </si>
+  <si>
+    <t>10033006</t>
+  </si>
+  <si>
+    <t>PRENAGEN HML CHO 180</t>
+  </si>
+  <si>
+    <t>20011063</t>
+  </si>
+  <si>
+    <t>PRENAGEN HML CHO 360</t>
+  </si>
+  <si>
+    <t>20033353</t>
+  </si>
+  <si>
+    <t>HILO/S HI-CAL CHO250</t>
+  </si>
+  <si>
+    <t>10000578</t>
+  </si>
+  <si>
+    <t>DIABETASOL VNL.170GR</t>
+  </si>
+  <si>
+    <t>20139959</t>
+  </si>
+  <si>
+    <t>PRMN SALMON LM 120G</t>
+  </si>
+  <si>
+    <t>10000088</t>
+  </si>
+  <si>
+    <t>FF SKM CKLT KLG 370</t>
+  </si>
+  <si>
+    <t>10015124</t>
+  </si>
+  <si>
+    <t>FF SKM COKLAT 6X37</t>
+  </si>
+  <si>
+    <t>20141099</t>
+  </si>
+  <si>
+    <t>FF CRMY GULA ARN 240</t>
+  </si>
+  <si>
+    <t>20125788</t>
+  </si>
+  <si>
+    <t>HLTHYWY1+ SP MADU700</t>
+  </si>
+  <si>
+    <t>20125790</t>
+  </si>
+  <si>
+    <t>HLTHYWY3+ SB MADU700</t>
+  </si>
+  <si>
+    <t>20135200</t>
+  </si>
+  <si>
+    <t>VIDORAN BABY0-6 550G</t>
+  </si>
+  <si>
+    <t>20129773</t>
+  </si>
+  <si>
+    <t>VDORAN BABY6-12 550G</t>
+  </si>
+  <si>
+    <t>20098368</t>
+  </si>
+  <si>
+    <t>VDORAN XMRT1+ VAN325</t>
+  </si>
+  <si>
+    <t>20098371</t>
+  </si>
+  <si>
+    <t>VDORAN SUSU MADU 350</t>
+  </si>
+  <si>
+    <t>20070110</t>
+  </si>
+  <si>
+    <t>VDORAN XMRT1+ MDU700</t>
+  </si>
+  <si>
+    <t>20090042</t>
+  </si>
+  <si>
+    <t>VDORAN XMRT1+ VAN700</t>
+  </si>
+  <si>
+    <t>20082394</t>
+  </si>
+  <si>
+    <t>VDORAN XMRT3+ MDU700</t>
+  </si>
+  <si>
+    <t>20090437</t>
+  </si>
+  <si>
+    <t>VDORAN XMRT3+ VAN700</t>
+  </si>
+  <si>
+    <t>20117985</t>
+  </si>
+  <si>
+    <t>VIDORAN XM5+ MADU700</t>
+  </si>
+  <si>
+    <t>20098370</t>
+  </si>
+  <si>
+    <t>VDORAN XMRT1+ MDU350</t>
+  </si>
+  <si>
+    <t>20098369</t>
+  </si>
+  <si>
+    <t>VDORAN XMRT3+ VAN350</t>
+  </si>
+  <si>
+    <t>20117983</t>
+  </si>
+  <si>
+    <t>VIDORAN XM5+ COKL700</t>
+  </si>
+  <si>
+    <t>20106381</t>
+  </si>
+  <si>
+    <t>VDRAN XMRT3+ MDU 900</t>
+  </si>
+  <si>
+    <t>20117981</t>
+  </si>
+  <si>
+    <t>VIDORAN XM3+ VNL900</t>
+  </si>
+  <si>
+    <t>20138473</t>
+  </si>
+  <si>
+    <t>VDORAN BABY6-12 900G</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>20138474</t>
+  </si>
+  <si>
+    <t>VIDORAN 5  MADU 900G</t>
+  </si>
+  <si>
+    <t>20113346</t>
+  </si>
+  <si>
+    <t>VDRAN XMRT1+ VAN 900</t>
+  </si>
+  <si>
+    <t>20101825</t>
+  </si>
+  <si>
+    <t>VDRAN XMRT1+ MDU 900</t>
   </si>
   <si>
     <t>20032058</t>
@@ -73,19 +736,7 @@
     <t>FF KENTAL MANIS 6X37</t>
   </si>
   <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>10015124</t>
-  </si>
-  <si>
-    <t>FF SKM COKLAT 6X37</t>
-  </si>
-  <si>
-    <t>8</t>
+    <t>15</t>
   </si>
   <si>
     <t>20013433</t>
@@ -94,466 +745,40 @@
     <t>INDOMILK SKM PTH6X37</t>
   </si>
   <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>10000724</t>
-  </si>
-  <si>
-    <t>SUN BBR SS BRS/M 120</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>10031256</t>
-  </si>
-  <si>
-    <t>SUN BBR SS AYM&amp;B 120</t>
-  </si>
-  <si>
-    <t>20073496</t>
-  </si>
-  <si>
-    <t>SUN BBR SS UBI/U120G</t>
-  </si>
-  <si>
-    <t>10022197</t>
-  </si>
-  <si>
-    <t>SUN BBR.PISANG SC120</t>
-  </si>
-  <si>
-    <t>10000146</t>
-  </si>
-  <si>
-    <t>SUN KC HIJAU EKO 120</t>
-  </si>
-  <si>
-    <t>10000143</t>
-  </si>
-  <si>
-    <t>SUN BRS MERAH EKO120</t>
-  </si>
-  <si>
-    <t>20001705</t>
-  </si>
-  <si>
-    <t>MILNA BISC.6+ PSG110</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20001701</t>
-  </si>
-  <si>
-    <t>MILNA BISC.6+ ORG110</t>
-  </si>
-  <si>
-    <t>10010825</t>
-  </si>
-  <si>
-    <t>MLNA WGAN AYM+KP 120</t>
-  </si>
-  <si>
-    <t>10000720</t>
-  </si>
-  <si>
-    <t>PROMINA TIM SP&amp;WR120</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>10003707</t>
-  </si>
-  <si>
-    <t>PROMINA C.CHKN BR120</t>
-  </si>
-  <si>
-    <t>10021949</t>
-  </si>
-  <si>
-    <t>PROMINA DGNG&amp;BRO 100</t>
-  </si>
-  <si>
-    <t>20012830</t>
-  </si>
-  <si>
-    <t>PRMNA TIM AYM KP 100</t>
-  </si>
-  <si>
-    <t>20002201</t>
-  </si>
-  <si>
-    <t>PROMINA AYM,T,W 100G</t>
-  </si>
-  <si>
-    <t>20012831</t>
-  </si>
-  <si>
-    <t>PROMINA TIM SLMON100</t>
-  </si>
-  <si>
-    <t>10033560</t>
-  </si>
-  <si>
-    <t>PROMINA CHO.AVCD 100</t>
-  </si>
-  <si>
-    <t>20139959</t>
-  </si>
-  <si>
-    <t>PRMN SALMON LM 120G</t>
-  </si>
-  <si>
-    <t>20100805</t>
-  </si>
-  <si>
-    <t>PRMNA PUDNG CHO 4X25</t>
-  </si>
-  <si>
-    <t>20067680</t>
-  </si>
-  <si>
-    <t>PRMNA PUDNG STRW 100</t>
-  </si>
-  <si>
-    <t>20113322</t>
-  </si>
-  <si>
-    <t>PROMINA PASTA M&amp;C 70</t>
-  </si>
-  <si>
-    <t>20126004</t>
-  </si>
-  <si>
-    <t>PROMINA PASTA CCS 60</t>
-  </si>
-  <si>
-    <t>20126003</t>
-  </si>
-  <si>
-    <t>PRMNA MI BT AYM KP75</t>
-  </si>
-  <si>
-    <t>20135120</t>
-  </si>
-  <si>
-    <t>PRMNA SFTCRN BUTER15</t>
-  </si>
-  <si>
-    <t>10025325</t>
-  </si>
-  <si>
-    <t>PRMNA SUPMI AYM SY81</t>
-  </si>
-  <si>
-    <t>10025326</t>
-  </si>
-  <si>
-    <t>PRMN SUPMI DG&amp;SYR 84</t>
-  </si>
-  <si>
-    <t>20094437</t>
-  </si>
-  <si>
-    <t>PROMINA CRUNCHIES 20</t>
-  </si>
-  <si>
-    <t>20129287</t>
-  </si>
-  <si>
-    <t>PRMINA CRN SEAWED 20</t>
-  </si>
-  <si>
-    <t>20129288</t>
-  </si>
-  <si>
-    <t>PRMINA CRN CHKN.BR20</t>
-  </si>
-  <si>
-    <t>20136087</t>
-  </si>
-  <si>
-    <t>PRMNA SFTCRN STRWB15</t>
-  </si>
-  <si>
-    <t>20141387</t>
-  </si>
-  <si>
-    <t>PROMINA MC CHO.AL 42</t>
-  </si>
-  <si>
-    <t>20141376</t>
-  </si>
-  <si>
-    <t>PROMINA MC BL.CHS 42</t>
-  </si>
-  <si>
-    <t>20133324</t>
-  </si>
-  <si>
-    <t>PRMINA CRCKR BRCLI20</t>
-  </si>
-  <si>
-    <t>20134695</t>
-  </si>
-  <si>
-    <t>PRMNA CRCKR BRRIES20</t>
-  </si>
-  <si>
-    <t>20077368</t>
-  </si>
-  <si>
-    <t>PRMINA PUFF BNANA 15</t>
-  </si>
-  <si>
-    <t>20077369</t>
-  </si>
-  <si>
-    <t>PRMINA PUFF BLUBR 15</t>
-  </si>
-  <si>
-    <t>20092042</t>
-  </si>
-  <si>
-    <t>PRMINA PUFF STRWAP15</t>
-  </si>
-  <si>
-    <t>20139421</t>
-  </si>
-  <si>
-    <t>PRMINA YGR MLT SRW 8</t>
-  </si>
-  <si>
-    <t>20139431</t>
-  </si>
-  <si>
-    <t>PRMINA YGR MLT MLK 8</t>
-  </si>
-  <si>
-    <t>20109115</t>
-  </si>
-  <si>
-    <t>MLNA PUFFS ORG BNN15</t>
-  </si>
-  <si>
-    <t>20103062</t>
-  </si>
-  <si>
-    <t>MLNA PUFFS ORG AMB15</t>
-  </si>
-  <si>
-    <t>20103061</t>
-  </si>
-  <si>
-    <t>MLNA PUFFS ORG CHS15</t>
-  </si>
-  <si>
-    <t>20027865</t>
-  </si>
-  <si>
-    <t>MILNA SUP AYM JG 100</t>
-  </si>
-  <si>
-    <t>20027867</t>
-  </si>
-  <si>
-    <t>MILNA ATI AYM BYM120</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>20122054</t>
-  </si>
-  <si>
-    <t>MLNA BBR SLMN CB 100</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>20138171</t>
-  </si>
-  <si>
-    <t>PRMN MELTY B.STRW 42</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>20137013</t>
-  </si>
-  <si>
-    <t>MILNA CRNCH CHSE 20G</t>
-  </si>
-  <si>
-    <t>20115159</t>
-  </si>
-  <si>
-    <t>MLNA RC.CRAC BNANA20</t>
-  </si>
-  <si>
-    <t>20115158</t>
-  </si>
-  <si>
-    <t>MLNA RC.CRACK SPC 20</t>
-  </si>
-  <si>
-    <t>20092863</t>
-  </si>
-  <si>
-    <t>YB BABY CRCK STRW 25</t>
-  </si>
-  <si>
-    <t>20080924</t>
-  </si>
-  <si>
-    <t>YB BABY CRACK BNN 25</t>
-  </si>
-  <si>
-    <t>20138661</t>
-  </si>
-  <si>
-    <t>BROMON CKS MIX.F 100</t>
-  </si>
-  <si>
-    <t>20138660</t>
-  </si>
-  <si>
-    <t>BOROMON CKS MILK 100</t>
-  </si>
-  <si>
-    <t>20141377</t>
-  </si>
-  <si>
-    <t>PROMNA PSTA BLOGNESE</t>
-  </si>
-  <si>
-    <t>20068905</t>
-  </si>
-  <si>
-    <t>FF SKM PUTIH 535G</t>
-  </si>
-  <si>
-    <t>20068906</t>
-  </si>
-  <si>
-    <t>FF SKM COKELAT 535G</t>
-  </si>
-  <si>
-    <t>20118115</t>
-  </si>
-  <si>
-    <t>FRISIAN FLAG PTH 240</t>
-  </si>
-  <si>
-    <t>20112945</t>
-  </si>
-  <si>
-    <t>FF SKM COKLAT 240G</t>
-  </si>
-  <si>
-    <t>20121733</t>
-  </si>
-  <si>
-    <t>FF GOLD SKM PTH 240G</t>
-  </si>
-  <si>
-    <t>20142228</t>
-  </si>
-  <si>
-    <t>CAP ENAK CHOCO 535G</t>
-  </si>
-  <si>
-    <t>20094283</t>
-  </si>
-  <si>
-    <t>INDOMILK KM PTH 535G</t>
-  </si>
-  <si>
-    <t>20120855</t>
-  </si>
-  <si>
-    <t>INDOMILK SWIS CHO535</t>
-  </si>
-  <si>
-    <t>20125783</t>
-  </si>
-  <si>
-    <t>CAP/ENAK KKM PTH 535</t>
-  </si>
-  <si>
-    <t>20141099</t>
-  </si>
-  <si>
-    <t>FF CRMY GULA ARN 240</t>
-  </si>
-  <si>
-    <t>20105631</t>
-  </si>
-  <si>
-    <t>CARNATION KKM 405G</t>
-  </si>
-  <si>
-    <t>20101859</t>
-  </si>
-  <si>
-    <t>SUNBAY EVP.MILK 380G</t>
-  </si>
-  <si>
-    <t>10005489</t>
-  </si>
-  <si>
-    <t>FF KENTAL MANIS 370G</t>
-  </si>
-  <si>
-    <t>10000255</t>
-  </si>
-  <si>
-    <t>FF GOLD SKM PTH 370G</t>
-  </si>
-  <si>
-    <t>20089819</t>
-  </si>
-  <si>
-    <t>FF KENTAL MANIS 490G</t>
-  </si>
-  <si>
-    <t>10000088</t>
-  </si>
-  <si>
-    <t>FF SKM CKLT KLG 370</t>
-  </si>
-  <si>
-    <t>10000021</t>
-  </si>
-  <si>
-    <t>ENAK K/MNS PUTIH 370</t>
-  </si>
-  <si>
-    <t>10036665</t>
-  </si>
-  <si>
-    <t>CARNATION KKM 365G</t>
-  </si>
-  <si>
-    <t>20002313</t>
-  </si>
-  <si>
-    <t>FF KRM MNS OMELA 370</t>
-  </si>
-  <si>
-    <t>20054589</t>
-  </si>
-  <si>
-    <t>3SAPI KRIMER 490G</t>
+    <t>20087580</t>
+  </si>
+  <si>
+    <t>ENTRASOL GLD VAN560</t>
+  </si>
+  <si>
+    <t>10025373</t>
+  </si>
+  <si>
+    <t>ENTRASOL GOLD VAN170</t>
+  </si>
+  <si>
+    <t>20021571</t>
+  </si>
+  <si>
+    <t>ANLENE GOLD VAN 560G</t>
+  </si>
+  <si>
+    <t>10020147</t>
+  </si>
+  <si>
+    <t>ANLENE GOLD CKLT 230</t>
+  </si>
+  <si>
+    <t>10008064</t>
+  </si>
+  <si>
+    <t>ANLENE GOLD ORG240G</t>
+  </si>
+  <si>
+    <t>10012172</t>
+  </si>
+  <si>
+    <t>ANLENE GOLD VNLA 230</t>
   </si>
   <si>
     <t>10003653</t>
@@ -562,6 +787,9 @@
     <t>MRINAGA BMT1 LAC.390</t>
   </si>
   <si>
+    <t>16</t>
+  </si>
+  <si>
     <t>20014399</t>
   </si>
   <si>
@@ -586,190 +814,16 @@
     <t>MORINAGA CK MADU 190</t>
   </si>
   <si>
-    <t>20098370</t>
-  </si>
-  <si>
-    <t>VDORAN XMRT1+ MDU350</t>
-  </si>
-  <si>
-    <t>20098369</t>
-  </si>
-  <si>
-    <t>VDORAN XMRT3+ VAN350</t>
-  </si>
-  <si>
-    <t>20135200</t>
-  </si>
-  <si>
-    <t>VIDORAN BABY0-6 550G</t>
-  </si>
-  <si>
-    <t>20129773</t>
-  </si>
-  <si>
-    <t>VDORAN BABY6-12 550G</t>
-  </si>
-  <si>
-    <t>20117983</t>
-  </si>
-  <si>
-    <t>VIDORAN XM5+ COKL700</t>
-  </si>
-  <si>
-    <t>20070110</t>
-  </si>
-  <si>
-    <t>VDORAN XMRT1+ MDU700</t>
-  </si>
-  <si>
-    <t>20090042</t>
-  </si>
-  <si>
-    <t>VDORAN XMRT1+ VAN700</t>
-  </si>
-  <si>
-    <t>20082394</t>
-  </si>
-  <si>
-    <t>VDORAN XMRT3+ MDU700</t>
-  </si>
-  <si>
-    <t>20090437</t>
-  </si>
-  <si>
-    <t>VDORAN XMRT3+ VAN700</t>
-  </si>
-  <si>
-    <t>20117985</t>
-  </si>
-  <si>
-    <t>VIDORAN XM5+ MADU700</t>
-  </si>
-  <si>
-    <t>20113346</t>
-  </si>
-  <si>
-    <t>VDRAN XMRT1+ VAN 900</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>20101825</t>
-  </si>
-  <si>
-    <t>VDRAN XMRT1+ MDU 900</t>
-  </si>
-  <si>
-    <t>20106381</t>
-  </si>
-  <si>
-    <t>VDRAN XMRT3+ MDU 900</t>
-  </si>
-  <si>
-    <t>20117981</t>
-  </si>
-  <si>
-    <t>VIDORAN XM3+ VNL900</t>
-  </si>
-  <si>
-    <t>20138473</t>
-  </si>
-  <si>
-    <t>VDORAN BABY6-12 900G</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>20138474</t>
-  </si>
-  <si>
-    <t>VIDORAN 5  MADU 900G</t>
-  </si>
-  <si>
-    <t>20125790</t>
-  </si>
-  <si>
-    <t>HLTHYWY3+ SB MADU700</t>
-  </si>
-  <si>
-    <t>20125788</t>
-  </si>
-  <si>
-    <t>HLTHYWY1+ SP MADU700</t>
-  </si>
-  <si>
-    <t>20136510</t>
-  </si>
-  <si>
-    <t>MILO 3IN1 ACT-GO 400</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>20027850</t>
-  </si>
-  <si>
-    <t>ZEE VNILA TWST 340G</t>
-  </si>
-  <si>
-    <t>20027848</t>
-  </si>
-  <si>
-    <t>ZEE SWIZZ CHO 340G</t>
-  </si>
-  <si>
-    <t>20033353</t>
-  </si>
-  <si>
-    <t>HILO/S HI-CAL CHO250</t>
-  </si>
-  <si>
-    <t>10000578</t>
-  </si>
-  <si>
-    <t>DIABETASOL VNL.170GR</t>
-  </si>
-  <si>
-    <t>20021571</t>
-  </si>
-  <si>
-    <t>ANLENE GOLD VAN 560G</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>10020147</t>
-  </si>
-  <si>
-    <t>ANLENE GOLD CKLT 230</t>
-  </si>
-  <si>
-    <t>10008064</t>
-  </si>
-  <si>
-    <t>ANLENE GOLD ORG240G</t>
-  </si>
-  <si>
-    <t>10012172</t>
-  </si>
-  <si>
-    <t>ANLENE GOLD VNLA 230</t>
-  </si>
-  <si>
-    <t>20087580</t>
-  </si>
-  <si>
-    <t>ENTRASOL GLD VAN560</t>
-  </si>
-  <si>
-    <t>10025373</t>
-  </si>
-  <si>
-    <t>ENTRASOL GOLD VAN170</t>
+    <t>10010874</t>
+  </si>
+  <si>
+    <t>DNCOW 1+ MDU BOX 120</t>
+  </si>
+  <si>
+    <t>10005338</t>
+  </si>
+  <si>
+    <t>DNCOW FRTGO BOX 195G</t>
   </si>
   <si>
     <t>10026038</t>
@@ -793,22 +847,316 @@
     <t>SGM EKSPL3+ MADU 150</t>
   </si>
   <si>
+    <t>20037098</t>
+  </si>
+  <si>
+    <t>SGM SOYA 1+ VANL 400</t>
+  </si>
+  <si>
+    <t>20040302</t>
+  </si>
+  <si>
+    <t>SGM EKSPL3+ MADU 400</t>
+  </si>
+  <si>
+    <t>20040301</t>
+  </si>
+  <si>
+    <t>SGM EKSPL3+ VAN 400G</t>
+  </si>
+  <si>
+    <t>10009494</t>
+  </si>
+  <si>
+    <t>DANCOW FORTIGRO 390G</t>
+  </si>
+  <si>
+    <t>20040340</t>
+  </si>
+  <si>
+    <t>SGM ANANDA1 BOX 400G</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>20040312</t>
+  </si>
+  <si>
+    <t>SGM ANANDA2 BOX 400G</t>
+  </si>
+  <si>
     <t>20040299</t>
   </si>
   <si>
     <t>SGM EKSPL1+ MADU 400</t>
   </si>
   <si>
-    <t>20040302</t>
-  </si>
-  <si>
-    <t>SGM EKSPL3+ MADU 400</t>
-  </si>
-  <si>
-    <t>20040301</t>
-  </si>
-  <si>
-    <t>SGM EKSPL3+ VAN 400G</t>
+    <t>20040300</t>
+  </si>
+  <si>
+    <t>SGM EKSPL1+ VAN 400G</t>
+  </si>
+  <si>
+    <t>20087025</t>
+  </si>
+  <si>
+    <t>SGM EKSPL3+ VAN 600G</t>
+  </si>
+  <si>
+    <t>20087024</t>
+  </si>
+  <si>
+    <t>SGM EKSPL3+ MADU 600</t>
+  </si>
+  <si>
+    <t>20047323</t>
+  </si>
+  <si>
+    <t>SGM ANANDA1 BOX 550G</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20047324</t>
+  </si>
+  <si>
+    <t>SGM ANANDA2 BOX 550G</t>
+  </si>
+  <si>
+    <t>20074147</t>
+  </si>
+  <si>
+    <t>SGM EKSPL1+ MADU 600</t>
+  </si>
+  <si>
+    <t>20077508</t>
+  </si>
+  <si>
+    <t>SGM EKSPL1+ VAN 600G</t>
+  </si>
+  <si>
+    <t>20040294</t>
+  </si>
+  <si>
+    <t>SGM EKSPL1+ MADU 900</t>
+  </si>
+  <si>
+    <t>10005279</t>
+  </si>
+  <si>
+    <t>SGM ANANDA2 BOX 150G</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>20040293</t>
+  </si>
+  <si>
+    <t>SGM EKSPL1+ VAN 900G</t>
+  </si>
+  <si>
+    <t>20040296</t>
+  </si>
+  <si>
+    <t>SGM EKSPL3+ MADU 900</t>
+  </si>
+  <si>
+    <t>20040295</t>
+  </si>
+  <si>
+    <t>SGM EKSPL3+ VAN 900G</t>
+  </si>
+  <si>
+    <t>20066494</t>
+  </si>
+  <si>
+    <t>SGM EKSPL5+ MADU 900</t>
+  </si>
+  <si>
+    <t>10005315</t>
+  </si>
+  <si>
+    <t>SGM ANANDA1 BOX 150G</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>20040297</t>
+  </si>
+  <si>
+    <t>SGM ANANDA1 BOX 1KG</t>
+  </si>
+  <si>
+    <t>20040298</t>
+  </si>
+  <si>
+    <t>SGM ANANDA2 BOX 1KG</t>
+  </si>
+  <si>
+    <t>20065379</t>
+  </si>
+  <si>
+    <t>SGM SOYA1+ VANL 700G</t>
+  </si>
+  <si>
+    <t>20071686</t>
+  </si>
+  <si>
+    <t>SGM SOYA1+ MADU 700G</t>
+  </si>
+  <si>
+    <t>20005712</t>
+  </si>
+  <si>
+    <t>DNCOW 5+ VAN BOX 350</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>10009495</t>
+  </si>
+  <si>
+    <t>DNCW FRTG FL.CRM 390</t>
+  </si>
+  <si>
+    <t>10009493</t>
+  </si>
+  <si>
+    <t>DNCOW FRTGO COK 390G</t>
+  </si>
+  <si>
+    <t>10006259</t>
+  </si>
+  <si>
+    <t>DNCOW FRTGO ENR 780G</t>
+  </si>
+  <si>
+    <t>10006260</t>
+  </si>
+  <si>
+    <t>DNCOW FRTGO COK 780</t>
+  </si>
+  <si>
+    <t>10006258</t>
+  </si>
+  <si>
+    <t>DNCOWFRTGO F.CR 780G</t>
+  </si>
+  <si>
+    <t>10006262</t>
+  </si>
+  <si>
+    <t>DNCOW 1+ MDU BOX 750</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>10015652</t>
+  </si>
+  <si>
+    <t>DNCOW 1+ VAN BOX 750</t>
+  </si>
+  <si>
+    <t>10013035</t>
+  </si>
+  <si>
+    <t>DNCOW 3+ MDU BOX 750</t>
+  </si>
+  <si>
+    <t>10015650</t>
+  </si>
+  <si>
+    <t>DNCOW 3+ VAN BOX 750</t>
+  </si>
+  <si>
+    <t>10023780</t>
+  </si>
+  <si>
+    <t>DNCOW 5+ MDU BOX 750</t>
+  </si>
+  <si>
+    <t>10009496</t>
+  </si>
+  <si>
+    <t>DNCOW 1+ MDU BOX 350</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>10015653</t>
+  </si>
+  <si>
+    <t>DNCOW 1+ VAN BOX 350</t>
+  </si>
+  <si>
+    <t>10012967</t>
+  </si>
+  <si>
+    <t>DNCOW 3+ MDU BOX 350</t>
+  </si>
+  <si>
+    <t>10015651</t>
+  </si>
+  <si>
+    <t>DNCOW3+ VAN BOX  350</t>
+  </si>
+  <si>
+    <t>20017679</t>
+  </si>
+  <si>
+    <t>LACTOGEN PRO LANJ350</t>
+  </si>
+  <si>
+    <t>20113345</t>
+  </si>
+  <si>
+    <t>LACTOGRW PRO1+VAN350</t>
+  </si>
+  <si>
+    <t>20035629</t>
+  </si>
+  <si>
+    <t>BEBELAC 1+VNL BOX350</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>20035633</t>
+  </si>
+  <si>
+    <t>BEBELAC3+ VNL BOX350</t>
+  </si>
+  <si>
+    <t>20035635</t>
+  </si>
+  <si>
+    <t>BEBELAC3+ MDU BOX350</t>
+  </si>
+  <si>
+    <t>10025848</t>
+  </si>
+  <si>
+    <t>NTRILON 3 RYL VAN400</t>
+  </si>
+  <si>
+    <t>20055287</t>
+  </si>
+  <si>
+    <t>LACTOGRW PRO1+MDU350</t>
+  </si>
+  <si>
+    <t>20017965</t>
+  </si>
+  <si>
+    <t>LACTOGEN PRO FORM350</t>
   </si>
   <si>
     <t>20040303</t>
@@ -817,325 +1165,7 @@
     <t>SGM EKSPL3+ CKLT 400</t>
   </si>
   <si>
-    <t>20040340</t>
-  </si>
-  <si>
-    <t>SGM ANANDA1 BOX 400G</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>20040312</t>
-  </si>
-  <si>
-    <t>SGM ANANDA2 BOX 400G</t>
-  </si>
-  <si>
-    <t>20040300</t>
-  </si>
-  <si>
-    <t>SGM EKSPL1+ VAN 400G</t>
-  </si>
-  <si>
-    <t>20037098</t>
-  </si>
-  <si>
-    <t>SGM SOYA 1+ VANL 400</t>
-  </si>
-  <si>
-    <t>20087025</t>
-  </si>
-  <si>
-    <t>SGM EKSPL3+ VAN 600G</t>
-  </si>
-  <si>
-    <t>20087024</t>
-  </si>
-  <si>
-    <t>SGM EKSPL3+ MADU 600</t>
-  </si>
-  <si>
-    <t>20047323</t>
-  </si>
-  <si>
-    <t>SGM ANANDA1 BOX 550G</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>20047324</t>
-  </si>
-  <si>
-    <t>SGM ANANDA2 BOX 550G</t>
-  </si>
-  <si>
-    <t>20074147</t>
-  </si>
-  <si>
-    <t>SGM EKSPL1+ MADU 600</t>
-  </si>
-  <si>
-    <t>20077508</t>
-  </si>
-  <si>
-    <t>SGM EKSPL1+ VAN 600G</t>
-  </si>
-  <si>
-    <t>20040294</t>
-  </si>
-  <si>
-    <t>SGM EKSPL1+ MADU 900</t>
-  </si>
-  <si>
-    <t>10005279</t>
-  </si>
-  <si>
-    <t>SGM ANANDA2 BOX 150G</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>20040293</t>
-  </si>
-  <si>
-    <t>SGM EKSPL1+ VAN 900G</t>
-  </si>
-  <si>
-    <t>20040296</t>
-  </si>
-  <si>
-    <t>SGM EKSPL3+ MADU 900</t>
-  </si>
-  <si>
-    <t>20040295</t>
-  </si>
-  <si>
-    <t>SGM EKSPL3+ VAN 900G</t>
-  </si>
-  <si>
-    <t>20066494</t>
-  </si>
-  <si>
-    <t>SGM EKSPL5+ MADU 900</t>
-  </si>
-  <si>
-    <t>10005315</t>
-  </si>
-  <si>
-    <t>SGM ANANDA1 BOX 150G</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>20040297</t>
-  </si>
-  <si>
-    <t>SGM ANANDA1 BOX 1KG</t>
-  </si>
-  <si>
-    <t>20040298</t>
-  </si>
-  <si>
-    <t>SGM ANANDA2 BOX 1KG</t>
-  </si>
-  <si>
-    <t>20065379</t>
-  </si>
-  <si>
-    <t>SGM SOYA1+ VANL 700G</t>
-  </si>
-  <si>
-    <t>20071686</t>
-  </si>
-  <si>
-    <t>SGM SOYA1+ MADU 700G</t>
-  </si>
-  <si>
-    <t>20011063</t>
-  </si>
-  <si>
-    <t>PRENAGEN HML CHO 360</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>10033006</t>
-  </si>
-  <si>
-    <t>PRENAGEN HML CHO 180</t>
-  </si>
-  <si>
-    <t>20055287</t>
-  </si>
-  <si>
-    <t>LACTOGRW PRO1+MDU350</t>
-  </si>
-  <si>
-    <t>20017965</t>
-  </si>
-  <si>
-    <t>LACTOGEN PRO FORM350</t>
-  </si>
-  <si>
-    <t>20017679</t>
-  </si>
-  <si>
-    <t>LACTOGEN PRO LANJ350</t>
-  </si>
-  <si>
-    <t>20113345</t>
-  </si>
-  <si>
-    <t>LACTOGRW PRO1+VAN350</t>
-  </si>
-  <si>
-    <t>10006262</t>
-  </si>
-  <si>
-    <t>DNCOW 1+ MDU BOX 750</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>10015652</t>
-  </si>
-  <si>
-    <t>DNCOW 1+ VAN BOX 750</t>
-  </si>
-  <si>
-    <t>10013035</t>
-  </si>
-  <si>
-    <t>DNCOW 3+ MDU BOX 750</t>
-  </si>
-  <si>
-    <t>10015650</t>
-  </si>
-  <si>
-    <t>DNCOW 3+ VAN BOX 750</t>
-  </si>
-  <si>
-    <t>10023780</t>
-  </si>
-  <si>
-    <t>DNCOW 5+ MDU BOX 750</t>
-  </si>
-  <si>
-    <t>10009496</t>
-  </si>
-  <si>
-    <t>DNCOW 1+ MDU BOX 350</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>10015653</t>
-  </si>
-  <si>
-    <t>DNCOW 1+ VAN BOX 350</t>
-  </si>
-  <si>
-    <t>10012967</t>
-  </si>
-  <si>
-    <t>DNCOW 3+ MDU BOX 350</t>
-  </si>
-  <si>
-    <t>10015651</t>
-  </si>
-  <si>
-    <t>DNCOW3+ VAN BOX  350</t>
-  </si>
-  <si>
-    <t>10010874</t>
-  </si>
-  <si>
-    <t>DNCOW 1+ MDU BOX 120</t>
-  </si>
-  <si>
-    <t>20005712</t>
-  </si>
-  <si>
-    <t>DNCOW 5+ VAN BOX 350</t>
-  </si>
-  <si>
-    <t>10005338</t>
-  </si>
-  <si>
-    <t>DNCOW FRTGO BOX 195G</t>
-  </si>
-  <si>
-    <t>10009494</t>
-  </si>
-  <si>
-    <t>DANCOW FORTIGRO 390G</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>10009495</t>
-  </si>
-  <si>
-    <t>DNCW FRTG FL.CRM 390</t>
-  </si>
-  <si>
-    <t>10009493</t>
-  </si>
-  <si>
-    <t>DNCOW FRTGO COK 390G</t>
-  </si>
-  <si>
-    <t>10006259</t>
-  </si>
-  <si>
-    <t>DNCOW FRTGO ENR 780G</t>
-  </si>
-  <si>
-    <t>10006260</t>
-  </si>
-  <si>
-    <t>DNCOW FRTGO COK 780</t>
-  </si>
-  <si>
-    <t>10006258</t>
-  </si>
-  <si>
-    <t>DNCOWFRTGO F.CR 780G</t>
-  </si>
-  <si>
-    <t>20035629</t>
-  </si>
-  <si>
-    <t>BEBELAC 1+VNL BOX350</t>
-  </si>
-  <si>
     <t>26</t>
-  </si>
-  <si>
-    <t>20035633</t>
-  </si>
-  <si>
-    <t>BEBELAC3+ VNL BOX350</t>
-  </si>
-  <si>
-    <t>20035635</t>
-  </si>
-  <si>
-    <t>BEBELAC3+ MDU BOX350</t>
-  </si>
-  <si>
-    <t>10025848</t>
-  </si>
-  <si>
-    <t>NTRILON 3 RYL VAN400</t>
   </si>
   <si>
     <t>20057224</t>
@@ -1600,7 +1630,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F183"/>
+  <dimension ref="A1:F188"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1687,15 +1717,15 @@
         <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -1704,18 +1734,18 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -1724,18 +1754,18 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -1744,18 +1774,18 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -1764,18 +1794,18 @@
         <v>4</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -1784,87 +1814,87 @@
         <v>4</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>5</v>
@@ -1872,19 +1902,19 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>5</v>
@@ -1892,19 +1922,19 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>5</v>
@@ -1912,70 +1942,70 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>44</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>44</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
@@ -1984,18 +2014,18 @@
         <v>8</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>51</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
@@ -2004,7 +2034,7 @@
         <v>8</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>5</v>
@@ -2012,10 +2042,10 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
@@ -2024,7 +2054,7 @@
         <v>8</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>5</v>
@@ -2032,10 +2062,10 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
@@ -2044,18 +2074,18 @@
         <v>8</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>51</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
@@ -2064,67 +2094,67 @@
         <v>8</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>5</v>
+        <v>63</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E25" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="F25" s="1" t="s">
-        <v>51</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>5</v>
@@ -2132,10 +2162,10 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
@@ -2144,18 +2174,18 @@
         <v>11</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>5</v>
+        <v>63</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
@@ -2164,7 +2194,7 @@
         <v>11</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>5</v>
@@ -2172,10 +2202,10 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
@@ -2184,7 +2214,7 @@
         <v>11</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>5</v>
@@ -2192,10 +2222,10 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
@@ -2204,18 +2234,18 @@
         <v>11</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>5</v>
+        <v>63</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
@@ -2224,47 +2254,47 @@
         <v>11</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>5</v>
@@ -2272,19 +2302,19 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D34" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E34" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>24</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>5</v>
@@ -2292,382 +2322,382 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>118</v>
+        <v>19</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>121</v>
+        <v>23</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -2681,113 +2711,113 @@
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>124</v>
+        <v>26</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B55" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B55" s="1" t="s">
-        <v>126</v>
-      </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B56" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B56" s="1" t="s">
-        <v>128</v>
-      </c>
       <c r="C56" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B57" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B57" s="1" t="s">
-        <v>130</v>
-      </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="B58" s="1" t="s">
-        <v>132</v>
-      </c>
       <c r="C58" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>51</v>
+        <v>16</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B59" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="C59" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E59" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C59" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="F59" s="1" t="s">
-        <v>51</v>
+        <v>16</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -2801,410 +2831,410 @@
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>17</v>
+        <v>137</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>21</v>
+        <v>63</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>21</v>
+        <v>63</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>118</v>
+        <v>15</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>121</v>
+        <v>19</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>124</v>
+        <v>23</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>51</v>
+        <v>16</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>20</v>
+        <v>134</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -3212,239 +3242,239 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>118</v>
+        <v>8</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>121</v>
+        <v>11</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>118</v>
+        <v>32</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>118</v>
+        <v>32</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>44</v>
+        <v>12</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>118</v>
+        <v>32</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>44</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>118</v>
+        <v>32</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>44</v>
+        <v>12</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>118</v>
+        <v>35</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>44</v>
+        <v>5</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>121</v>
+        <v>35</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>121</v>
+        <v>35</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>121</v>
+        <v>35</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>121</v>
+        <v>35</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>51</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>121</v>
+        <v>35</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>5</v>
@@ -3452,79 +3482,79 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>124</v>
+        <v>38</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>5</v>
+        <v>63</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>124</v>
+        <v>38</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>5</v>
+        <v>63</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>124</v>
+        <v>38</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>5</v>
+        <v>63</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>124</v>
+        <v>38</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>5</v>
@@ -3532,19 +3562,19 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>5</v>
@@ -3552,19 +3582,19 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>213</v>
+        <v>134</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>5</v>
@@ -3581,10 +3611,10 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>213</v>
+        <v>134</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>5</v>
@@ -3601,10 +3631,10 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>213</v>
+        <v>134</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>5</v>
@@ -3621,10 +3651,10 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>213</v>
+        <v>134</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>5</v>
@@ -3641,50 +3671,50 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>222</v>
+        <v>137</v>
       </c>
       <c r="E102" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B103" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B103" s="1" t="s">
-        <v>224</v>
-      </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>222</v>
+        <v>137</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B104" s="1" t="s">
-        <v>226</v>
-      </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>222</v>
+        <v>137</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -3692,19 +3722,19 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="B105" s="1" t="s">
-        <v>228</v>
-      </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>222</v>
+        <v>137</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>5</v>
@@ -3712,19 +3742,19 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B106" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="B106" s="1" t="s">
-        <v>230</v>
-      </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>231</v>
+        <v>137</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>5</v>
@@ -3732,56 +3762,56 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D107" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="B107" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="C107" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D107" s="1" t="s">
-        <v>231</v>
-      </c>
       <c r="E107" s="1" t="s">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B108" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="B108" s="1" t="s">
-        <v>235</v>
-      </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B109" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="B109" s="1" t="s">
-        <v>237</v>
-      </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E109" s="1" t="s">
         <v>11</v>
@@ -3792,299 +3822,299 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="B110" s="1" t="s">
-        <v>239</v>
-      </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>44</v>
+        <v>5</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B111" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="B111" s="1" t="s">
+      <c r="C111" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D111" s="1" t="s">
         <v>241</v>
-      </c>
-      <c r="C111" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>242</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B112" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="B112" s="1" t="s">
-        <v>244</v>
-      </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>44</v>
+        <v>16</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B113" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="B113" s="1" t="s">
-        <v>246</v>
-      </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>44</v>
+        <v>16</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B114" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="B114" s="1" t="s">
-        <v>248</v>
-      </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>44</v>
+        <v>12</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B115" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="B115" s="1" t="s">
-        <v>250</v>
-      </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B116" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="B116" s="1" t="s">
-        <v>252</v>
-      </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>44</v>
+        <v>12</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="B117" s="1" t="s">
-        <v>254</v>
-      </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D119" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="B119" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="C119" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>255</v>
-      </c>
       <c r="E119" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B120" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="B120" s="1" t="s">
-        <v>261</v>
-      </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B121" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="B121" s="1" t="s">
-        <v>263</v>
-      </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B122" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="B122" s="1" t="s">
-        <v>265</v>
-      </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B123" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="B123" s="1" t="s">
-        <v>267</v>
-      </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B124" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="B124" s="1" t="s">
-        <v>269</v>
-      </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>5</v>
@@ -4092,19 +4122,19 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>5</v>
@@ -4112,19 +4142,19 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D126" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="B126" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="C126" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D126" s="1" t="s">
-        <v>270</v>
-      </c>
       <c r="E126" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>5</v>
@@ -4132,19 +4162,19 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B127" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="B127" s="1" t="s">
-        <v>276</v>
-      </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>5</v>
@@ -4152,19 +4182,19 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B128" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="B128" s="1" t="s">
-        <v>278</v>
-      </c>
       <c r="C128" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>5</v>
@@ -4172,19 +4202,19 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B129" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="B129" s="1" t="s">
-        <v>280</v>
-      </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>5</v>
@@ -4192,19 +4222,19 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B130" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="B130" s="1" t="s">
-        <v>282</v>
-      </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>5</v>
@@ -4212,19 +4242,19 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>5</v>
@@ -4232,19 +4262,19 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>5</v>
@@ -4252,19 +4282,19 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D133" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="B133" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="C133" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D133" s="1" t="s">
-        <v>283</v>
-      </c>
       <c r="E133" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>5</v>
@@ -4272,19 +4302,19 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B134" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="B134" s="1" t="s">
-        <v>291</v>
-      </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>5</v>
@@ -4292,19 +4322,19 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B135" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="B135" s="1" t="s">
-        <v>293</v>
-      </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>5</v>
@@ -4312,19 +4342,19 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>5</v>
@@ -4332,19 +4362,19 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>5</v>
@@ -4352,19 +4382,19 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>5</v>
@@ -4372,39 +4402,39 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D139" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="B139" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="C139" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>294</v>
-      </c>
       <c r="E139" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>44</v>
+        <v>5</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="B140" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="B140" s="1" t="s">
-        <v>304</v>
-      </c>
       <c r="C140" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>5</v>
@@ -4412,19 +4442,19 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>5</v>
@@ -4432,39 +4462,39 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>44</v>
+        <v>5</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>5</v>
@@ -4472,19 +4502,19 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D144" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="B144" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="C144" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D144" s="1" t="s">
-        <v>305</v>
-      </c>
       <c r="E144" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>5</v>
@@ -4492,59 +4522,59 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B145" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="B145" s="1" t="s">
-        <v>315</v>
-      </c>
       <c r="C145" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>44</v>
+        <v>5</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>51</v>
+        <v>5</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>5</v>
@@ -4552,39 +4582,39 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D149" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="B149" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="C149" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D149" s="1" t="s">
-        <v>316</v>
-      </c>
       <c r="E149" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>5</v>
@@ -4592,19 +4622,19 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B150" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="B150" s="1" t="s">
-        <v>326</v>
-      </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>5</v>
@@ -4612,39 +4642,39 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="B151" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="B151" s="1" t="s">
-        <v>328</v>
-      </c>
       <c r="C151" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>5</v>
@@ -4652,19 +4682,19 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>5</v>
@@ -4672,19 +4702,19 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D154" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="B154" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="C154" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D154" s="1" t="s">
-        <v>329</v>
-      </c>
       <c r="E154" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>5</v>
@@ -4692,19 +4722,19 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B155" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="B155" s="1" t="s">
-        <v>337</v>
-      </c>
       <c r="C155" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>5</v>
@@ -4712,19 +4742,19 @@
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B156" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="B156" s="1" t="s">
-        <v>339</v>
-      </c>
       <c r="C156" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>5</v>
@@ -4732,19 +4762,19 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>5</v>
@@ -4752,19 +4782,19 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>5</v>
@@ -4772,19 +4802,19 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>5</v>
@@ -4792,19 +4822,19 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D160" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="B160" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="C160" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D160" s="1" t="s">
-        <v>340</v>
-      </c>
       <c r="E160" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>5</v>
@@ -4812,19 +4842,19 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B161" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="B161" s="1" t="s">
-        <v>350</v>
-      </c>
       <c r="C161" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>5</v>
@@ -4832,19 +4862,19 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="B162" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="B162" s="1" t="s">
-        <v>352</v>
-      </c>
       <c r="C162" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>5</v>
@@ -4852,19 +4882,19 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="B163" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="B163" s="1" t="s">
-        <v>354</v>
-      </c>
       <c r="C163" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>5</v>
@@ -4872,19 +4902,19 @@
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>5</v>
@@ -4892,19 +4922,19 @@
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D165" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="B165" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="C165" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D165" s="1" t="s">
-        <v>355</v>
-      </c>
       <c r="E165" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>5</v>
@@ -4912,19 +4942,19 @@
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="B166" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="B166" s="1" t="s">
-        <v>361</v>
-      </c>
       <c r="C166" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>5</v>
@@ -4932,19 +4962,19 @@
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="B167" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="B167" s="1" t="s">
-        <v>363</v>
-      </c>
       <c r="C167" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>5</v>
@@ -4952,19 +4982,19 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="B168" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="B168" s="1" t="s">
-        <v>365</v>
-      </c>
       <c r="C168" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>5</v>
@@ -4972,19 +5002,19 @@
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="B169" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="B169" s="1" t="s">
-        <v>367</v>
-      </c>
       <c r="C169" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>5</v>
@@ -4992,19 +5022,19 @@
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>5</v>
@@ -5012,19 +5042,19 @@
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D171" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="B171" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="C171" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D171" s="1" t="s">
-        <v>368</v>
-      </c>
       <c r="E171" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>5</v>
@@ -5032,19 +5062,19 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="B172" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="B172" s="1" t="s">
-        <v>374</v>
-      </c>
       <c r="C172" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>5</v>
@@ -5052,19 +5082,19 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="B173" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="B173" s="1" t="s">
-        <v>376</v>
-      </c>
       <c r="C173" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>5</v>
@@ -5072,19 +5102,19 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>5</v>
@@ -5092,19 +5122,19 @@
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>5</v>
@@ -5112,19 +5142,19 @@
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>5</v>
@@ -5132,19 +5162,19 @@
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D177" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="B177" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="C177" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D177" s="1" t="s">
-        <v>377</v>
-      </c>
       <c r="E177" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>5</v>
@@ -5152,19 +5182,19 @@
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="B178" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="B178" s="1" t="s">
+      <c r="C178" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D178" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="C178" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D178" s="1" t="s">
-        <v>377</v>
-      </c>
       <c r="E178" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>5</v>
@@ -5181,10 +5211,10 @@
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>5</v>
@@ -5192,59 +5222,59 @@
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="B180" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="B180" s="1" t="s">
-        <v>392</v>
-      </c>
       <c r="C180" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="B181" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="B181" s="1" t="s">
-        <v>394</v>
-      </c>
       <c r="C181" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="B182" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="B182" s="1" t="s">
-        <v>396</v>
-      </c>
       <c r="C182" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>5</v>
@@ -5252,21 +5282,121 @@
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="B183" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="B183" s="1" t="s">
+      <c r="C183" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D183" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="E183" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F183" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A184" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="C183" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D183" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="E183" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F183" s="1" t="s">
+      <c r="B184" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="C184" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D184" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="E184" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F184" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A185" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="B185" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="C185" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D185" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="E185" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F185" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A186" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="C186" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D186" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="E186" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F186" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A187" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="B187" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="C187" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D187" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="E187" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F187" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A188" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="B188" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="C188" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D188" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="E188" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F188" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/MBF04S.xlsx
+++ b/MBF04S.xlsx
@@ -607,6 +607,117 @@
     <t>FF CRMY GULA ARN 240</t>
   </si>
   <si>
+    <t>20070110</t>
+  </si>
+  <si>
+    <t>VDORAN XMRT1+ MDU700</t>
+  </si>
+  <si>
+    <t>20090042</t>
+  </si>
+  <si>
+    <t>VDORAN XMRT1+ VAN700</t>
+  </si>
+  <si>
+    <t>20082394</t>
+  </si>
+  <si>
+    <t>VDORAN XMRT3+ MDU700</t>
+  </si>
+  <si>
+    <t>20090437</t>
+  </si>
+  <si>
+    <t>VDORAN XMRT3+ VAN700</t>
+  </si>
+  <si>
+    <t>20117983</t>
+  </si>
+  <si>
+    <t>VIDORAN XM5+ COKL700</t>
+  </si>
+  <si>
+    <t>20098371</t>
+  </si>
+  <si>
+    <t>VDORAN SUSU MADU 350</t>
+  </si>
+  <si>
+    <t>20098369</t>
+  </si>
+  <si>
+    <t>VDORAN XMRT3+ VAN350</t>
+  </si>
+  <si>
+    <t>20101825</t>
+  </si>
+  <si>
+    <t>VDRAN XMRT1+ MDU 900</t>
+  </si>
+  <si>
+    <t>20113346</t>
+  </si>
+  <si>
+    <t>VDRAN XMRT1+ VAN 900</t>
+  </si>
+  <si>
+    <t>20106381</t>
+  </si>
+  <si>
+    <t>VDRAN XMRT3+ MDU 900</t>
+  </si>
+  <si>
+    <t>20098370</t>
+  </si>
+  <si>
+    <t>VDORAN XMRT1+ MDU350</t>
+  </si>
+  <si>
+    <t>20098368</t>
+  </si>
+  <si>
+    <t>VDORAN XMRT1+ VAN325</t>
+  </si>
+  <si>
+    <t>20138473</t>
+  </si>
+  <si>
+    <t>VDORAN BABY6-12 900G</t>
+  </si>
+  <si>
+    <t>20117981</t>
+  </si>
+  <si>
+    <t>VIDORAN XM3+ VNL900</t>
+  </si>
+  <si>
+    <t>20138474</t>
+  </si>
+  <si>
+    <t>VIDORAN 5  MADU 900G</t>
+  </si>
+  <si>
+    <t>20135200</t>
+  </si>
+  <si>
+    <t>VIDORAN BABY0-6 550G</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>20129773</t>
+  </si>
+  <si>
+    <t>VDORAN BABY6-12 550G</t>
+  </si>
+  <si>
+    <t>20117985</t>
+  </si>
+  <si>
+    <t>VIDORAN XM5+ MADU700</t>
+  </si>
+  <si>
     <t>20125788</t>
   </si>
   <si>
@@ -617,117 +728,6 @@
   </si>
   <si>
     <t>HLTHYWY3+ SB MADU700</t>
-  </si>
-  <si>
-    <t>20135200</t>
-  </si>
-  <si>
-    <t>VIDORAN BABY0-6 550G</t>
-  </si>
-  <si>
-    <t>20129773</t>
-  </si>
-  <si>
-    <t>VDORAN BABY6-12 550G</t>
-  </si>
-  <si>
-    <t>20098368</t>
-  </si>
-  <si>
-    <t>VDORAN XMRT1+ VAN325</t>
-  </si>
-  <si>
-    <t>20098371</t>
-  </si>
-  <si>
-    <t>VDORAN SUSU MADU 350</t>
-  </si>
-  <si>
-    <t>20070110</t>
-  </si>
-  <si>
-    <t>VDORAN XMRT1+ MDU700</t>
-  </si>
-  <si>
-    <t>20090042</t>
-  </si>
-  <si>
-    <t>VDORAN XMRT1+ VAN700</t>
-  </si>
-  <si>
-    <t>20082394</t>
-  </si>
-  <si>
-    <t>VDORAN XMRT3+ MDU700</t>
-  </si>
-  <si>
-    <t>20090437</t>
-  </si>
-  <si>
-    <t>VDORAN XMRT3+ VAN700</t>
-  </si>
-  <si>
-    <t>20117985</t>
-  </si>
-  <si>
-    <t>VIDORAN XM5+ MADU700</t>
-  </si>
-  <si>
-    <t>20098370</t>
-  </si>
-  <si>
-    <t>VDORAN XMRT1+ MDU350</t>
-  </si>
-  <si>
-    <t>20098369</t>
-  </si>
-  <si>
-    <t>VDORAN XMRT3+ VAN350</t>
-  </si>
-  <si>
-    <t>20117983</t>
-  </si>
-  <si>
-    <t>VIDORAN XM5+ COKL700</t>
-  </si>
-  <si>
-    <t>20106381</t>
-  </si>
-  <si>
-    <t>VDRAN XMRT3+ MDU 900</t>
-  </si>
-  <si>
-    <t>20117981</t>
-  </si>
-  <si>
-    <t>VIDORAN XM3+ VNL900</t>
-  </si>
-  <si>
-    <t>20138473</t>
-  </si>
-  <si>
-    <t>VDORAN BABY6-12 900G</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>20138474</t>
-  </si>
-  <si>
-    <t>VIDORAN 5  MADU 900G</t>
-  </si>
-  <si>
-    <t>20113346</t>
-  </si>
-  <si>
-    <t>VDRAN XMRT1+ VAN 900</t>
-  </si>
-  <si>
-    <t>20101825</t>
-  </si>
-  <si>
-    <t>VDRAN XMRT1+ MDU 900</t>
   </si>
   <si>
     <t>20032058</t>
@@ -3451,10 +3451,10 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>5</v>
@@ -3471,10 +3471,10 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>5</v>
@@ -3494,10 +3494,10 @@
         <v>38</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>63</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -3514,10 +3514,10 @@
         <v>38</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>63</v>
+        <v>5</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -3534,10 +3534,10 @@
         <v>38</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>63</v>
+        <v>5</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -3551,10 +3551,10 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>38</v>
+        <v>134</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>5</v>
@@ -3574,10 +3574,10 @@
         <v>134</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>5</v>
+        <v>63</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -3594,7 +3594,7 @@
         <v>134</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>5</v>
@@ -3614,7 +3614,7 @@
         <v>134</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>5</v>
@@ -3634,7 +3634,7 @@
         <v>134</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>5</v>
@@ -3651,10 +3651,10 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>5</v>
@@ -3674,10 +3674,10 @@
         <v>137</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>5</v>
+        <v>63</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -3694,10 +3694,10 @@
         <v>137</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>63</v>
+        <v>16</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -3714,7 +3714,7 @@
         <v>137</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -3734,10 +3734,10 @@
         <v>137</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -3751,33 +3751,33 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>137</v>
+        <v>230</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>5</v>
+        <v>63</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D107" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="B107" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="C107" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D107" s="1" t="s">
-        <v>232</v>
-      </c>
       <c r="E107" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -3791,13 +3791,13 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -3811,10 +3811,10 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -3831,10 +3831,10 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>5</v>

--- a/MBF04S.xlsx
+++ b/MBF04S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1128" uniqueCount="409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1128" uniqueCount="408">
   <si>
     <t/>
   </si>
@@ -67,7 +67,7 @@
     <t>20068905</t>
   </si>
   <si>
-    <t>FF SKM PUTIH 535G</t>
+    <t>FF SKM PUTIH 535 G</t>
   </si>
   <si>
     <t>5</t>
@@ -79,7 +79,7 @@
     <t>20068906</t>
   </si>
   <si>
-    <t>FF SKM COKELAT 535G</t>
+    <t>FF SKM COKELAT 535 G</t>
   </si>
   <si>
     <t>6</t>
@@ -607,6 +607,12 @@
     <t>FF CRMY GULA ARN 240</t>
   </si>
   <si>
+    <t>20040303</t>
+  </si>
+  <si>
+    <t>SGM EKSPL3+ CKLT 400</t>
+  </si>
+  <si>
     <t>20070110</t>
   </si>
   <si>
@@ -640,7 +646,7 @@
     <t>20098371</t>
   </si>
   <si>
-    <t>VDORAN SUSU MADU 350</t>
+    <t>VDORAN SUSU MADU 325</t>
   </si>
   <si>
     <t>20098369</t>
@@ -670,7 +676,7 @@
     <t>20098370</t>
   </si>
   <si>
-    <t>VDORAN XMRT1+ MDU350</t>
+    <t>VDORAN XMRT1+ MDU325</t>
   </si>
   <si>
     <t>20098368</t>
@@ -1157,15 +1163,6 @@
   </si>
   <si>
     <t>LACTOGEN PRO FORM350</t>
-  </si>
-  <si>
-    <t>20040303</t>
-  </si>
-  <si>
-    <t>SGM EKSPL3+ CKLT 400</t>
-  </si>
-  <si>
-    <t>26</t>
   </si>
   <si>
     <t>20057224</t>
@@ -3451,10 +3448,10 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>5</v>
@@ -3474,7 +3471,7 @@
         <v>38</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>5</v>
@@ -3494,7 +3491,7 @@
         <v>38</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>5</v>
@@ -3514,7 +3511,7 @@
         <v>38</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>5</v>
@@ -3534,7 +3531,7 @@
         <v>38</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>5</v>
@@ -3551,10 +3548,10 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>134</v>
+        <v>38</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>5</v>
@@ -3574,10 +3571,10 @@
         <v>134</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>63</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -3594,10 +3591,10 @@
         <v>134</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>5</v>
+        <v>63</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -3614,7 +3611,7 @@
         <v>134</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>5</v>
@@ -3634,7 +3631,7 @@
         <v>134</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>5</v>
@@ -3651,10 +3648,10 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>5</v>
@@ -3674,10 +3671,10 @@
         <v>137</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>63</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -3694,10 +3691,10 @@
         <v>137</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -3714,10 +3711,10 @@
         <v>137</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -3734,10 +3731,10 @@
         <v>137</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -3751,30 +3748,30 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>230</v>
+        <v>137</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>63</v>
+        <v>16</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B107" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="B107" s="1" t="s">
+      <c r="C107" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D107" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="C107" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D107" s="1" t="s">
-        <v>230</v>
-      </c>
       <c r="E107" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>63</v>
@@ -3791,13 +3788,13 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>5</v>
+        <v>63</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -3811,10 +3808,10 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -3831,10 +3828,10 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>5</v>
@@ -3851,33 +3848,33 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B112" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="B112" s="1" t="s">
+      <c r="C112" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D112" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="C112" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>241</v>
-      </c>
       <c r="E112" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -3891,10 +3888,10 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>16</v>
@@ -3911,13 +3908,13 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -3931,10 +3928,10 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>12</v>
@@ -3951,10 +3948,10 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>12</v>
@@ -3971,10 +3968,10 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>12</v>
@@ -3991,10 +3988,10 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>12</v>
@@ -4011,10 +4008,10 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>12</v>
@@ -4022,19 +4019,19 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B120" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="B120" s="1" t="s">
+      <c r="C120" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D120" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C120" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>258</v>
-      </c>
       <c r="E120" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>12</v>
@@ -4051,10 +4048,10 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>12</v>
@@ -4071,10 +4068,10 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>12</v>
@@ -4091,10 +4088,10 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>12</v>
@@ -4111,13 +4108,13 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -4131,10 +4128,10 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>5</v>
@@ -4151,10 +4148,10 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>273</v>
+        <v>260</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>5</v>
@@ -4162,19 +4159,19 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="B127" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="B127" s="1" t="s">
+      <c r="C127" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D127" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="C127" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>273</v>
-      </c>
       <c r="E127" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>5</v>
@@ -4191,10 +4188,10 @@
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>5</v>
@@ -4211,10 +4208,10 @@
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>5</v>
@@ -4231,10 +4228,10 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>5</v>
@@ -4251,10 +4248,10 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>5</v>
@@ -4271,10 +4268,10 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>5</v>
@@ -4291,10 +4288,10 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>288</v>
+        <v>275</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>5</v>
@@ -4302,19 +4299,19 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B134" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="B134" s="1" t="s">
+      <c r="C134" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D134" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="C134" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D134" s="1" t="s">
-        <v>288</v>
-      </c>
       <c r="E134" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>5</v>
@@ -4331,10 +4328,10 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>5</v>
@@ -4351,10 +4348,10 @@
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>5</v>
@@ -4371,10 +4368,10 @@
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>5</v>
@@ -4391,10 +4388,10 @@
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>5</v>
@@ -4411,10 +4408,10 @@
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>301</v>
+        <v>290</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>5</v>
@@ -4422,19 +4419,19 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B140" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="B140" s="1" t="s">
+      <c r="C140" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D140" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="C140" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>301</v>
-      </c>
       <c r="E140" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>5</v>
@@ -4451,10 +4448,10 @@
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>5</v>
@@ -4471,10 +4468,10 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>5</v>
@@ -4491,10 +4488,10 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>5</v>
@@ -4511,10 +4508,10 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>5</v>
@@ -4522,19 +4519,19 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="B145" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="B145" s="1" t="s">
+      <c r="C145" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D145" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="C145" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D145" s="1" t="s">
-        <v>312</v>
-      </c>
       <c r="E145" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>5</v>
@@ -4551,10 +4548,10 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>5</v>
@@ -4571,10 +4568,10 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>5</v>
@@ -4591,13 +4588,13 @@
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -4611,30 +4608,30 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="B150" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="B150" s="1" t="s">
+      <c r="C150" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D150" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="C150" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D150" s="1" t="s">
-        <v>323</v>
-      </c>
       <c r="E150" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>5</v>
@@ -4651,13 +4648,13 @@
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
@@ -4671,13 +4668,13 @@
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
@@ -4691,10 +4688,10 @@
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>5</v>
@@ -4711,10 +4708,10 @@
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>5</v>
@@ -4722,19 +4719,19 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B155" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B155" s="1" t="s">
+      <c r="C155" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D155" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="C155" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D155" s="1" t="s">
-        <v>334</v>
-      </c>
       <c r="E155" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>5</v>
@@ -4751,10 +4748,10 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>5</v>
@@ -4771,10 +4768,10 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>5</v>
@@ -4791,10 +4788,10 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>5</v>
@@ -4811,10 +4808,10 @@
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>5</v>
@@ -4831,10 +4828,10 @@
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>347</v>
+        <v>336</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>5</v>
@@ -4842,19 +4839,19 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="B161" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="B161" s="1" t="s">
+      <c r="C161" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D161" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="C161" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D161" s="1" t="s">
-        <v>347</v>
-      </c>
       <c r="E161" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>5</v>
@@ -4871,10 +4868,10 @@
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>5</v>
@@ -4891,10 +4888,10 @@
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>5</v>
@@ -4911,10 +4908,10 @@
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>5</v>
@@ -4931,10 +4928,10 @@
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>5</v>
@@ -4942,19 +4939,19 @@
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="B166" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="B166" s="1" t="s">
+      <c r="C166" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D166" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="C166" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D166" s="1" t="s">
-        <v>358</v>
-      </c>
       <c r="E166" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>5</v>
@@ -4971,10 +4968,10 @@
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>5</v>
@@ -4991,10 +4988,10 @@
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>5</v>
@@ -5011,10 +5008,10 @@
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>5</v>
@@ -5031,10 +5028,10 @@
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>5</v>
@@ -5051,10 +5048,10 @@
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>5</v>
@@ -5062,19 +5059,19 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="B172" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="B172" s="1" t="s">
+      <c r="C172" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D172" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="C172" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D172" s="1" t="s">
-        <v>371</v>
-      </c>
       <c r="E172" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>5</v>
@@ -5091,10 +5088,10 @@
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>5</v>
@@ -5111,10 +5108,10 @@
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>5</v>
@@ -5131,10 +5128,10 @@
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>5</v>
@@ -5151,10 +5148,10 @@
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>5</v>
@@ -5171,10 +5168,10 @@
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>384</v>
+        <v>373</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>5</v>
@@ -5182,16 +5179,16 @@
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="B178" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="B178" s="1" t="s">
+      <c r="C178" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D178" s="1" t="s">
         <v>386</v>
-      </c>
-      <c r="C178" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D178" s="1" t="s">
-        <v>387</v>
       </c>
       <c r="E178" s="1" t="s">
         <v>4</v>
@@ -5202,16 +5199,16 @@
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="B179" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="B179" s="1" t="s">
-        <v>389</v>
-      </c>
       <c r="C179" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E179" s="1" t="s">
         <v>8</v>
@@ -5222,16 +5219,16 @@
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="B180" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="B180" s="1" t="s">
-        <v>391</v>
-      </c>
       <c r="C180" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E180" s="1" t="s">
         <v>11</v>
@@ -5242,16 +5239,16 @@
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="B181" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="B181" s="1" t="s">
-        <v>393</v>
-      </c>
       <c r="C181" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E181" s="1" t="s">
         <v>15</v>
@@ -5262,16 +5259,16 @@
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="B182" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="B182" s="1" t="s">
-        <v>395</v>
-      </c>
       <c r="C182" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E182" s="1" t="s">
         <v>19</v>
@@ -5282,16 +5279,16 @@
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="B183" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="B183" s="1" t="s">
-        <v>397</v>
-      </c>
       <c r="C183" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E183" s="1" t="s">
         <v>23</v>
@@ -5302,16 +5299,16 @@
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="B184" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="B184" s="1" t="s">
+      <c r="C184" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D184" s="1" t="s">
         <v>399</v>
-      </c>
-      <c r="C184" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D184" s="1" t="s">
-        <v>400</v>
       </c>
       <c r="E184" s="1" t="s">
         <v>4</v>
@@ -5322,16 +5319,16 @@
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B185" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="B185" s="1" t="s">
-        <v>402</v>
-      </c>
       <c r="C185" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E185" s="1" t="s">
         <v>8</v>
@@ -5342,16 +5339,16 @@
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B186" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="B186" s="1" t="s">
-        <v>404</v>
-      </c>
       <c r="C186" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E186" s="1" t="s">
         <v>11</v>
@@ -5362,16 +5359,16 @@
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="B187" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="B187" s="1" t="s">
-        <v>406</v>
-      </c>
       <c r="C187" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E187" s="1" t="s">
         <v>15</v>
@@ -5382,16 +5379,16 @@
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="B188" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="B188" s="1" t="s">
-        <v>408</v>
-      </c>
       <c r="C188" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E188" s="1" t="s">
         <v>19</v>

--- a/MBF04S.xlsx
+++ b/MBF04S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1128" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1152" uniqueCount="417">
   <si>
     <t/>
   </si>
@@ -67,7 +67,7 @@
     <t>20068905</t>
   </si>
   <si>
-    <t>FF SKM PUTIH 535 G</t>
+    <t>FF SKM PUTIH 535G</t>
   </si>
   <si>
     <t>5</t>
@@ -79,7 +79,7 @@
     <t>20068906</t>
   </si>
   <si>
-    <t>FF SKM COKELAT 535 G</t>
+    <t>FF SKM COKELAT 535G</t>
   </si>
   <si>
     <t>6</t>
@@ -1163,6 +1163,33 @@
   </si>
   <si>
     <t>LACTOGEN PRO FORM350</t>
+  </si>
+  <si>
+    <t>20142948</t>
+  </si>
+  <si>
+    <t>BEBELOVE 6-12BLN 775</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>20142950</t>
+  </si>
+  <si>
+    <t>BEBELAC 1+ VAN 775G</t>
+  </si>
+  <si>
+    <t>20142951</t>
+  </si>
+  <si>
+    <t>BEBELAC 1+ MADU 775</t>
+  </si>
+  <si>
+    <t>20142947</t>
+  </si>
+  <si>
+    <t>BEBELOVE  0-6BLN 775</t>
   </si>
   <si>
     <t>20057224</t>
@@ -1627,7 +1654,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F188"/>
+  <dimension ref="A1:F192"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -5194,7 +5221,7 @@
         <v>4</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
@@ -5214,7 +5241,7 @@
         <v>8</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
@@ -5234,7 +5261,7 @@
         <v>11</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
@@ -5254,7 +5281,7 @@
         <v>15</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
@@ -5268,10 +5295,10 @@
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>5</v>
@@ -5279,19 +5306,19 @@
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="B183" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="C183" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D183" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="B183" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="C183" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D183" s="1" t="s">
-        <v>386</v>
-      </c>
       <c r="E183" s="1" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>5</v>
@@ -5299,19 +5326,19 @@
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>5</v>
@@ -5328,13 +5355,13 @@
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
@@ -5348,13 +5375,13 @@
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
@@ -5368,10 +5395,10 @@
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F187" s="1" t="s">
         <v>5</v>
@@ -5388,12 +5415,92 @@
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="E188" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F188" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A189" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="B189" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="C189" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D189" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="E189" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F189" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A190" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="B190" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="C190" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D190" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="E190" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F190" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A191" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="B191" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="C191" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D191" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="E191" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F191" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A192" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="B192" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="C192" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D192" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="E192" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F188" s="1" t="s">
+      <c r="F192" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/MBF04S.xlsx
+++ b/MBF04S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1152" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1146" uniqueCount="416">
   <si>
     <t/>
   </si>
@@ -463,18 +463,6 @@
     <t>YB BABY CRACK BNN 25</t>
   </si>
   <si>
-    <t>20138661</t>
-  </si>
-  <si>
-    <t>BROMON CKS MIX.F 100</t>
-  </si>
-  <si>
-    <t>20138660</t>
-  </si>
-  <si>
-    <t>BOROMON CKS MILK 100</t>
-  </si>
-  <si>
     <t>20125783</t>
   </si>
   <si>
@@ -1262,6 +1250,15 @@
   </si>
   <si>
     <t>BEBELAC1+ VNL BX1000</t>
+  </si>
+  <si>
+    <t>20142954</t>
+  </si>
+  <si>
+    <t>VIDORAN 5+VAN 700G</t>
+  </si>
+  <si>
+    <t>998</t>
   </si>
 </sst>
 </file>
@@ -1654,13 +1651,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F192"/>
+  <dimension ref="A1:F191"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="5" width="4" customWidth="1"/>
+    <col min="4" max="4" width="5" customWidth="1"/>
+    <col min="5" max="5" width="4" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2995,10 +2993,10 @@
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>16</v>
@@ -3015,10 +3013,10 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>16</v>
@@ -3038,10 +3036,10 @@
         <v>29</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -3058,10 +3056,10 @@
         <v>29</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -3078,7 +3076,7 @@
         <v>29</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>20</v>
@@ -3098,10 +3096,10 @@
         <v>29</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -3118,7 +3116,7 @@
         <v>29</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>20</v>
@@ -3138,7 +3136,7 @@
         <v>29</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>16</v>
@@ -3158,10 +3156,10 @@
         <v>29</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -3178,7 +3176,7 @@
         <v>29</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>16</v>
@@ -3198,10 +3196,10 @@
         <v>29</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>35</v>
+        <v>134</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>5</v>
+        <v>63</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -3215,13 +3213,13 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -3235,13 +3233,13 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>134</v>
+        <v>8</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>63</v>
+        <v>16</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -3258,10 +3256,10 @@
         <v>32</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -3278,10 +3276,10 @@
         <v>32</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -3298,10 +3296,10 @@
         <v>32</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -3318,10 +3316,10 @@
         <v>32</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>63</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -3338,7 +3336,7 @@
         <v>32</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>12</v>
@@ -3355,10 +3353,10 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>5</v>
@@ -3375,13 +3373,13 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -3398,10 +3396,10 @@
         <v>35</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -3418,7 +3416,7 @@
         <v>35</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>20</v>
@@ -3438,10 +3436,10 @@
         <v>35</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -3455,13 +3453,13 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -3475,10 +3473,10 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>5</v>
@@ -3498,7 +3496,7 @@
         <v>38</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>5</v>
@@ -3518,7 +3516,7 @@
         <v>38</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>5</v>
@@ -3538,7 +3536,7 @@
         <v>38</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>5</v>
@@ -3555,10 +3553,10 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>38</v>
+        <v>134</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>5</v>
@@ -3575,13 +3573,13 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>38</v>
+        <v>134</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>5</v>
+        <v>63</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -3598,7 +3596,7 @@
         <v>134</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>5</v>
@@ -3618,10 +3616,10 @@
         <v>134</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>63</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -3638,7 +3636,7 @@
         <v>134</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>5</v>
@@ -3655,10 +3653,10 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>5</v>
@@ -3675,13 +3673,13 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>5</v>
+        <v>63</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -3698,10 +3696,10 @@
         <v>137</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -3718,10 +3716,10 @@
         <v>137</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>63</v>
+        <v>5</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -3738,7 +3736,7 @@
         <v>137</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>16</v>
@@ -3755,53 +3753,53 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>137</v>
+        <v>228</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>5</v>
+        <v>63</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D106" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="B106" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="C106" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D106" s="1" t="s">
-        <v>137</v>
-      </c>
       <c r="E106" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>63</v>
+        <v>5</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -3815,13 +3813,13 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>63</v>
+        <v>5</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -3835,10 +3833,10 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -3855,53 +3853,53 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D111" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="B111" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="C111" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>232</v>
-      </c>
       <c r="E111" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -3915,13 +3913,13 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -3935,13 +3933,13 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -3955,10 +3953,10 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>12</v>
@@ -3975,10 +3973,10 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>12</v>
@@ -3995,10 +3993,10 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>12</v>
@@ -4015,10 +4013,10 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>12</v>
@@ -4026,19 +4024,19 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D119" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="B119" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="C119" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>243</v>
-      </c>
       <c r="E119" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>12</v>
@@ -4046,19 +4044,19 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>12</v>
@@ -4075,10 +4073,10 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>12</v>
@@ -4095,10 +4093,10 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>12</v>
@@ -4115,13 +4113,13 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -4135,13 +4133,13 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -4155,10 +4153,10 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>5</v>
@@ -4166,19 +4164,19 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D126" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="B126" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="C126" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D126" s="1" t="s">
-        <v>260</v>
-      </c>
       <c r="E126" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>5</v>
@@ -4186,19 +4184,19 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>5</v>
@@ -4215,10 +4213,10 @@
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>5</v>
@@ -4235,10 +4233,10 @@
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>5</v>
@@ -4255,10 +4253,10 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>5</v>
@@ -4275,10 +4273,10 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>5</v>
@@ -4295,10 +4293,10 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>5</v>
@@ -4306,19 +4304,19 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D133" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="B133" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="C133" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D133" s="1" t="s">
-        <v>275</v>
-      </c>
       <c r="E133" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>5</v>
@@ -4326,19 +4324,19 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>5</v>
@@ -4355,10 +4353,10 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>5</v>
@@ -4375,10 +4373,10 @@
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>5</v>
@@ -4395,10 +4393,10 @@
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>5</v>
@@ -4415,10 +4413,10 @@
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>5</v>
@@ -4426,19 +4424,19 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D139" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="B139" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="C139" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>290</v>
-      </c>
       <c r="E139" s="1" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>5</v>
@@ -4446,19 +4444,19 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>5</v>
@@ -4475,10 +4473,10 @@
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>5</v>
@@ -4495,10 +4493,10 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>5</v>
@@ -4515,10 +4513,10 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>5</v>
@@ -4526,19 +4524,19 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D144" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="B144" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="C144" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D144" s="1" t="s">
-        <v>303</v>
-      </c>
       <c r="E144" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>5</v>
@@ -4546,19 +4544,19 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>5</v>
@@ -4575,10 +4573,10 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>5</v>
@@ -4595,13 +4593,13 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
@@ -4615,10 +4613,10 @@
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>5</v>
@@ -4626,42 +4624,42 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D149" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="B149" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="C149" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D149" s="1" t="s">
-        <v>314</v>
-      </c>
       <c r="E149" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
@@ -4675,10 +4673,10 @@
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>5</v>
@@ -4695,13 +4693,13 @@
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
@@ -4715,10 +4713,10 @@
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>5</v>
@@ -4726,19 +4724,19 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D154" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="B154" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="C154" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D154" s="1" t="s">
-        <v>325</v>
-      </c>
       <c r="E154" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>5</v>
@@ -4746,19 +4744,19 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>5</v>
@@ -4775,10 +4773,10 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>5</v>
@@ -4795,10 +4793,10 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>5</v>
@@ -4815,10 +4813,10 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>5</v>
@@ -4835,10 +4833,10 @@
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>5</v>
@@ -4846,19 +4844,19 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D160" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="B160" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="C160" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D160" s="1" t="s">
-        <v>336</v>
-      </c>
       <c r="E160" s="1" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>5</v>
@@ -4866,19 +4864,19 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>5</v>
@@ -4895,10 +4893,10 @@
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>5</v>
@@ -4915,10 +4913,10 @@
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>5</v>
@@ -4935,10 +4933,10 @@
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>5</v>
@@ -4946,19 +4944,19 @@
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D165" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="B165" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="C165" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D165" s="1" t="s">
-        <v>349</v>
-      </c>
       <c r="E165" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>5</v>
@@ -4966,19 +4964,19 @@
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>5</v>
@@ -4995,10 +4993,10 @@
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>5</v>
@@ -5015,10 +5013,10 @@
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>5</v>
@@ -5035,10 +5033,10 @@
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>5</v>
@@ -5055,10 +5053,10 @@
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>5</v>
@@ -5066,19 +5064,19 @@
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D171" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="B171" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="C171" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D171" s="1" t="s">
-        <v>360</v>
-      </c>
       <c r="E171" s="1" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>5</v>
@@ -5086,19 +5084,19 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>5</v>
@@ -5115,10 +5113,10 @@
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>5</v>
@@ -5135,10 +5133,10 @@
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>5</v>
@@ -5155,10 +5153,10 @@
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>5</v>
@@ -5175,50 +5173,50 @@
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D177" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="B177" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="C177" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D177" s="1" t="s">
-        <v>373</v>
-      </c>
       <c r="E177" s="1" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>16</v>
@@ -5235,10 +5233,10 @@
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>16</v>
@@ -5255,50 +5253,50 @@
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="B181" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="C181" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D181" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="B181" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="C181" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D181" s="1" t="s">
-        <v>386</v>
-      </c>
       <c r="E181" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>5</v>
@@ -5315,10 +5313,10 @@
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>5</v>
@@ -5335,10 +5333,10 @@
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>5</v>
@@ -5355,10 +5353,10 @@
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>5</v>
@@ -5375,10 +5373,10 @@
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="F186" s="1" t="s">
         <v>5</v>
@@ -5386,42 +5384,42 @@
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="B187" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="C187" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D187" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="B187" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="C187" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D187" s="1" t="s">
-        <v>395</v>
-      </c>
       <c r="E187" s="1" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
@@ -5435,13 +5433,13 @@
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
@@ -5455,13 +5453,13 @@
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
@@ -5475,33 +5473,13 @@
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A192" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="B192" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="C192" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D192" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="E192" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F192" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/MBF04S.xlsx
+++ b/MBF04S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1146" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1170" uniqueCount="425">
   <si>
     <t/>
   </si>
@@ -487,6 +487,795 @@
     <t>FF GOLD SKM PTH 370G</t>
   </si>
   <si>
+    <t>20002313</t>
+  </si>
+  <si>
+    <t>FF KRM MNS OMELA 370</t>
+  </si>
+  <si>
+    <t>20054589</t>
+  </si>
+  <si>
+    <t>3SAPI KRIMER 490G</t>
+  </si>
+  <si>
+    <t>10036665</t>
+  </si>
+  <si>
+    <t>CARNATION KKM 365G</t>
+  </si>
+  <si>
+    <t>20105631</t>
+  </si>
+  <si>
+    <t>CARNATION KKM 405G</t>
+  </si>
+  <si>
+    <t>20101859</t>
+  </si>
+  <si>
+    <t>SUNBAY EVP.MILK 380G</t>
+  </si>
+  <si>
+    <t>20136510</t>
+  </si>
+  <si>
+    <t>MILO 3IN1 ACT-GO 400</t>
+  </si>
+  <si>
+    <t>20027850</t>
+  </si>
+  <si>
+    <t>ZEE VNILA TWST 340G</t>
+  </si>
+  <si>
+    <t>20027848</t>
+  </si>
+  <si>
+    <t>ZEE SWIZZ CHO 340G</t>
+  </si>
+  <si>
+    <t>10033006</t>
+  </si>
+  <si>
+    <t>PRENAGEN HML CHO 180</t>
+  </si>
+  <si>
+    <t>20011063</t>
+  </si>
+  <si>
+    <t>PRENAGEN HML CHO 360</t>
+  </si>
+  <si>
+    <t>20033353</t>
+  </si>
+  <si>
+    <t>HILO/S HI-CAL CHO250</t>
+  </si>
+  <si>
+    <t>10000578</t>
+  </si>
+  <si>
+    <t>DIABETASOL VNL.170GR</t>
+  </si>
+  <si>
+    <t>20070110</t>
+  </si>
+  <si>
+    <t>VDORAN XMRT1+ MDU700</t>
+  </si>
+  <si>
+    <t>20090042</t>
+  </si>
+  <si>
+    <t>VDORAN XMRT1+ VAN700</t>
+  </si>
+  <si>
+    <t>20082394</t>
+  </si>
+  <si>
+    <t>VDORAN XMRT3+ MDU700</t>
+  </si>
+  <si>
+    <t>20090437</t>
+  </si>
+  <si>
+    <t>VDORAN XMRT3+ VAN700</t>
+  </si>
+  <si>
+    <t>20117983</t>
+  </si>
+  <si>
+    <t>VIDORAN XM5+ COKL700</t>
+  </si>
+  <si>
+    <t>20142907</t>
+  </si>
+  <si>
+    <t>MILKOW A/G 1 MDU 600</t>
+  </si>
+  <si>
+    <t>,(E-1B)</t>
+  </si>
+  <si>
+    <t>20142909</t>
+  </si>
+  <si>
+    <t>MILKOW A/G 1 VNL 600</t>
+  </si>
+  <si>
+    <t>20142910</t>
+  </si>
+  <si>
+    <t>MILKOW A/G 1 MDU 900</t>
+  </si>
+  <si>
+    <t>20142908</t>
+  </si>
+  <si>
+    <t>MILKOW A/G 1 VNL 900</t>
+  </si>
+  <si>
+    <t>20098371</t>
+  </si>
+  <si>
+    <t>VDORAN SUSU MADU 325</t>
+  </si>
+  <si>
+    <t>20098369</t>
+  </si>
+  <si>
+    <t>VDORAN XMRT3+ VAN350</t>
+  </si>
+  <si>
+    <t>20101825</t>
+  </si>
+  <si>
+    <t>VDRAN XMRT1+ MDU 900</t>
+  </si>
+  <si>
+    <t>20113346</t>
+  </si>
+  <si>
+    <t>VDRAN XMRT1+ VAN 900</t>
+  </si>
+  <si>
+    <t>20106381</t>
+  </si>
+  <si>
+    <t>VDRAN XMRT3+ MDU 900</t>
+  </si>
+  <si>
+    <t>20098370</t>
+  </si>
+  <si>
+    <t>VDORAN XMRT1+ MDU325</t>
+  </si>
+  <si>
+    <t>20098368</t>
+  </si>
+  <si>
+    <t>VDORAN XMRT1+ VAN325</t>
+  </si>
+  <si>
+    <t>20138473</t>
+  </si>
+  <si>
+    <t>VDORAN BABY6-12 900G</t>
+  </si>
+  <si>
+    <t>20117981</t>
+  </si>
+  <si>
+    <t>VIDORAN XM3+ VNL900</t>
+  </si>
+  <si>
+    <t>20138474</t>
+  </si>
+  <si>
+    <t>VIDORAN 5  MADU 900G</t>
+  </si>
+  <si>
+    <t>20142954</t>
+  </si>
+  <si>
+    <t>VIDORAN 5+VAN 700G</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>20135200</t>
+  </si>
+  <si>
+    <t>VIDORAN BABY0-6 550G</t>
+  </si>
+  <si>
+    <t>20129773</t>
+  </si>
+  <si>
+    <t>VDORAN BABY6-12 550G</t>
+  </si>
+  <si>
+    <t>20117985</t>
+  </si>
+  <si>
+    <t>VIDORAN XM5+ MADU700</t>
+  </si>
+  <si>
+    <t>20032058</t>
+  </si>
+  <si>
+    <t>FF KENTAL MANIS 6X37</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>20013433</t>
+  </si>
+  <si>
+    <t>INDOMILK SKM PTH6X37</t>
+  </si>
+  <si>
+    <t>20087580</t>
+  </si>
+  <si>
+    <t>ENTRASOL GLD VAN560</t>
+  </si>
+  <si>
+    <t>10025373</t>
+  </si>
+  <si>
+    <t>ENTRASOL GOLD VAN170</t>
+  </si>
+  <si>
+    <t>20021571</t>
+  </si>
+  <si>
+    <t>ANLENE GOLD VAN 560G</t>
+  </si>
+  <si>
+    <t>10020147</t>
+  </si>
+  <si>
+    <t>ANLENE GOLD CKLT 230</t>
+  </si>
+  <si>
+    <t>10008064</t>
+  </si>
+  <si>
+    <t>ANLENE GOLD ORG240G</t>
+  </si>
+  <si>
+    <t>10012172</t>
+  </si>
+  <si>
+    <t>ANLENE GOLD VNLA 230</t>
+  </si>
+  <si>
+    <t>10003653</t>
+  </si>
+  <si>
+    <t>MRINAGA BMT1 LAC.390</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>20014399</t>
+  </si>
+  <si>
+    <t>MORINAGA CK3 VAN 780</t>
+  </si>
+  <si>
+    <t>10005241</t>
+  </si>
+  <si>
+    <t>MORINAGA CM ORGN 190</t>
+  </si>
+  <si>
+    <t>10008314</t>
+  </si>
+  <si>
+    <t>MORINAGA CK VNLA 190</t>
+  </si>
+  <si>
+    <t>10008316</t>
+  </si>
+  <si>
+    <t>MORINAGA CK MADU 190</t>
+  </si>
+  <si>
+    <t>10010874</t>
+  </si>
+  <si>
+    <t>DNCOW 1+ MDU BOX 120</t>
+  </si>
+  <si>
+    <t>10005338</t>
+  </si>
+  <si>
+    <t>DNCOW FRTGO BOX 195G</t>
+  </si>
+  <si>
+    <t>10026038</t>
+  </si>
+  <si>
+    <t>SGM EKSPL1+ MADU 150</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>20040575</t>
+  </si>
+  <si>
+    <t>SGM EKSPL1+ VAN 150G</t>
+  </si>
+  <si>
+    <t>20056930</t>
+  </si>
+  <si>
+    <t>SGM EKSPL3+ MADU 150</t>
+  </si>
+  <si>
+    <t>20037098</t>
+  </si>
+  <si>
+    <t>SGM SOYA 1+ VANL 400</t>
+  </si>
+  <si>
+    <t>20040302</t>
+  </si>
+  <si>
+    <t>SGM EKSPL3+ MADU 400</t>
+  </si>
+  <si>
+    <t>20040301</t>
+  </si>
+  <si>
+    <t>SGM EKSPL3+ VAN 400G</t>
+  </si>
+  <si>
+    <t>10009494</t>
+  </si>
+  <si>
+    <t>DANCOW FORTIGRO 390G</t>
+  </si>
+  <si>
+    <t>20040340</t>
+  </si>
+  <si>
+    <t>SGM ANANDA1 BOX 400G</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>20040312</t>
+  </si>
+  <si>
+    <t>SGM ANANDA2 BOX 400G</t>
+  </si>
+  <si>
+    <t>20040299</t>
+  </si>
+  <si>
+    <t>SGM EKSPL1+ MADU 400</t>
+  </si>
+  <si>
+    <t>20040300</t>
+  </si>
+  <si>
+    <t>SGM EKSPL1+ VAN 400G</t>
+  </si>
+  <si>
+    <t>20087025</t>
+  </si>
+  <si>
+    <t>SGM EKSPL3+ VAN 600G</t>
+  </si>
+  <si>
+    <t>20087024</t>
+  </si>
+  <si>
+    <t>SGM EKSPL3+ MADU 600</t>
+  </si>
+  <si>
+    <t>20047323</t>
+  </si>
+  <si>
+    <t>SGM ANANDA1 BOX 550G</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20047324</t>
+  </si>
+  <si>
+    <t>SGM ANANDA2 BOX 550G</t>
+  </si>
+  <si>
+    <t>20074147</t>
+  </si>
+  <si>
+    <t>SGM EKSPL1+ MADU 600</t>
+  </si>
+  <si>
+    <t>20077508</t>
+  </si>
+  <si>
+    <t>SGM EKSPL1+ VAN 600G</t>
+  </si>
+  <si>
+    <t>20040294</t>
+  </si>
+  <si>
+    <t>SGM EKSPL1+ MADU 900</t>
+  </si>
+  <si>
+    <t>10005279</t>
+  </si>
+  <si>
+    <t>SGM ANANDA2 BOX 150G</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>20040293</t>
+  </si>
+  <si>
+    <t>SGM EKSPL1+ VAN 900G</t>
+  </si>
+  <si>
+    <t>20040296</t>
+  </si>
+  <si>
+    <t>SGM EKSPL3+ MADU 900</t>
+  </si>
+  <si>
+    <t>20040295</t>
+  </si>
+  <si>
+    <t>SGM EKSPL3+ VAN 900G</t>
+  </si>
+  <si>
+    <t>20066494</t>
+  </si>
+  <si>
+    <t>SGM EKSPL5+ MADU 900</t>
+  </si>
+  <si>
+    <t>10005315</t>
+  </si>
+  <si>
+    <t>SGM ANANDA1 BOX 150G</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>20040297</t>
+  </si>
+  <si>
+    <t>SGM ANANDA1 BOX 1KG</t>
+  </si>
+  <si>
+    <t>20040298</t>
+  </si>
+  <si>
+    <t>SGM ANANDA2 BOX 1KG</t>
+  </si>
+  <si>
+    <t>20065379</t>
+  </si>
+  <si>
+    <t>SGM SOYA1+ VANL 700G</t>
+  </si>
+  <si>
+    <t>20071686</t>
+  </si>
+  <si>
+    <t>SGM SOYA1+ MADU 700G</t>
+  </si>
+  <si>
+    <t>20005712</t>
+  </si>
+  <si>
+    <t>DNCOW 5+ VAN BOX 350</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>10009495</t>
+  </si>
+  <si>
+    <t>DNCW FRTG FL.CRM 390</t>
+  </si>
+  <si>
+    <t>10009493</t>
+  </si>
+  <si>
+    <t>DNCOW FRTGO COK 390G</t>
+  </si>
+  <si>
+    <t>10006259</t>
+  </si>
+  <si>
+    <t>DNCOW FRTGO ENR 780G</t>
+  </si>
+  <si>
+    <t>10006260</t>
+  </si>
+  <si>
+    <t>DNCOW FRTGO COK 780</t>
+  </si>
+  <si>
+    <t>10006258</t>
+  </si>
+  <si>
+    <t>DNCOWFRTGO F.CR 780G</t>
+  </si>
+  <si>
+    <t>10006262</t>
+  </si>
+  <si>
+    <t>DNCOW 1+ MDU BOX 750</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>10015652</t>
+  </si>
+  <si>
+    <t>DNCOW 1+ VAN BOX 750</t>
+  </si>
+  <si>
+    <t>10013035</t>
+  </si>
+  <si>
+    <t>DNCOW 3+ MDU BOX 750</t>
+  </si>
+  <si>
+    <t>10015650</t>
+  </si>
+  <si>
+    <t>DNCOW 3+ VAN BOX 750</t>
+  </si>
+  <si>
+    <t>10023780</t>
+  </si>
+  <si>
+    <t>DNCOW 5+ MDU BOX 750</t>
+  </si>
+  <si>
+    <t>10009496</t>
+  </si>
+  <si>
+    <t>DNCOW 1+ MDU BOX 350</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>10015653</t>
+  </si>
+  <si>
+    <t>DNCOW 1+ VAN BOX 350</t>
+  </si>
+  <si>
+    <t>10012967</t>
+  </si>
+  <si>
+    <t>DNCOW 3+ MDU BOX 350</t>
+  </si>
+  <si>
+    <t>10015651</t>
+  </si>
+  <si>
+    <t>DNCOW3+ VAN BOX  350</t>
+  </si>
+  <si>
+    <t>20017679</t>
+  </si>
+  <si>
+    <t>LACTOGEN PRO LANJ350</t>
+  </si>
+  <si>
+    <t>20113345</t>
+  </si>
+  <si>
+    <t>LACTOGRW PRO1+VAN350</t>
+  </si>
+  <si>
+    <t>20035629</t>
+  </si>
+  <si>
+    <t>BEBELAC 1+VNL BOX350</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>20035633</t>
+  </si>
+  <si>
+    <t>BEBELAC3+ VNL BOX350</t>
+  </si>
+  <si>
+    <t>20035635</t>
+  </si>
+  <si>
+    <t>BEBELAC3+ MDU BOX350</t>
+  </si>
+  <si>
+    <t>10025848</t>
+  </si>
+  <si>
+    <t>NTRILON 3 RYL VAN400</t>
+  </si>
+  <si>
+    <t>20055287</t>
+  </si>
+  <si>
+    <t>LACTOGRW PRO1+MDU350</t>
+  </si>
+  <si>
+    <t>20017965</t>
+  </si>
+  <si>
+    <t>LACTOGEN PRO FORM350</t>
+  </si>
+  <si>
+    <t>20142948</t>
+  </si>
+  <si>
+    <t>BEBELOVE 6-12BLN 775</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>20142950</t>
+  </si>
+  <si>
+    <t>BEBELAC 1+ VAN 775G</t>
+  </si>
+  <si>
+    <t>20142951</t>
+  </si>
+  <si>
+    <t>BEBELAC 1+ MADU 775</t>
+  </si>
+  <si>
+    <t>20142947</t>
+  </si>
+  <si>
+    <t>BEBELOVE  0-6BLN 775</t>
+  </si>
+  <si>
+    <t>20057224</t>
+  </si>
+  <si>
+    <t>BEBELOVE1 0-6 BOX175</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>20045528</t>
+  </si>
+  <si>
+    <t>BEBELOVE2 6-12BOX175</t>
+  </si>
+  <si>
+    <t>20043039</t>
+  </si>
+  <si>
+    <t>BEBELAC1+ MDU BOX175</t>
+  </si>
+  <si>
+    <t>20035626</t>
+  </si>
+  <si>
+    <t>BEBELOVE 1 BOX 350GR</t>
+  </si>
+  <si>
+    <t>20035627</t>
+  </si>
+  <si>
+    <t>BEBELOVE2 6-12BOX350</t>
+  </si>
+  <si>
+    <t>20035631</t>
+  </si>
+  <si>
+    <t>BEBELAC1+ MDU BOX350</t>
+  </si>
+  <si>
+    <t>20136285</t>
+  </si>
+  <si>
+    <t>BEBELOVE2 6-12BOX620</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>20122291</t>
+  </si>
+  <si>
+    <t>BEBELAC1+ MDU BOX600</t>
+  </si>
+  <si>
+    <t>20122288</t>
+  </si>
+  <si>
+    <t>BEBELAC1+ VAN BOX600</t>
+  </si>
+  <si>
+    <t>20069146</t>
+  </si>
+  <si>
+    <t>BEBELAC1+ MDU BX1000</t>
+  </si>
+  <si>
+    <t>20069147</t>
+  </si>
+  <si>
+    <t>BEBELAC1+ VNL BX1000</t>
+  </si>
+  <si>
+    <t>20139959</t>
+  </si>
+  <si>
+    <t>PRMN SALMON LM 120G</t>
+  </si>
+  <si>
+    <t>999</t>
+  </si>
+  <si>
+    <t>10000088</t>
+  </si>
+  <si>
+    <t>FF SKM CKLT KLG 370</t>
+  </si>
+  <si>
+    <t>10015124</t>
+  </si>
+  <si>
+    <t>FF SKM COKLAT 6X37</t>
+  </si>
+  <si>
+    <t>20141099</t>
+  </si>
+  <si>
+    <t>FF CRMY GULA ARN 240</t>
+  </si>
+  <si>
+    <t>20040303</t>
+  </si>
+  <si>
+    <t>SGM EKSPL3+ CKLT 400</t>
+  </si>
+  <si>
+    <t>20125788</t>
+  </si>
+  <si>
+    <t>HLTHYWY1+ SP MADU700</t>
+  </si>
+  <si>
+    <t>20125790</t>
+  </si>
+  <si>
+    <t>HLTHYWY3+ SB MADU700</t>
+  </si>
+  <si>
     <t>20089819</t>
   </si>
   <si>
@@ -497,768 +1286,6 @@
   </si>
   <si>
     <t>ENAK K/MNS PUTIH 370</t>
-  </si>
-  <si>
-    <t>20002313</t>
-  </si>
-  <si>
-    <t>FF KRM MNS OMELA 370</t>
-  </si>
-  <si>
-    <t>20054589</t>
-  </si>
-  <si>
-    <t>3SAPI KRIMER 490G</t>
-  </si>
-  <si>
-    <t>10036665</t>
-  </si>
-  <si>
-    <t>CARNATION KKM 365G</t>
-  </si>
-  <si>
-    <t>20105631</t>
-  </si>
-  <si>
-    <t>CARNATION KKM 405G</t>
-  </si>
-  <si>
-    <t>20101859</t>
-  </si>
-  <si>
-    <t>SUNBAY EVP.MILK 380G</t>
-  </si>
-  <si>
-    <t>20136510</t>
-  </si>
-  <si>
-    <t>MILO 3IN1 ACT-GO 400</t>
-  </si>
-  <si>
-    <t>20027850</t>
-  </si>
-  <si>
-    <t>ZEE VNILA TWST 340G</t>
-  </si>
-  <si>
-    <t>20027848</t>
-  </si>
-  <si>
-    <t>ZEE SWIZZ CHO 340G</t>
-  </si>
-  <si>
-    <t>10033006</t>
-  </si>
-  <si>
-    <t>PRENAGEN HML CHO 180</t>
-  </si>
-  <si>
-    <t>20011063</t>
-  </si>
-  <si>
-    <t>PRENAGEN HML CHO 360</t>
-  </si>
-  <si>
-    <t>20033353</t>
-  </si>
-  <si>
-    <t>HILO/S HI-CAL CHO250</t>
-  </si>
-  <si>
-    <t>10000578</t>
-  </si>
-  <si>
-    <t>DIABETASOL VNL.170GR</t>
-  </si>
-  <si>
-    <t>20139959</t>
-  </si>
-  <si>
-    <t>PRMN SALMON LM 120G</t>
-  </si>
-  <si>
-    <t>10000088</t>
-  </si>
-  <si>
-    <t>FF SKM CKLT KLG 370</t>
-  </si>
-  <si>
-    <t>10015124</t>
-  </si>
-  <si>
-    <t>FF SKM COKLAT 6X37</t>
-  </si>
-  <si>
-    <t>20141099</t>
-  </si>
-  <si>
-    <t>FF CRMY GULA ARN 240</t>
-  </si>
-  <si>
-    <t>20040303</t>
-  </si>
-  <si>
-    <t>SGM EKSPL3+ CKLT 400</t>
-  </si>
-  <si>
-    <t>20070110</t>
-  </si>
-  <si>
-    <t>VDORAN XMRT1+ MDU700</t>
-  </si>
-  <si>
-    <t>20090042</t>
-  </si>
-  <si>
-    <t>VDORAN XMRT1+ VAN700</t>
-  </si>
-  <si>
-    <t>20082394</t>
-  </si>
-  <si>
-    <t>VDORAN XMRT3+ MDU700</t>
-  </si>
-  <si>
-    <t>20090437</t>
-  </si>
-  <si>
-    <t>VDORAN XMRT3+ VAN700</t>
-  </si>
-  <si>
-    <t>20117983</t>
-  </si>
-  <si>
-    <t>VIDORAN XM5+ COKL700</t>
-  </si>
-  <si>
-    <t>20098371</t>
-  </si>
-  <si>
-    <t>VDORAN SUSU MADU 325</t>
-  </si>
-  <si>
-    <t>20098369</t>
-  </si>
-  <si>
-    <t>VDORAN XMRT3+ VAN350</t>
-  </si>
-  <si>
-    <t>20101825</t>
-  </si>
-  <si>
-    <t>VDRAN XMRT1+ MDU 900</t>
-  </si>
-  <si>
-    <t>20113346</t>
-  </si>
-  <si>
-    <t>VDRAN XMRT1+ VAN 900</t>
-  </si>
-  <si>
-    <t>20106381</t>
-  </si>
-  <si>
-    <t>VDRAN XMRT3+ MDU 900</t>
-  </si>
-  <si>
-    <t>20098370</t>
-  </si>
-  <si>
-    <t>VDORAN XMRT1+ MDU325</t>
-  </si>
-  <si>
-    <t>20098368</t>
-  </si>
-  <si>
-    <t>VDORAN XMRT1+ VAN325</t>
-  </si>
-  <si>
-    <t>20138473</t>
-  </si>
-  <si>
-    <t>VDORAN BABY6-12 900G</t>
-  </si>
-  <si>
-    <t>20117981</t>
-  </si>
-  <si>
-    <t>VIDORAN XM3+ VNL900</t>
-  </si>
-  <si>
-    <t>20138474</t>
-  </si>
-  <si>
-    <t>VIDORAN 5  MADU 900G</t>
-  </si>
-  <si>
-    <t>20135200</t>
-  </si>
-  <si>
-    <t>VIDORAN BABY0-6 550G</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>20129773</t>
-  </si>
-  <si>
-    <t>VDORAN BABY6-12 550G</t>
-  </si>
-  <si>
-    <t>20117985</t>
-  </si>
-  <si>
-    <t>VIDORAN XM5+ MADU700</t>
-  </si>
-  <si>
-    <t>20125788</t>
-  </si>
-  <si>
-    <t>HLTHYWY1+ SP MADU700</t>
-  </si>
-  <si>
-    <t>20125790</t>
-  </si>
-  <si>
-    <t>HLTHYWY3+ SB MADU700</t>
-  </si>
-  <si>
-    <t>20032058</t>
-  </si>
-  <si>
-    <t>FF KENTAL MANIS 6X37</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>20013433</t>
-  </si>
-  <si>
-    <t>INDOMILK SKM PTH6X37</t>
-  </si>
-  <si>
-    <t>20087580</t>
-  </si>
-  <si>
-    <t>ENTRASOL GLD VAN560</t>
-  </si>
-  <si>
-    <t>10025373</t>
-  </si>
-  <si>
-    <t>ENTRASOL GOLD VAN170</t>
-  </si>
-  <si>
-    <t>20021571</t>
-  </si>
-  <si>
-    <t>ANLENE GOLD VAN 560G</t>
-  </si>
-  <si>
-    <t>10020147</t>
-  </si>
-  <si>
-    <t>ANLENE GOLD CKLT 230</t>
-  </si>
-  <si>
-    <t>10008064</t>
-  </si>
-  <si>
-    <t>ANLENE GOLD ORG240G</t>
-  </si>
-  <si>
-    <t>10012172</t>
-  </si>
-  <si>
-    <t>ANLENE GOLD VNLA 230</t>
-  </si>
-  <si>
-    <t>10003653</t>
-  </si>
-  <si>
-    <t>MRINAGA BMT1 LAC.390</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>20014399</t>
-  </si>
-  <si>
-    <t>MORINAGA CK3 VAN 780</t>
-  </si>
-  <si>
-    <t>10005241</t>
-  </si>
-  <si>
-    <t>MORINAGA CM ORGN 190</t>
-  </si>
-  <si>
-    <t>10008314</t>
-  </si>
-  <si>
-    <t>MORINAGA CK VNLA 190</t>
-  </si>
-  <si>
-    <t>10008316</t>
-  </si>
-  <si>
-    <t>MORINAGA CK MADU 190</t>
-  </si>
-  <si>
-    <t>10010874</t>
-  </si>
-  <si>
-    <t>DNCOW 1+ MDU BOX 120</t>
-  </si>
-  <si>
-    <t>10005338</t>
-  </si>
-  <si>
-    <t>DNCOW FRTGO BOX 195G</t>
-  </si>
-  <si>
-    <t>10026038</t>
-  </si>
-  <si>
-    <t>SGM EKSPL1+ MADU 150</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>20040575</t>
-  </si>
-  <si>
-    <t>SGM EKSPL1+ VAN 150G</t>
-  </si>
-  <si>
-    <t>20056930</t>
-  </si>
-  <si>
-    <t>SGM EKSPL3+ MADU 150</t>
-  </si>
-  <si>
-    <t>20037098</t>
-  </si>
-  <si>
-    <t>SGM SOYA 1+ VANL 400</t>
-  </si>
-  <si>
-    <t>20040302</t>
-  </si>
-  <si>
-    <t>SGM EKSPL3+ MADU 400</t>
-  </si>
-  <si>
-    <t>20040301</t>
-  </si>
-  <si>
-    <t>SGM EKSPL3+ VAN 400G</t>
-  </si>
-  <si>
-    <t>10009494</t>
-  </si>
-  <si>
-    <t>DANCOW FORTIGRO 390G</t>
-  </si>
-  <si>
-    <t>20040340</t>
-  </si>
-  <si>
-    <t>SGM ANANDA1 BOX 400G</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>20040312</t>
-  </si>
-  <si>
-    <t>SGM ANANDA2 BOX 400G</t>
-  </si>
-  <si>
-    <t>20040299</t>
-  </si>
-  <si>
-    <t>SGM EKSPL1+ MADU 400</t>
-  </si>
-  <si>
-    <t>20040300</t>
-  </si>
-  <si>
-    <t>SGM EKSPL1+ VAN 400G</t>
-  </si>
-  <si>
-    <t>20087025</t>
-  </si>
-  <si>
-    <t>SGM EKSPL3+ VAN 600G</t>
-  </si>
-  <si>
-    <t>20087024</t>
-  </si>
-  <si>
-    <t>SGM EKSPL3+ MADU 600</t>
-  </si>
-  <si>
-    <t>20047323</t>
-  </si>
-  <si>
-    <t>SGM ANANDA1 BOX 550G</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>20047324</t>
-  </si>
-  <si>
-    <t>SGM ANANDA2 BOX 550G</t>
-  </si>
-  <si>
-    <t>20074147</t>
-  </si>
-  <si>
-    <t>SGM EKSPL1+ MADU 600</t>
-  </si>
-  <si>
-    <t>20077508</t>
-  </si>
-  <si>
-    <t>SGM EKSPL1+ VAN 600G</t>
-  </si>
-  <si>
-    <t>20040294</t>
-  </si>
-  <si>
-    <t>SGM EKSPL1+ MADU 900</t>
-  </si>
-  <si>
-    <t>10005279</t>
-  </si>
-  <si>
-    <t>SGM ANANDA2 BOX 150G</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>20040293</t>
-  </si>
-  <si>
-    <t>SGM EKSPL1+ VAN 900G</t>
-  </si>
-  <si>
-    <t>20040296</t>
-  </si>
-  <si>
-    <t>SGM EKSPL3+ MADU 900</t>
-  </si>
-  <si>
-    <t>20040295</t>
-  </si>
-  <si>
-    <t>SGM EKSPL3+ VAN 900G</t>
-  </si>
-  <si>
-    <t>20066494</t>
-  </si>
-  <si>
-    <t>SGM EKSPL5+ MADU 900</t>
-  </si>
-  <si>
-    <t>10005315</t>
-  </si>
-  <si>
-    <t>SGM ANANDA1 BOX 150G</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>20040297</t>
-  </si>
-  <si>
-    <t>SGM ANANDA1 BOX 1KG</t>
-  </si>
-  <si>
-    <t>20040298</t>
-  </si>
-  <si>
-    <t>SGM ANANDA2 BOX 1KG</t>
-  </si>
-  <si>
-    <t>20065379</t>
-  </si>
-  <si>
-    <t>SGM SOYA1+ VANL 700G</t>
-  </si>
-  <si>
-    <t>20071686</t>
-  </si>
-  <si>
-    <t>SGM SOYA1+ MADU 700G</t>
-  </si>
-  <si>
-    <t>20005712</t>
-  </si>
-  <si>
-    <t>DNCOW 5+ VAN BOX 350</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>10009495</t>
-  </si>
-  <si>
-    <t>DNCW FRTG FL.CRM 390</t>
-  </si>
-  <si>
-    <t>10009493</t>
-  </si>
-  <si>
-    <t>DNCOW FRTGO COK 390G</t>
-  </si>
-  <si>
-    <t>10006259</t>
-  </si>
-  <si>
-    <t>DNCOW FRTGO ENR 780G</t>
-  </si>
-  <si>
-    <t>10006260</t>
-  </si>
-  <si>
-    <t>DNCOW FRTGO COK 780</t>
-  </si>
-  <si>
-    <t>10006258</t>
-  </si>
-  <si>
-    <t>DNCOWFRTGO F.CR 780G</t>
-  </si>
-  <si>
-    <t>10006262</t>
-  </si>
-  <si>
-    <t>DNCOW 1+ MDU BOX 750</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>10015652</t>
-  </si>
-  <si>
-    <t>DNCOW 1+ VAN BOX 750</t>
-  </si>
-  <si>
-    <t>10013035</t>
-  </si>
-  <si>
-    <t>DNCOW 3+ MDU BOX 750</t>
-  </si>
-  <si>
-    <t>10015650</t>
-  </si>
-  <si>
-    <t>DNCOW 3+ VAN BOX 750</t>
-  </si>
-  <si>
-    <t>10023780</t>
-  </si>
-  <si>
-    <t>DNCOW 5+ MDU BOX 750</t>
-  </si>
-  <si>
-    <t>10009496</t>
-  </si>
-  <si>
-    <t>DNCOW 1+ MDU BOX 350</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>10015653</t>
-  </si>
-  <si>
-    <t>DNCOW 1+ VAN BOX 350</t>
-  </si>
-  <si>
-    <t>10012967</t>
-  </si>
-  <si>
-    <t>DNCOW 3+ MDU BOX 350</t>
-  </si>
-  <si>
-    <t>10015651</t>
-  </si>
-  <si>
-    <t>DNCOW3+ VAN BOX  350</t>
-  </si>
-  <si>
-    <t>20017679</t>
-  </si>
-  <si>
-    <t>LACTOGEN PRO LANJ350</t>
-  </si>
-  <si>
-    <t>20113345</t>
-  </si>
-  <si>
-    <t>LACTOGRW PRO1+VAN350</t>
-  </si>
-  <si>
-    <t>20035629</t>
-  </si>
-  <si>
-    <t>BEBELAC 1+VNL BOX350</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>20035633</t>
-  </si>
-  <si>
-    <t>BEBELAC3+ VNL BOX350</t>
-  </si>
-  <si>
-    <t>20035635</t>
-  </si>
-  <si>
-    <t>BEBELAC3+ MDU BOX350</t>
-  </si>
-  <si>
-    <t>10025848</t>
-  </si>
-  <si>
-    <t>NTRILON 3 RYL VAN400</t>
-  </si>
-  <si>
-    <t>20055287</t>
-  </si>
-  <si>
-    <t>LACTOGRW PRO1+MDU350</t>
-  </si>
-  <si>
-    <t>20017965</t>
-  </si>
-  <si>
-    <t>LACTOGEN PRO FORM350</t>
-  </si>
-  <si>
-    <t>20142948</t>
-  </si>
-  <si>
-    <t>BEBELOVE 6-12BLN 775</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>20142950</t>
-  </si>
-  <si>
-    <t>BEBELAC 1+ VAN 775G</t>
-  </si>
-  <si>
-    <t>20142951</t>
-  </si>
-  <si>
-    <t>BEBELAC 1+ MADU 775</t>
-  </si>
-  <si>
-    <t>20142947</t>
-  </si>
-  <si>
-    <t>BEBELOVE  0-6BLN 775</t>
-  </si>
-  <si>
-    <t>20057224</t>
-  </si>
-  <si>
-    <t>BEBELOVE1 0-6 BOX175</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>20045528</t>
-  </si>
-  <si>
-    <t>BEBELOVE2 6-12BOX175</t>
-  </si>
-  <si>
-    <t>20043039</t>
-  </si>
-  <si>
-    <t>BEBELAC1+ MDU BOX175</t>
-  </si>
-  <si>
-    <t>20035626</t>
-  </si>
-  <si>
-    <t>BEBELOVE 1 BOX 350GR</t>
-  </si>
-  <si>
-    <t>20035627</t>
-  </si>
-  <si>
-    <t>BEBELOVE2 6-12BOX350</t>
-  </si>
-  <si>
-    <t>20035631</t>
-  </si>
-  <si>
-    <t>BEBELAC1+ MDU BOX350</t>
-  </si>
-  <si>
-    <t>20136285</t>
-  </si>
-  <si>
-    <t>BEBELOVE2 6-12BOX620</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>20122291</t>
-  </si>
-  <si>
-    <t>BEBELAC1+ MDU BOX600</t>
-  </si>
-  <si>
-    <t>20122288</t>
-  </si>
-  <si>
-    <t>BEBELAC1+ VAN BOX600</t>
-  </si>
-  <si>
-    <t>20069146</t>
-  </si>
-  <si>
-    <t>BEBELAC1+ MDU BX1000</t>
-  </si>
-  <si>
-    <t>20069147</t>
-  </si>
-  <si>
-    <t>BEBELAC1+ VNL BX1000</t>
-  </si>
-  <si>
-    <t>20142954</t>
-  </si>
-  <si>
-    <t>VIDORAN 5+VAN 700G</t>
-  </si>
-  <si>
-    <t>998</t>
   </si>
 </sst>
 </file>
@@ -1651,7 +1678,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F191"/>
+  <dimension ref="A1:F195"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -3116,10 +3143,10 @@
         <v>29</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -3136,7 +3163,7 @@
         <v>29</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>16</v>
@@ -3159,7 +3186,7 @@
         <v>35</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>5</v>
+        <v>63</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -3173,13 +3200,13 @@
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -3193,13 +3220,13 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>134</v>
+        <v>8</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>63</v>
+        <v>16</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -3216,10 +3243,10 @@
         <v>32</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -3236,10 +3263,10 @@
         <v>32</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -3256,10 +3283,10 @@
         <v>32</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -3276,10 +3303,10 @@
         <v>32</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>63</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -3296,7 +3323,7 @@
         <v>32</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>12</v>
@@ -3313,10 +3340,10 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>5</v>
@@ -3333,13 +3360,13 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -3353,10 +3380,10 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>5</v>
@@ -3373,13 +3400,13 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -3393,13 +3420,13 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -3413,41 +3440,41 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>20</v>
+        <v>194</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F89" s="1" t="s">
         <v>194</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E89" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F89" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
@@ -3456,18 +3483,18 @@
         <v>38</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>5</v>
+        <v>194</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
@@ -3476,27 +3503,27 @@
         <v>38</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>5</v>
+        <v>194</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>38</v>
+        <v>134</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>5</v>
@@ -3504,39 +3531,39 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>38</v>
+        <v>134</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>5</v>
+        <v>63</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>38</v>
+        <v>134</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>5</v>
@@ -3544,10 +3571,10 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
@@ -3556,7 +3583,7 @@
         <v>134</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>5</v>
@@ -3564,10 +3591,10 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
@@ -3576,27 +3603,27 @@
         <v>134</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>63</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>5</v>
@@ -3604,50 +3631,50 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>5</v>
+        <v>63</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
@@ -3656,7 +3683,7 @@
         <v>137</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>5</v>
@@ -3664,10 +3691,10 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
@@ -3676,27 +3703,27 @@
         <v>137</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>63</v>
+        <v>16</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>137</v>
+        <v>223</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>16</v>
@@ -3704,219 +3731,219 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B103" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D103" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="C103" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>137</v>
-      </c>
       <c r="E103" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>5</v>
+        <v>63</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>137</v>
+        <v>223</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>63</v>
+        <v>5</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>63</v>
+        <v>20</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B107" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D107" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="C107" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D107" s="1" t="s">
-        <v>228</v>
-      </c>
       <c r="E107" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>12</v>
@@ -3924,19 +3951,19 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>12</v>
@@ -3944,19 +3971,19 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B115" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D115" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="C115" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D115" s="1" t="s">
-        <v>239</v>
-      </c>
       <c r="E115" s="1" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>12</v>
@@ -3964,19 +3991,19 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>12</v>
@@ -3984,19 +4011,19 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>12</v>
@@ -4004,19 +4031,19 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>12</v>
@@ -4024,99 +4051,99 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B122" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D122" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="C122" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D122" s="1" t="s">
-        <v>256</v>
-      </c>
       <c r="E122" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>5</v>
@@ -4124,19 +4151,19 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>5</v>
@@ -4144,19 +4171,19 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>5</v>
@@ -4164,19 +4191,19 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>5</v>
@@ -4184,19 +4211,19 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>5</v>
@@ -4204,19 +4231,19 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>5</v>
@@ -4224,19 +4251,19 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B129" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D129" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="C129" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>271</v>
-      </c>
       <c r="E129" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>5</v>
@@ -4244,19 +4271,19 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>5</v>
@@ -4264,19 +4291,19 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>5</v>
@@ -4284,19 +4311,19 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>5</v>
@@ -4304,19 +4331,19 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>5</v>
@@ -4324,19 +4351,19 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>5</v>
@@ -4344,19 +4371,19 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B135" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D135" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="C135" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>286</v>
-      </c>
       <c r="E135" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>5</v>
@@ -4364,19 +4391,19 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>5</v>
@@ -4384,19 +4411,19 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>5</v>
@@ -4404,19 +4431,19 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>5</v>
@@ -4424,19 +4451,19 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>5</v>
@@ -4444,19 +4471,19 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B140" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D140" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="C140" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>299</v>
-      </c>
       <c r="E140" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>5</v>
@@ -4464,19 +4491,19 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>5</v>
@@ -4484,19 +4511,19 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>5</v>
@@ -4504,39 +4531,39 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>5</v>
@@ -4544,19 +4571,19 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B145" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D145" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="C145" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D145" s="1" t="s">
-        <v>310</v>
-      </c>
       <c r="E145" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>5</v>
@@ -4564,59 +4591,59 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>5</v>
@@ -4624,19 +4651,19 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>5</v>
@@ -4644,39 +4671,39 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B150" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D150" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="C150" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D150" s="1" t="s">
-        <v>321</v>
-      </c>
       <c r="E150" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>5</v>
@@ -4684,19 +4711,19 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>5</v>
@@ -4704,19 +4731,19 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>5</v>
@@ -4724,19 +4751,19 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>5</v>
@@ -4744,19 +4771,19 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>5</v>
@@ -4764,19 +4791,19 @@
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B156" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D156" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="C156" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D156" s="1" t="s">
-        <v>332</v>
-      </c>
       <c r="E156" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>5</v>
@@ -4784,19 +4811,19 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>5</v>
@@ -4804,19 +4831,19 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>5</v>
@@ -4824,19 +4851,19 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>5</v>
@@ -4844,19 +4871,19 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>5</v>
@@ -4864,19 +4891,19 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B161" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D161" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="C161" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D161" s="1" t="s">
-        <v>345</v>
-      </c>
       <c r="E161" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>5</v>
@@ -4884,19 +4911,19 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>5</v>
@@ -4904,19 +4931,19 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>5</v>
@@ -4924,19 +4951,19 @@
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>5</v>
@@ -4944,19 +4971,19 @@
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>5</v>
@@ -4964,19 +4991,19 @@
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>5</v>
@@ -4984,19 +5011,19 @@
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B167" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D167" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="C167" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D167" s="1" t="s">
-        <v>356</v>
-      </c>
       <c r="E167" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>5</v>
@@ -5004,19 +5031,19 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>5</v>
@@ -5024,19 +5051,19 @@
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>5</v>
@@ -5044,19 +5071,19 @@
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>5</v>
@@ -5064,19 +5091,19 @@
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>5</v>
@@ -5084,179 +5111,179 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B173" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="C173" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D173" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="C173" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D173" s="1" t="s">
-        <v>369</v>
-      </c>
       <c r="E173" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E176" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B177" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D177" s="1" t="s">
         <v>384</v>
-      </c>
-      <c r="C177" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D177" s="1" t="s">
-        <v>382</v>
       </c>
       <c r="E177" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E178" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E179" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>5</v>
@@ -5264,19 +5291,19 @@
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>5</v>
@@ -5284,19 +5311,19 @@
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>5</v>
@@ -5304,59 +5331,59 @@
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B183" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="C183" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D183" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="C183" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D183" s="1" t="s">
-        <v>391</v>
-      </c>
       <c r="E183" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>5</v>
@@ -5364,19 +5391,19 @@
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F186" s="1" t="s">
         <v>5</v>
@@ -5384,102 +5411,182 @@
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="E187" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B188" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="C188" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D188" s="1" t="s">
         <v>408</v>
-      </c>
-      <c r="C188" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D188" s="1" t="s">
-        <v>404</v>
       </c>
       <c r="E188" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="E189" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="F191" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A192" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="B192" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="C192" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D192" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="E192" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F192" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A193" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="B193" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="C193" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D193" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="E193" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F193" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A194" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="B194" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="C194" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D194" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="E194" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F194" s="1" t="s">
         <v>20</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A195" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B195" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="C195" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D195" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="E195" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F195" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/MBF04S.xlsx
+++ b/MBF04S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1170" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1188" uniqueCount="431">
   <si>
     <t/>
   </si>
@@ -463,6 +463,18 @@
     <t>YB BABY CRACK BNN 25</t>
   </si>
   <si>
+    <t>20143372</t>
+  </si>
+  <si>
+    <t>MNDE BRMN CKS BNNA40</t>
+  </si>
+  <si>
+    <t>20143371</t>
+  </si>
+  <si>
+    <t>MNDE BRMN CKS TMGO40</t>
+  </si>
+  <si>
     <t>20125783</t>
   </si>
   <si>
@@ -515,6 +527,12 @@
   </si>
   <si>
     <t>SUNBAY EVP.MILK 380G</t>
+  </si>
+  <si>
+    <t>20143301</t>
+  </si>
+  <si>
+    <t>INDMLK CRM MTCHA 260</t>
   </si>
   <si>
     <t>20136510</t>
@@ -1678,7 +1696,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F195"/>
+  <dimension ref="A1:F198"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -3020,10 +3038,10 @@
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>16</v>
@@ -3040,10 +3058,10 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E68" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>16</v>
@@ -3063,10 +3081,10 @@
         <v>29</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -3083,10 +3101,10 @@
         <v>29</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -3103,7 +3121,7 @@
         <v>29</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>20</v>
@@ -3123,10 +3141,10 @@
         <v>29</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -3143,10 +3161,10 @@
         <v>29</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -3163,7 +3181,7 @@
         <v>29</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>16</v>
@@ -3183,10 +3201,10 @@
         <v>29</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>63</v>
+        <v>5</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -3200,13 +3218,13 @@
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E76" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E76" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F76" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -3220,13 +3238,13 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -3240,10 +3258,10 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>16</v>
@@ -3263,10 +3281,10 @@
         <v>32</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>63</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -3283,10 +3301,10 @@
         <v>32</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -3303,10 +3321,10 @@
         <v>32</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -3323,10 +3341,10 @@
         <v>32</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>12</v>
+        <v>63</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -3340,13 +3358,13 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -3360,10 +3378,10 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>5</v>
@@ -3380,13 +3398,13 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -3403,7 +3421,7 @@
         <v>38</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>5</v>
@@ -3423,7 +3441,7 @@
         <v>38</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>5</v>
@@ -3443,18 +3461,18 @@
         <v>38</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>194</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B89" s="1" t="s">
         <v>195</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>196</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
@@ -3463,18 +3481,18 @@
         <v>38</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>194</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>197</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>198</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
@@ -3483,18 +3501,18 @@
         <v>38</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>194</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>199</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>200</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
@@ -3503,10 +3521,10 @@
         <v>38</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -3520,13 +3538,13 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>134</v>
+        <v>38</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>5</v>
+        <v>200</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -3540,13 +3558,13 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>134</v>
+        <v>38</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>63</v>
+        <v>16</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -3560,13 +3578,13 @@
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>134</v>
+        <v>38</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>5</v>
+        <v>200</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -3583,7 +3601,7 @@
         <v>134</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>5</v>
@@ -3603,10 +3621,10 @@
         <v>134</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>5</v>
+        <v>63</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -3620,10 +3638,10 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>5</v>
@@ -3640,13 +3658,13 @@
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>63</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -3660,13 +3678,13 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -3683,7 +3701,7 @@
         <v>137</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>5</v>
@@ -3703,10 +3721,10 @@
         <v>137</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -3720,10 +3738,10 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>223</v>
+        <v>137</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>16</v>
@@ -3731,62 +3749,62 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B103" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="B103" s="1" t="s">
-        <v>225</v>
-      </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>223</v>
+        <v>137</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>63</v>
+        <v>5</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="B104" s="1" t="s">
-        <v>227</v>
-      </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>223</v>
+        <v>137</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>63</v>
+        <v>16</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="B105" s="1" t="s">
+      <c r="C105" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D105" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="C105" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>223</v>
-      </c>
       <c r="E105" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -3800,73 +3818,73 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>20</v>
+        <v>63</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B107" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="B107" s="1" t="s">
-        <v>234</v>
-      </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B108" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="B108" s="1" t="s">
-        <v>236</v>
-      </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B109" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="B109" s="1" t="s">
+      <c r="C109" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D109" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="C109" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>232</v>
-      </c>
       <c r="E109" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -3880,13 +3898,13 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -3900,13 +3918,13 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -3920,10 +3938,10 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>12</v>
@@ -3940,10 +3958,10 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>12</v>
@@ -3960,10 +3978,10 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>12</v>
@@ -3971,19 +3989,19 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B115" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="B115" s="1" t="s">
-        <v>251</v>
-      </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>12</v>
@@ -3991,19 +4009,19 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B116" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="B116" s="1" t="s">
-        <v>253</v>
-      </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>12</v>
@@ -4011,19 +4029,19 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="B117" s="1" t="s">
+      <c r="C117" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D117" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="C117" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>249</v>
-      </c>
       <c r="E117" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>12</v>
@@ -4040,10 +4058,10 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>12</v>
@@ -4060,13 +4078,13 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -4080,13 +4098,13 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -4100,30 +4118,30 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="B122" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="B122" s="1" t="s">
-        <v>266</v>
-      </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>5</v>
@@ -4131,19 +4149,19 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B123" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="B123" s="1" t="s">
-        <v>268</v>
-      </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>5</v>
@@ -4151,19 +4169,19 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B124" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="B124" s="1" t="s">
+      <c r="C124" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D124" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="C124" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D124" s="1" t="s">
-        <v>264</v>
-      </c>
       <c r="E124" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>5</v>
@@ -4180,10 +4198,10 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>5</v>
@@ -4200,10 +4218,10 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>5</v>
@@ -4220,10 +4238,10 @@
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>5</v>
@@ -4240,10 +4258,10 @@
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>5</v>
@@ -4251,19 +4269,19 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B129" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="B129" s="1" t="s">
-        <v>281</v>
-      </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>5</v>
@@ -4271,19 +4289,19 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B130" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="B130" s="1" t="s">
-        <v>283</v>
-      </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>5</v>
@@ -4291,19 +4309,19 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B131" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B131" s="1" t="s">
+      <c r="C131" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D131" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>279</v>
-      </c>
       <c r="E131" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>5</v>
@@ -4320,10 +4338,10 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>5</v>
@@ -4340,10 +4358,10 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>5</v>
@@ -4360,10 +4378,10 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>5</v>
@@ -4371,19 +4389,19 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B135" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="B135" s="1" t="s">
-        <v>294</v>
-      </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>5</v>
@@ -4391,19 +4409,19 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B136" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="B136" s="1" t="s">
-        <v>296</v>
-      </c>
       <c r="C136" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>5</v>
@@ -4411,19 +4429,19 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="B137" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="B137" s="1" t="s">
+      <c r="C137" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D137" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="C137" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>292</v>
-      </c>
       <c r="E137" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>5</v>
@@ -4440,10 +4458,10 @@
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>5</v>
@@ -4460,10 +4478,10 @@
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>5</v>
@@ -4471,19 +4489,19 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B140" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="B140" s="1" t="s">
-        <v>305</v>
-      </c>
       <c r="C140" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>5</v>
@@ -4491,19 +4509,19 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B141" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="B141" s="1" t="s">
-        <v>307</v>
-      </c>
       <c r="C141" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>5</v>
@@ -4511,19 +4529,19 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B142" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="B142" s="1" t="s">
+      <c r="C142" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D142" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="C142" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D142" s="1" t="s">
-        <v>303</v>
-      </c>
       <c r="E142" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>5</v>
@@ -4540,13 +4558,13 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -4560,10 +4578,10 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>5</v>
@@ -4571,19 +4589,19 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="B145" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="B145" s="1" t="s">
-        <v>316</v>
-      </c>
       <c r="C145" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>5</v>
@@ -4591,19 +4609,19 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B146" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="B146" s="1" t="s">
-        <v>318</v>
-      </c>
       <c r="C146" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>12</v>
@@ -4611,19 +4629,19 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B147" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="B147" s="1" t="s">
+      <c r="C147" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D147" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="C147" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D147" s="1" t="s">
-        <v>314</v>
-      </c>
       <c r="E147" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>5</v>
@@ -4640,10 +4658,10 @@
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>5</v>
@@ -4660,30 +4678,30 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B150" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="B150" s="1" t="s">
-        <v>327</v>
-      </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>5</v>
@@ -4691,19 +4709,19 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B151" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="B151" s="1" t="s">
-        <v>329</v>
-      </c>
       <c r="C151" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>5</v>
@@ -4711,19 +4729,19 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B152" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="B152" s="1" t="s">
+      <c r="C152" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D152" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="C152" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D152" s="1" t="s">
-        <v>325</v>
-      </c>
       <c r="E152" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>5</v>
@@ -4740,10 +4758,10 @@
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>5</v>
@@ -4760,10 +4778,10 @@
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>5</v>
@@ -4780,10 +4798,10 @@
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>5</v>
@@ -4791,19 +4809,19 @@
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="B156" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="B156" s="1" t="s">
-        <v>340</v>
-      </c>
       <c r="C156" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>5</v>
@@ -4811,19 +4829,19 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B157" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="B157" s="1" t="s">
-        <v>342</v>
-      </c>
       <c r="C157" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>5</v>
@@ -4831,19 +4849,19 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B158" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="B158" s="1" t="s">
+      <c r="C158" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D158" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="C158" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D158" s="1" t="s">
-        <v>338</v>
-      </c>
       <c r="E158" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>5</v>
@@ -4860,10 +4878,10 @@
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>5</v>
@@ -4880,10 +4898,10 @@
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>5</v>
@@ -4891,19 +4909,19 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="B161" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="B161" s="1" t="s">
-        <v>351</v>
-      </c>
       <c r="C161" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>5</v>
@@ -4911,19 +4929,19 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="B162" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="B162" s="1" t="s">
-        <v>353</v>
-      </c>
       <c r="C162" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>5</v>
@@ -4931,19 +4949,19 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="B163" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="B163" s="1" t="s">
+      <c r="C163" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D163" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="C163" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D163" s="1" t="s">
-        <v>349</v>
-      </c>
       <c r="E163" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>5</v>
@@ -4960,10 +4978,10 @@
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>5</v>
@@ -4980,10 +4998,10 @@
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>5</v>
@@ -5000,10 +5018,10 @@
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>5</v>
@@ -5011,19 +5029,19 @@
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B167" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="B167" s="1" t="s">
-        <v>364</v>
-      </c>
       <c r="C167" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>5</v>
@@ -5031,19 +5049,19 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="B168" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="B168" s="1" t="s">
-        <v>366</v>
-      </c>
       <c r="C168" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>5</v>
@@ -5051,19 +5069,19 @@
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="B169" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="B169" s="1" t="s">
+      <c r="C169" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D169" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="C169" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D169" s="1" t="s">
-        <v>362</v>
-      </c>
       <c r="E169" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>5</v>
@@ -5080,10 +5098,10 @@
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>5</v>
@@ -5100,10 +5118,10 @@
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>5</v>
@@ -5120,70 +5138,70 @@
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="B173" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="B173" s="1" t="s">
-        <v>377</v>
-      </c>
       <c r="C173" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="B174" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="B174" s="1" t="s">
-        <v>379</v>
-      </c>
       <c r="C174" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="B175" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="B175" s="1" t="s">
+      <c r="C175" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D175" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="C175" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D175" s="1" t="s">
-        <v>375</v>
-      </c>
       <c r="E175" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>16</v>
@@ -5200,70 +5218,70 @@
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="B177" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="B177" s="1" t="s">
-        <v>386</v>
-      </c>
       <c r="C177" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="B178" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="B178" s="1" t="s">
-        <v>388</v>
-      </c>
       <c r="C178" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="B179" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="B179" s="1" t="s">
+      <c r="C179" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D179" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="C179" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D179" s="1" t="s">
-        <v>384</v>
-      </c>
       <c r="E179" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>5</v>
@@ -5280,10 +5298,10 @@
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>5</v>
@@ -5300,10 +5318,10 @@
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>5</v>
@@ -5320,10 +5338,10 @@
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>5</v>
@@ -5331,59 +5349,59 @@
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="B183" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="B183" s="1" t="s">
-        <v>399</v>
-      </c>
       <c r="C183" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="B184" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="B184" s="1" t="s">
-        <v>401</v>
-      </c>
       <c r="C184" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="B185" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="B185" s="1" t="s">
+      <c r="C185" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D185" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="C185" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D185" s="1" t="s">
-        <v>397</v>
-      </c>
       <c r="E185" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>5</v>
@@ -5400,13 +5418,13 @@
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
@@ -5420,73 +5438,73 @@
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B188" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="B188" s="1" t="s">
-        <v>410</v>
-      </c>
       <c r="C188" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="B189" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="B189" s="1" t="s">
-        <v>412</v>
-      </c>
       <c r="C189" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="B190" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="B190" s="1" t="s">
+      <c r="C190" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D190" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="C190" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D190" s="1" t="s">
-        <v>408</v>
-      </c>
       <c r="E190" s="1" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
@@ -5500,13 +5518,13 @@
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
@@ -5520,13 +5538,13 @@
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
@@ -5540,13 +5558,13 @@
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
@@ -5560,13 +5578,13 @@
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
@@ -5580,12 +5598,72 @@
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="E195" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F195" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A196" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B196" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="C196" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D196" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="E196" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="F195" s="1" t="s">
+      <c r="F196" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A197" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="B197" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="C197" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D197" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="E197" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="F197" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A198" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="B198" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="C198" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D198" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="E198" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="F198" s="1" t="s">
         <v>16</v>
       </c>
     </row>

--- a/MBF04S.xlsx
+++ b/MBF04S.xlsx
@@ -3584,7 +3584,7 @@
         <v>32</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>200</v>
+        <v>16</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">

--- a/MBF04S.xlsx
+++ b/MBF04S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1188" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1218" uniqueCount="433">
   <si>
     <t/>
   </si>
@@ -535,6 +535,18 @@
     <t>INDMLK CRM MTCHA 260</t>
   </si>
   <si>
+    <t>20140647</t>
+  </si>
+  <si>
+    <t>ENAK K/MNS COKLAT260</t>
+  </si>
+  <si>
+    <t>20140646</t>
+  </si>
+  <si>
+    <t>ENAK K/MNS PUTIH 260</t>
+  </si>
+  <si>
     <t>20136510</t>
   </si>
   <si>
@@ -577,6 +589,33 @@
     <t>DIABETASOL VNL.170GR</t>
   </si>
   <si>
+    <t>20142907</t>
+  </si>
+  <si>
+    <t>MILKOW A/G 1 MDU 600</t>
+  </si>
+  <si>
+    <t>,(E-1B)</t>
+  </si>
+  <si>
+    <t>20142908</t>
+  </si>
+  <si>
+    <t>MILKOW A/G 1 VNL 900</t>
+  </si>
+  <si>
+    <t>20142909</t>
+  </si>
+  <si>
+    <t>MILKOW A/G 1 VNL 600</t>
+  </si>
+  <si>
+    <t>20142910</t>
+  </si>
+  <si>
+    <t>MILKOW A/G 1 MDU 900</t>
+  </si>
+  <si>
     <t>20070110</t>
   </si>
   <si>
@@ -607,33 +646,6 @@
     <t>VIDORAN XM5+ COKL700</t>
   </si>
   <si>
-    <t>20142907</t>
-  </si>
-  <si>
-    <t>MILKOW A/G 1 MDU 600</t>
-  </si>
-  <si>
-    <t>,(E-1B)</t>
-  </si>
-  <si>
-    <t>20142909</t>
-  </si>
-  <si>
-    <t>MILKOW A/G 1 VNL 600</t>
-  </si>
-  <si>
-    <t>20142910</t>
-  </si>
-  <si>
-    <t>MILKOW A/G 1 MDU 900</t>
-  </si>
-  <si>
-    <t>20142908</t>
-  </si>
-  <si>
-    <t>MILKOW A/G 1 VNL 900</t>
-  </si>
-  <si>
     <t>20098371</t>
   </si>
   <si>
@@ -1286,12 +1298,6 @@
   </si>
   <si>
     <t>HLTHYWY1+ SP MADU700</t>
-  </si>
-  <si>
-    <t>20125790</t>
-  </si>
-  <si>
-    <t>HLTHYWY3+ SB MADU700</t>
   </si>
   <si>
     <t>20089819</t>
@@ -1696,7 +1702,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F198"/>
+  <dimension ref="A1:F203"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -3278,13 +3284,13 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>4</v>
+        <v>134</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -3298,10 +3304,10 @@
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>8</v>
+        <v>137</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>16</v>
@@ -3321,10 +3327,10 @@
         <v>32</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -3341,10 +3347,10 @@
         <v>32</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>63</v>
+        <v>16</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -3361,10 +3367,10 @@
         <v>32</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -3381,10 +3387,10 @@
         <v>32</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>5</v>
+        <v>63</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -3401,7 +3407,7 @@
         <v>32</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>12</v>
@@ -3418,10 +3424,10 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>5</v>
@@ -3438,13 +3444,13 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -3458,73 +3464,73 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>5</v>
+        <v>194</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>5</v>
+        <v>194</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>200</v>
+        <v>16</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -3541,10 +3547,10 @@
         <v>38</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>200</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -3561,10 +3567,10 @@
         <v>38</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -3581,10 +3587,10 @@
         <v>38</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -3598,10 +3604,10 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>134</v>
+        <v>38</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>5</v>
@@ -3618,150 +3624,150 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>134</v>
+        <v>38</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>63</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>211</v>
+        <v>192</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>212</v>
+        <v>193</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>134</v>
+        <v>38</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>5</v>
+        <v>194</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>213</v>
+        <v>197</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>214</v>
+        <v>198</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>134</v>
+        <v>38</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>5</v>
+        <v>194</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>215</v>
+        <v>199</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>134</v>
+        <v>38</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>217</v>
+        <v>195</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>137</v>
+        <v>38</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>63</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>5</v>
@@ -3769,79 +3775,79 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>229</v>
+        <v>134</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>229</v>
+        <v>137</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>63</v>
+        <v>5</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>229</v>
+        <v>137</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>63</v>
@@ -3849,59 +3855,59 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>229</v>
+        <v>137</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>238</v>
+        <v>137</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>238</v>
+        <v>137</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>16</v>
@@ -3909,19 +3915,19 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>16</v>
@@ -3929,139 +3935,139 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>12</v>
+        <v>63</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>12</v>
+        <v>63</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>12</v>
@@ -4069,19 +4075,19 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>12</v>
@@ -4089,19 +4095,19 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>12</v>
@@ -4109,19 +4115,19 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>12</v>
@@ -4129,139 +4135,139 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>5</v>
@@ -4269,19 +4275,19 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>5</v>
@@ -4289,19 +4295,19 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>5</v>
@@ -4309,19 +4315,19 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>5</v>
@@ -4329,19 +4335,19 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>5</v>
@@ -4349,19 +4355,19 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>5</v>
@@ -4369,19 +4375,19 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>5</v>
@@ -4389,19 +4395,19 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>5</v>
@@ -4409,19 +4415,19 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>5</v>
@@ -4429,16 +4435,16 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="E137" s="1" t="s">
         <v>4</v>
@@ -4449,16 +4455,16 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="E138" s="1" t="s">
         <v>8</v>
@@ -4469,16 +4475,16 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="E139" s="1" t="s">
         <v>11</v>
@@ -4489,16 +4495,16 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="E140" s="1" t="s">
         <v>15</v>
@@ -4509,16 +4515,16 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="E141" s="1" t="s">
         <v>19</v>
@@ -4529,19 +4535,19 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>309</v>
+        <v>289</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>5</v>
@@ -4549,19 +4555,19 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>5</v>
@@ -4569,19 +4575,19 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>5</v>
@@ -4589,19 +4595,19 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>5</v>
@@ -4609,39 +4615,39 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>320</v>
+        <v>302</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>5</v>
@@ -4649,19 +4655,19 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>5</v>
@@ -4669,39 +4675,39 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>5</v>
@@ -4709,19 +4715,19 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>5</v>
@@ -4729,39 +4735,39 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>331</v>
+        <v>313</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>5</v>
@@ -4769,19 +4775,19 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>5</v>
@@ -4789,39 +4795,39 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>5</v>
@@ -4829,19 +4835,19 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>5</v>
@@ -4849,16 +4855,16 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="E158" s="1" t="s">
         <v>4</v>
@@ -4869,16 +4875,16 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="E159" s="1" t="s">
         <v>8</v>
@@ -4889,16 +4895,16 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="E160" s="1" t="s">
         <v>11</v>
@@ -4909,16 +4915,16 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="E161" s="1" t="s">
         <v>15</v>
@@ -4929,16 +4935,16 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="E162" s="1" t="s">
         <v>19</v>
@@ -4949,19 +4955,19 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>355</v>
+        <v>335</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>5</v>
@@ -4969,19 +4975,19 @@
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>5</v>
@@ -4989,19 +4995,19 @@
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>5</v>
@@ -5009,19 +5015,19 @@
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>5</v>
@@ -5029,19 +5035,19 @@
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>5</v>
@@ -5049,19 +5055,19 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>5</v>
@@ -5069,16 +5075,16 @@
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="E169" s="1" t="s">
         <v>4</v>
@@ -5089,16 +5095,16 @@
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="E170" s="1" t="s">
         <v>8</v>
@@ -5109,16 +5115,16 @@
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="E171" s="1" t="s">
         <v>11</v>
@@ -5129,16 +5135,16 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="E172" s="1" t="s">
         <v>15</v>
@@ -5149,16 +5155,16 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="E173" s="1" t="s">
         <v>19</v>
@@ -5169,16 +5175,16 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="E174" s="1" t="s">
         <v>23</v>
@@ -5189,99 +5195,99 @@
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="E175" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="E176" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="E177" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="E178" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>390</v>
+        <v>372</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>5</v>
@@ -5289,19 +5295,19 @@
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>390</v>
+        <v>372</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>5</v>
@@ -5309,96 +5315,96 @@
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="E185" s="1" t="s">
         <v>4</v>
@@ -5409,56 +5415,56 @@
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>405</v>
+        <v>396</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="E186" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
-        <v>406</v>
+        <v>397</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>407</v>
+        <v>398</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="E187" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
-        <v>408</v>
+        <v>399</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="E188" s="1" t="s">
         <v>15</v>
@@ -5469,16 +5475,16 @@
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
-        <v>410</v>
+        <v>401</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="E189" s="1" t="s">
         <v>19</v>
@@ -5489,19 +5495,19 @@
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>413</v>
+        <v>404</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>414</v>
+        <v>394</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="F190" s="1" t="s">
         <v>5</v>
@@ -5509,79 +5515,79 @@
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
-        <v>415</v>
+        <v>405</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>422</v>
+        <v>413</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>5</v>
@@ -5589,19 +5595,19 @@
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
-        <v>423</v>
+        <v>414</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>5</v>
@@ -5609,19 +5615,19 @@
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
-        <v>425</v>
+        <v>416</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>426</v>
+        <v>417</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>134</v>
+        <v>8</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>5</v>
@@ -5629,19 +5635,19 @@
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>137</v>
+        <v>11</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>20</v>
@@ -5649,21 +5655,121 @@
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="B198" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="C198" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D198" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="E198" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F198" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A199" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B199" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="C199" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D199" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="E199" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F199" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A200" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B200" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="C200" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D200" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="E200" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F200" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A201" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="B201" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="C201" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D201" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="E201" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F201" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A202" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="B198" s="1" t="s">
+      <c r="B202" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="C198" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D198" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="E198" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="F198" s="1" t="s">
+      <c r="C202" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D202" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="E202" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F202" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A203" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="B203" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="C203" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D203" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="E203" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F203" s="1" t="s">
         <v>16</v>
       </c>
     </row>

--- a/MBF04S.xlsx
+++ b/MBF04S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1218" uniqueCount="433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1218" uniqueCount="432">
   <si>
     <t/>
   </si>
@@ -595,9 +595,6 @@
     <t>MILKOW A/G 1 MDU 600</t>
   </si>
   <si>
-    <t>,(E-1B)</t>
-  </si>
-  <si>
     <t>20142908</t>
   </si>
   <si>
@@ -733,6 +730,12 @@
     <t>VIDORAN XM5+ MADU700</t>
   </si>
   <si>
+    <t>20125788</t>
+  </si>
+  <si>
+    <t>HLTHYWY1+ SP MADU700</t>
+  </si>
+  <si>
     <t>20032058</t>
   </si>
   <si>
@@ -1292,12 +1295,6 @@
   </si>
   <si>
     <t>SGM EKSPL3+ CKLT 400</t>
-  </si>
-  <si>
-    <t>20125788</t>
-  </si>
-  <si>
-    <t>HLTHYWY1+ SP MADU700</t>
   </si>
   <si>
     <t>20089819</t>
@@ -3470,15 +3467,15 @@
         <v>4</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>194</v>
+        <v>16</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B89" s="1" t="s">
         <v>195</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>196</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
@@ -3495,10 +3492,10 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>197</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>198</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
@@ -3510,15 +3507,15 @@
         <v>11</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>194</v>
+        <v>16</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>199</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>200</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
@@ -3535,10 +3532,10 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>201</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>202</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
@@ -3555,10 +3552,10 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>203</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>204</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
@@ -3575,10 +3572,10 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>205</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>206</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
@@ -3595,10 +3592,10 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B95" s="1" t="s">
         <v>207</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>208</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
@@ -3615,10 +3612,10 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B96" s="1" t="s">
         <v>209</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>210</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
@@ -3650,15 +3647,15 @@
         <v>23</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>194</v>
+        <v>16</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>197</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>198</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
@@ -3670,15 +3667,15 @@
         <v>26</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>194</v>
+        <v>16</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B99" s="1" t="s">
         <v>199</v>
-      </c>
-      <c r="B99" s="1" t="s">
-        <v>200</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
@@ -3695,10 +3692,10 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>195</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>196</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
@@ -3715,10 +3712,10 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B101" s="1" t="s">
         <v>211</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>212</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
@@ -3735,10 +3732,10 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>213</v>
-      </c>
-      <c r="B102" s="1" t="s">
-        <v>214</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
@@ -3755,10 +3752,10 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B103" s="1" t="s">
         <v>215</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>216</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
@@ -3775,10 +3772,10 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>217</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>218</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
@@ -3795,10 +3792,10 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>219</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>220</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
@@ -3815,10 +3812,10 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B106" s="1" t="s">
         <v>221</v>
-      </c>
-      <c r="B106" s="1" t="s">
-        <v>222</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
@@ -3835,10 +3832,10 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B107" s="1" t="s">
         <v>223</v>
-      </c>
-      <c r="B107" s="1" t="s">
-        <v>224</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
@@ -3855,10 +3852,10 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B108" s="1" t="s">
         <v>225</v>
-      </c>
-      <c r="B108" s="1" t="s">
-        <v>226</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
@@ -3875,10 +3872,10 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B109" s="1" t="s">
         <v>227</v>
-      </c>
-      <c r="B109" s="1" t="s">
-        <v>228</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
@@ -3895,10 +3892,10 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>229</v>
-      </c>
-      <c r="B110" s="1" t="s">
-        <v>230</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
@@ -3915,16 +3912,16 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B111" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="B111" s="1" t="s">
+      <c r="C111" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D111" s="1" t="s">
         <v>232</v>
-      </c>
-      <c r="C111" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>233</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>4</v>
@@ -3935,16 +3932,16 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B112" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="B112" s="1" t="s">
-        <v>235</v>
-      </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>8</v>
@@ -3955,16 +3952,16 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B113" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="B113" s="1" t="s">
-        <v>237</v>
-      </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E113" s="1" t="s">
         <v>11</v>
@@ -3975,16 +3972,16 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B114" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="B114" s="1" t="s">
-        <v>239</v>
-      </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E114" s="1" t="s">
         <v>15</v>
@@ -3995,59 +3992,59 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B115" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="B115" s="1" t="s">
-        <v>241</v>
-      </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D116" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="B116" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="C116" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D116" s="1" t="s">
-        <v>242</v>
-      </c>
       <c r="E116" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="B117" s="1" t="s">
-        <v>246</v>
-      </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>16</v>
@@ -4055,39 +4052,39 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B118" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="B118" s="1" t="s">
-        <v>248</v>
-      </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B119" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="B119" s="1" t="s">
-        <v>250</v>
-      </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>12</v>
@@ -4095,19 +4092,19 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B120" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="B120" s="1" t="s">
-        <v>252</v>
-      </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>12</v>
@@ -4115,19 +4112,19 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B121" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="B121" s="1" t="s">
-        <v>254</v>
-      </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>12</v>
@@ -4135,19 +4132,19 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B122" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="B122" s="1" t="s">
-        <v>256</v>
-      </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>12</v>
@@ -4155,19 +4152,19 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B123" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="B123" s="1" t="s">
-        <v>258</v>
-      </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>259</v>
+        <v>243</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>12</v>
@@ -4175,19 +4172,19 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D124" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="B124" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="C124" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D124" s="1" t="s">
-        <v>259</v>
-      </c>
       <c r="E124" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>12</v>
@@ -4195,19 +4192,19 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B125" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="B125" s="1" t="s">
-        <v>263</v>
-      </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>12</v>
@@ -4215,19 +4212,19 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B126" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="B126" s="1" t="s">
-        <v>265</v>
-      </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>12</v>
@@ -4235,19 +4232,19 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B127" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="B127" s="1" t="s">
-        <v>267</v>
-      </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>12</v>
@@ -4255,39 +4252,39 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B128" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="B128" s="1" t="s">
-        <v>269</v>
-      </c>
       <c r="C128" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B129" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="B129" s="1" t="s">
-        <v>271</v>
-      </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>5</v>
@@ -4295,19 +4292,19 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B130" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="B130" s="1" t="s">
-        <v>273</v>
-      </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>274</v>
+        <v>260</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>5</v>
@@ -4315,19 +4312,19 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D131" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="B131" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="C131" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>274</v>
-      </c>
       <c r="E131" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>5</v>
@@ -4335,19 +4332,19 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B132" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="B132" s="1" t="s">
-        <v>278</v>
-      </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>5</v>
@@ -4355,19 +4352,19 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B133" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="B133" s="1" t="s">
-        <v>280</v>
-      </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>5</v>
@@ -4375,19 +4372,19 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B134" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="B134" s="1" t="s">
-        <v>282</v>
-      </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>5</v>
@@ -4395,19 +4392,19 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B135" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="B135" s="1" t="s">
-        <v>284</v>
-      </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>5</v>
@@ -4415,19 +4412,19 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B136" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="B136" s="1" t="s">
-        <v>286</v>
-      </c>
       <c r="C136" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>5</v>
@@ -4435,19 +4432,19 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B137" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="B137" s="1" t="s">
-        <v>288</v>
-      </c>
       <c r="C137" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>289</v>
+        <v>275</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>5</v>
@@ -4455,19 +4452,19 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D138" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="B138" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="C138" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D138" s="1" t="s">
-        <v>289</v>
-      </c>
       <c r="E138" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>5</v>
@@ -4475,19 +4472,19 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B139" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="B139" s="1" t="s">
-        <v>293</v>
-      </c>
       <c r="C139" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>5</v>
@@ -4495,19 +4492,19 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B140" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="B140" s="1" t="s">
-        <v>295</v>
-      </c>
       <c r="C140" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>5</v>
@@ -4515,19 +4512,19 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B141" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="B141" s="1" t="s">
-        <v>297</v>
-      </c>
       <c r="C141" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>5</v>
@@ -4535,19 +4532,19 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="B142" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="B142" s="1" t="s">
-        <v>299</v>
-      </c>
       <c r="C142" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>5</v>
@@ -4555,19 +4552,19 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="B143" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="B143" s="1" t="s">
-        <v>301</v>
-      </c>
       <c r="C143" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>5</v>
@@ -4575,19 +4572,19 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D144" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="B144" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="C144" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D144" s="1" t="s">
-        <v>302</v>
-      </c>
       <c r="E144" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>5</v>
@@ -4595,19 +4592,19 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B145" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="B145" s="1" t="s">
-        <v>306</v>
-      </c>
       <c r="C145" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>5</v>
@@ -4615,19 +4612,19 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B146" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="B146" s="1" t="s">
-        <v>308</v>
-      </c>
       <c r="C146" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>5</v>
@@ -4635,19 +4632,19 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B147" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="B147" s="1" t="s">
-        <v>310</v>
-      </c>
       <c r="C147" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>5</v>
@@ -4655,19 +4652,19 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B148" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="B148" s="1" t="s">
-        <v>312</v>
-      </c>
       <c r="C148" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>5</v>
@@ -4675,19 +4672,19 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D149" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="B149" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="C149" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D149" s="1" t="s">
-        <v>313</v>
-      </c>
       <c r="E149" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>5</v>
@@ -4695,19 +4692,19 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B150" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="B150" s="1" t="s">
-        <v>317</v>
-      </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>5</v>
@@ -4715,19 +4712,19 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B151" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="B151" s="1" t="s">
-        <v>319</v>
-      </c>
       <c r="C151" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>5</v>
@@ -4735,59 +4732,59 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B152" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="B152" s="1" t="s">
-        <v>321</v>
-      </c>
       <c r="C152" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B153" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="B153" s="1" t="s">
-        <v>323</v>
-      </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D154" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="B154" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="C154" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D154" s="1" t="s">
-        <v>324</v>
-      </c>
       <c r="E154" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>5</v>
@@ -4795,59 +4792,59 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="B155" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="B155" s="1" t="s">
-        <v>328</v>
-      </c>
       <c r="C155" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="B156" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="B156" s="1" t="s">
-        <v>330</v>
-      </c>
       <c r="C156" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B157" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="B157" s="1" t="s">
-        <v>332</v>
-      </c>
       <c r="C157" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>5</v>
@@ -4855,19 +4852,19 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B158" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="B158" s="1" t="s">
-        <v>334</v>
-      </c>
       <c r="C158" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>5</v>
@@ -4875,19 +4872,19 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D159" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="B159" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="C159" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D159" s="1" t="s">
-        <v>335</v>
-      </c>
       <c r="E159" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>5</v>
@@ -4895,19 +4892,19 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B160" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="B160" s="1" t="s">
-        <v>339</v>
-      </c>
       <c r="C160" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>5</v>
@@ -4915,19 +4912,19 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="B161" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="B161" s="1" t="s">
-        <v>341</v>
-      </c>
       <c r="C161" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>5</v>
@@ -4935,19 +4932,19 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B162" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="B162" s="1" t="s">
-        <v>343</v>
-      </c>
       <c r="C162" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>5</v>
@@ -4955,19 +4952,19 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="B163" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="B163" s="1" t="s">
-        <v>345</v>
-      </c>
       <c r="C163" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>5</v>
@@ -4975,19 +4972,19 @@
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="B164" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="B164" s="1" t="s">
-        <v>347</v>
-      </c>
       <c r="C164" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>348</v>
+        <v>336</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>5</v>
@@ -4995,19 +4992,19 @@
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D165" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="B165" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="C165" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D165" s="1" t="s">
-        <v>348</v>
-      </c>
       <c r="E165" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>5</v>
@@ -5015,19 +5012,19 @@
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="B166" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="B166" s="1" t="s">
-        <v>352</v>
-      </c>
       <c r="C166" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>5</v>
@@ -5035,19 +5032,19 @@
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="B167" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="B167" s="1" t="s">
-        <v>354</v>
-      </c>
       <c r="C167" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>5</v>
@@ -5055,19 +5052,19 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="B168" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="B168" s="1" t="s">
-        <v>356</v>
-      </c>
       <c r="C168" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>5</v>
@@ -5075,19 +5072,19 @@
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="B169" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="B169" s="1" t="s">
-        <v>358</v>
-      </c>
       <c r="C169" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>5</v>
@@ -5095,19 +5092,19 @@
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D170" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="B170" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="C170" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D170" s="1" t="s">
-        <v>359</v>
-      </c>
       <c r="E170" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>5</v>
@@ -5115,19 +5112,19 @@
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="B171" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="B171" s="1" t="s">
-        <v>363</v>
-      </c>
       <c r="C171" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>5</v>
@@ -5135,19 +5132,19 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="B172" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="B172" s="1" t="s">
-        <v>365</v>
-      </c>
       <c r="C172" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>5</v>
@@ -5155,19 +5152,19 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="B173" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="B173" s="1" t="s">
-        <v>367</v>
-      </c>
       <c r="C173" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>5</v>
@@ -5175,19 +5172,19 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="B174" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="B174" s="1" t="s">
-        <v>369</v>
-      </c>
       <c r="C174" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>5</v>
@@ -5195,19 +5192,19 @@
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="B175" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="B175" s="1" t="s">
-        <v>371</v>
-      </c>
       <c r="C175" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>372</v>
+        <v>360</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>5</v>
@@ -5215,19 +5212,19 @@
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="B176" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="C176" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D176" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="B176" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="C176" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D176" s="1" t="s">
-        <v>372</v>
-      </c>
       <c r="E176" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>5</v>
@@ -5235,19 +5232,19 @@
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="B177" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="B177" s="1" t="s">
-        <v>376</v>
-      </c>
       <c r="C177" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>5</v>
@@ -5255,19 +5252,19 @@
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B178" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="B178" s="1" t="s">
-        <v>378</v>
-      </c>
       <c r="C178" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>5</v>
@@ -5275,19 +5272,19 @@
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="B179" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="B179" s="1" t="s">
-        <v>380</v>
-      </c>
       <c r="C179" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>5</v>
@@ -5295,19 +5292,19 @@
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B180" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="B180" s="1" t="s">
-        <v>382</v>
-      </c>
       <c r="C180" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>5</v>
@@ -5315,39 +5312,39 @@
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="B181" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="B181" s="1" t="s">
-        <v>384</v>
-      </c>
       <c r="C181" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>385</v>
+        <v>373</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="B182" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="C182" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D182" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="B182" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="C182" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D182" s="1" t="s">
-        <v>385</v>
-      </c>
       <c r="E182" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>16</v>
@@ -5355,19 +5352,19 @@
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="B183" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="B183" s="1" t="s">
-        <v>389</v>
-      </c>
       <c r="C183" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>16</v>
@@ -5375,19 +5372,19 @@
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="B184" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="B184" s="1" t="s">
-        <v>391</v>
-      </c>
       <c r="C184" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>16</v>
@@ -5395,39 +5392,39 @@
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="B185" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="B185" s="1" t="s">
-        <v>393</v>
-      </c>
       <c r="C185" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="C186" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D186" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="B186" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="C186" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D186" s="1" t="s">
-        <v>394</v>
-      </c>
       <c r="E186" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F186" s="1" t="s">
         <v>5</v>
@@ -5435,19 +5432,19 @@
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="B187" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="B187" s="1" t="s">
-        <v>398</v>
-      </c>
       <c r="C187" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F187" s="1" t="s">
         <v>5</v>
@@ -5455,19 +5452,19 @@
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="B188" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="B188" s="1" t="s">
-        <v>400</v>
-      </c>
       <c r="C188" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F188" s="1" t="s">
         <v>5</v>
@@ -5475,19 +5472,19 @@
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B189" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="B189" s="1" t="s">
-        <v>402</v>
-      </c>
       <c r="C189" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F189" s="1" t="s">
         <v>5</v>
@@ -5495,19 +5492,19 @@
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B190" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="B190" s="1" t="s">
-        <v>404</v>
-      </c>
       <c r="C190" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F190" s="1" t="s">
         <v>5</v>
@@ -5515,19 +5512,19 @@
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="B191" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="B191" s="1" t="s">
-        <v>406</v>
-      </c>
       <c r="C191" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>5</v>
@@ -5535,39 +5532,39 @@
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="B192" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="C192" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D192" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="B192" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="C192" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D192" s="1" t="s">
-        <v>407</v>
-      </c>
       <c r="E192" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="B193" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="B193" s="1" t="s">
-        <v>411</v>
-      </c>
       <c r="C193" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>16</v>
@@ -5575,39 +5572,39 @@
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="B194" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="B194" s="1" t="s">
-        <v>413</v>
-      </c>
       <c r="C194" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="B195" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="B195" s="1" t="s">
-        <v>415</v>
-      </c>
       <c r="C195" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>5</v>
@@ -5615,19 +5612,19 @@
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="B196" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="B196" s="1" t="s">
-        <v>417</v>
-      </c>
       <c r="C196" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>5</v>
@@ -5635,39 +5632,39 @@
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="B197" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="C197" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D197" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="B197" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="C197" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D197" s="1" t="s">
-        <v>418</v>
-      </c>
       <c r="E197" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="B198" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="B198" s="1" t="s">
-        <v>422</v>
-      </c>
       <c r="C198" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>20</v>
@@ -5675,19 +5672,19 @@
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="B199" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="B199" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="C199" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>20</v>
@@ -5695,39 +5692,39 @@
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="B200" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="B200" s="1" t="s">
-        <v>426</v>
-      </c>
       <c r="C200" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="B201" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="B201" s="1" t="s">
-        <v>428</v>
-      </c>
       <c r="C201" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>5</v>
@@ -5735,19 +5732,19 @@
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="B202" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="B202" s="1" t="s">
-        <v>430</v>
-      </c>
       <c r="C202" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>20</v>
@@ -5755,19 +5752,19 @@
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="B203" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="B203" s="1" t="s">
-        <v>432</v>
-      </c>
       <c r="C203" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>134</v>
+        <v>38</v>
       </c>
       <c r="F203" s="1" t="s">
         <v>16</v>

--- a/MBF04S.xlsx
+++ b/MBF04S.xlsx
@@ -67,7 +67,7 @@
     <t>20068905</t>
   </si>
   <si>
-    <t>FF SKM PUTIH 535G</t>
+    <t>FF SKM PUTIH 535 G</t>
   </si>
   <si>
     <t>5</t>
@@ -79,7 +79,7 @@
     <t>20068906</t>
   </si>
   <si>
-    <t>FF SKM COKELAT 535G</t>
+    <t>FF SKM COKELAT 535 G</t>
   </si>
   <si>
     <t>6</t>

--- a/MBF04S.xlsx
+++ b/MBF04S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1218" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1194" uniqueCount="432">
   <si>
     <t/>
   </si>
@@ -463,16 +463,22 @@
     <t>YB BABY CRACK BNN 25</t>
   </si>
   <si>
+    <t>20143371</t>
+  </si>
+  <si>
+    <t>MNDE BRMN CKS TMGO40</t>
+  </si>
+  <si>
     <t>20143372</t>
   </si>
   <si>
     <t>MNDE BRMN CKS BNNA40</t>
   </si>
   <si>
-    <t>20143371</t>
-  </si>
-  <si>
-    <t>MNDE BRMN CKS TMGO40</t>
+    <t>20142228</t>
+  </si>
+  <si>
+    <t>CAP ENAK CHOCO 535G</t>
   </si>
   <si>
     <t>20125783</t>
@@ -481,10 +487,22 @@
     <t>CAP/ENAK KKM PTH 535</t>
   </si>
   <si>
-    <t>20142228</t>
-  </si>
-  <si>
-    <t>CAP ENAK CHOCO 535G</t>
+    <t>20140647</t>
+  </si>
+  <si>
+    <t>ENAK K/MNS COKLAT260</t>
+  </si>
+  <si>
+    <t>20140646</t>
+  </si>
+  <si>
+    <t>ENAK K/MNS PUTIH 260</t>
+  </si>
+  <si>
+    <t>20143301</t>
+  </si>
+  <si>
+    <t>INDMLK CRM MTCHA 260</t>
   </si>
   <si>
     <t>10005489</t>
@@ -529,24 +547,6 @@
     <t>SUNBAY EVP.MILK 380G</t>
   </si>
   <si>
-    <t>20143301</t>
-  </si>
-  <si>
-    <t>INDMLK CRM MTCHA 260</t>
-  </si>
-  <si>
-    <t>20140647</t>
-  </si>
-  <si>
-    <t>ENAK K/MNS COKLAT260</t>
-  </si>
-  <si>
-    <t>20140646</t>
-  </si>
-  <si>
-    <t>ENAK K/MNS PUTIH 260</t>
-  </si>
-  <si>
     <t>20136510</t>
   </si>
   <si>
@@ -595,24 +595,24 @@
     <t>MILKOW A/G 1 MDU 600</t>
   </si>
   <si>
+    <t>20142909</t>
+  </si>
+  <si>
+    <t>MILKOW A/G 1 VNL 600</t>
+  </si>
+  <si>
+    <t>20142910</t>
+  </si>
+  <si>
+    <t>MILKOW A/G 1 MDU 900</t>
+  </si>
+  <si>
     <t>20142908</t>
   </si>
   <si>
     <t>MILKOW A/G 1 VNL 900</t>
   </si>
   <si>
-    <t>20142909</t>
-  </si>
-  <si>
-    <t>MILKOW A/G 1 VNL 600</t>
-  </si>
-  <si>
-    <t>20142910</t>
-  </si>
-  <si>
-    <t>MILKOW A/G 1 MDU 900</t>
-  </si>
-  <si>
     <t>20070110</t>
   </si>
   <si>
@@ -703,33 +703,33 @@
     <t>VIDORAN 5  MADU 900G</t>
   </si>
   <si>
+    <t>20135200</t>
+  </si>
+  <si>
+    <t>VIDORAN BABY0-6 550G</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>20129773</t>
+  </si>
+  <si>
+    <t>VDORAN BABY6-12 550G</t>
+  </si>
+  <si>
+    <t>20117985</t>
+  </si>
+  <si>
+    <t>VIDORAN XM5+ MADU700</t>
+  </si>
+  <si>
     <t>20142954</t>
   </si>
   <si>
     <t>VIDORAN 5+VAN 700G</t>
   </si>
   <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>20135200</t>
-  </si>
-  <si>
-    <t>VIDORAN BABY0-6 550G</t>
-  </si>
-  <si>
-    <t>20129773</t>
-  </si>
-  <si>
-    <t>VDORAN BABY6-12 550G</t>
-  </si>
-  <si>
-    <t>20117985</t>
-  </si>
-  <si>
-    <t>VIDORAN XM5+ MADU700</t>
-  </si>
-  <si>
     <t>20125788</t>
   </si>
   <si>
@@ -862,13 +862,13 @@
     <t>20040302</t>
   </si>
   <si>
-    <t>SGM EKSPL3+ MADU 400</t>
+    <t>SGM EKSPL3+ MADU 350</t>
   </si>
   <si>
     <t>20040301</t>
   </si>
   <si>
-    <t>SGM EKSPL3+ VAN 400G</t>
+    <t>SGM EKSPL3+ VAN 350G</t>
   </si>
   <si>
     <t>10009494</t>
@@ -895,13 +895,13 @@
     <t>20040299</t>
   </si>
   <si>
-    <t>SGM EKSPL1+ MADU 400</t>
+    <t>SGM EKSPL1+ MADU 350</t>
   </si>
   <si>
     <t>20040300</t>
   </si>
   <si>
-    <t>SGM EKSPL1+ VAN 400G</t>
+    <t>SGM EKSPL1+ VAN 350G</t>
   </si>
   <si>
     <t>20087025</t>
@@ -1234,7 +1234,7 @@
     <t>20136285</t>
   </si>
   <si>
-    <t>BEBELOVE2 6-12BOX620</t>
+    <t>BEBELOVE2 6-12BOX600</t>
   </si>
   <si>
     <t>28</t>
@@ -1279,34 +1279,34 @@
     <t>FF SKM CKLT KLG 370</t>
   </si>
   <si>
+    <t>20141099</t>
+  </si>
+  <si>
+    <t>FF CRMY GULA ARN 240</t>
+  </si>
+  <si>
     <t>10015124</t>
   </si>
   <si>
     <t>FF SKM COKLAT 6X37</t>
   </si>
   <si>
-    <t>20141099</t>
-  </si>
-  <si>
-    <t>FF CRMY GULA ARN 240</t>
-  </si>
-  <si>
     <t>20040303</t>
   </si>
   <si>
-    <t>SGM EKSPL3+ CKLT 400</t>
+    <t>SGM EKSPL3+ CKLT 350</t>
+  </si>
+  <si>
+    <t>10000021</t>
+  </si>
+  <si>
+    <t>ENAK K/MNS PUTIH 370</t>
   </si>
   <si>
     <t>20089819</t>
   </si>
   <si>
     <t>FF KENTAL MANIS 490G</t>
-  </si>
-  <si>
-    <t>10000021</t>
-  </si>
-  <si>
-    <t>ENAK K/MNS PUTIH 370</t>
   </si>
 </sst>
 </file>
@@ -1699,7 +1699,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F203"/>
+  <dimension ref="A1:F199"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -3127,7 +3127,7 @@
         <v>11</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -3147,7 +3147,7 @@
         <v>15</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -3167,7 +3167,7 @@
         <v>19</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -3187,7 +3187,7 @@
         <v>23</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -3204,10 +3204,10 @@
         <v>29</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -3224,10 +3224,10 @@
         <v>29</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -3244,10 +3244,10 @@
         <v>29</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>63</v>
+        <v>16</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -3267,7 +3267,7 @@
         <v>38</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -3307,7 +3307,7 @@
         <v>137</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -3632,90 +3632,90 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>193</v>
+        <v>211</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>38</v>
+        <v>134</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>196</v>
+        <v>212</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>38</v>
+        <v>134</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>198</v>
+        <v>214</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>199</v>
+        <v>215</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>38</v>
+        <v>134</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>194</v>
+        <v>216</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>195</v>
+        <v>217</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>38</v>
+        <v>134</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
@@ -3724,7 +3724,7 @@
         <v>134</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>5</v>
@@ -3732,79 +3732,79 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>63</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>5</v>
+        <v>63</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>5</v>
@@ -3812,10 +3812,10 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
@@ -3824,27 +3824,27 @@
         <v>137</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>137</v>
+        <v>232</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>63</v>
@@ -3852,39 +3852,39 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>137</v>
+        <v>232</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>137</v>
+        <v>232</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -3892,19 +3892,19 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>137</v>
+        <v>232</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>16</v>
@@ -3912,10 +3912,10 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
@@ -3924,98 +3924,98 @@
         <v>232</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>63</v>
+        <v>20</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>63</v>
+        <v>16</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
@@ -4024,18 +4024,18 @@
         <v>243</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
@@ -4044,18 +4044,18 @@
         <v>243</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
@@ -4064,18 +4064,18 @@
         <v>243</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
@@ -4084,7 +4084,7 @@
         <v>243</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>12</v>
@@ -4092,19 +4092,19 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>12</v>
@@ -4112,19 +4112,19 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>12</v>
@@ -4132,19 +4132,19 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>12</v>
@@ -4152,19 +4152,19 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>12</v>
@@ -4172,10 +4172,10 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
@@ -4184,7 +4184,7 @@
         <v>260</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>12</v>
@@ -4192,10 +4192,10 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
@@ -4204,18 +4204,18 @@
         <v>260</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
@@ -4224,67 +4224,67 @@
         <v>260</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>260</v>
+        <v>275</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>260</v>
+        <v>275</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>260</v>
+        <v>275</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>5</v>
@@ -4292,19 +4292,19 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>260</v>
+        <v>275</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>5</v>
@@ -4312,10 +4312,10 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>3</v>
@@ -4324,7 +4324,7 @@
         <v>275</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>5</v>
@@ -4332,10 +4332,10 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
@@ -4344,7 +4344,7 @@
         <v>275</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>5</v>
@@ -4352,10 +4352,10 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
@@ -4364,7 +4364,7 @@
         <v>275</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>5</v>
@@ -4372,19 +4372,19 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>275</v>
+        <v>290</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>5</v>
@@ -4392,19 +4392,19 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>275</v>
+        <v>290</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>5</v>
@@ -4412,19 +4412,19 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>275</v>
+        <v>290</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>5</v>
@@ -4432,19 +4432,19 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>275</v>
+        <v>290</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>5</v>
@@ -4452,10 +4452,10 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
@@ -4464,7 +4464,7 @@
         <v>290</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>5</v>
@@ -4472,10 +4472,10 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>3</v>
@@ -4484,7 +4484,7 @@
         <v>290</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>5</v>
@@ -4492,19 +4492,19 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>290</v>
+        <v>303</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>5</v>
@@ -4512,19 +4512,19 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>290</v>
+        <v>303</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>5</v>
@@ -4532,19 +4532,19 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>290</v>
+        <v>303</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>5</v>
@@ -4552,19 +4552,19 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>290</v>
+        <v>303</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>5</v>
@@ -4572,10 +4572,10 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>3</v>
@@ -4584,7 +4584,7 @@
         <v>303</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>5</v>
@@ -4592,19 +4592,19 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>5</v>
@@ -4612,19 +4612,19 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>5</v>
@@ -4632,19 +4632,19 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>5</v>
@@ -4652,19 +4652,19 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>5</v>
@@ -4672,10 +4672,10 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>3</v>
@@ -4684,27 +4684,27 @@
         <v>314</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>5</v>
@@ -4712,19 +4712,19 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>5</v>
@@ -4732,50 +4732,50 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>3</v>
@@ -4784,7 +4784,7 @@
         <v>325</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>5</v>
@@ -4792,19 +4792,19 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>5</v>
@@ -4812,39 +4812,39 @@
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>5</v>
@@ -4852,19 +4852,19 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>5</v>
@@ -4872,10 +4872,10 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>3</v>
@@ -4884,7 +4884,7 @@
         <v>336</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>5</v>
@@ -4892,10 +4892,10 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>3</v>
@@ -4904,7 +4904,7 @@
         <v>336</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>5</v>
@@ -4912,19 +4912,19 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>5</v>
@@ -4932,19 +4932,19 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>5</v>
@@ -4952,19 +4952,19 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>5</v>
@@ -4972,19 +4972,19 @@
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>5</v>
@@ -4992,10 +4992,10 @@
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>3</v>
@@ -5004,7 +5004,7 @@
         <v>349</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>5</v>
@@ -5012,19 +5012,19 @@
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>349</v>
+        <v>360</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>5</v>
@@ -5032,19 +5032,19 @@
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>349</v>
+        <v>360</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>5</v>
@@ -5052,19 +5052,19 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>349</v>
+        <v>360</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>5</v>
@@ -5072,19 +5072,19 @@
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>349</v>
+        <v>360</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>5</v>
@@ -5092,10 +5092,10 @@
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>3</v>
@@ -5104,7 +5104,7 @@
         <v>360</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>5</v>
@@ -5112,10 +5112,10 @@
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>3</v>
@@ -5124,7 +5124,7 @@
         <v>360</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>5</v>
@@ -5132,19 +5132,19 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>360</v>
+        <v>373</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>5</v>
@@ -5152,19 +5152,19 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>360</v>
+        <v>373</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>5</v>
@@ -5172,19 +5172,19 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>360</v>
+        <v>373</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>5</v>
@@ -5192,19 +5192,19 @@
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>360</v>
+        <v>373</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>5</v>
@@ -5212,10 +5212,10 @@
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>3</v>
@@ -5224,7 +5224,7 @@
         <v>373</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>5</v>
@@ -5232,10 +5232,10 @@
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>3</v>
@@ -5244,7 +5244,7 @@
         <v>373</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>5</v>
@@ -5252,170 +5252,170 @@
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>373</v>
+        <v>386</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>373</v>
+        <v>386</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>373</v>
+        <v>386</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>373</v>
+        <v>386</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="E182" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="E183" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="E184" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="E185" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>3</v>
@@ -5424,7 +5424,7 @@
         <v>395</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F186" s="1" t="s">
         <v>5</v>
@@ -5432,10 +5432,10 @@
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>3</v>
@@ -5444,7 +5444,7 @@
         <v>395</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="F187" s="1" t="s">
         <v>5</v>
@@ -5452,19 +5452,19 @@
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>395</v>
+        <v>408</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F188" s="1" t="s">
         <v>5</v>
@@ -5472,59 +5472,59 @@
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>395</v>
+        <v>408</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>395</v>
+        <v>408</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>395</v>
+        <v>408</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>5</v>
@@ -5532,10 +5532,10 @@
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>3</v>
@@ -5544,7 +5544,7 @@
         <v>408</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F192" s="1" t="s">
         <v>5</v>
@@ -5552,90 +5552,90 @@
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>408</v>
+        <v>419</v>
       </c>
       <c r="E193" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>408</v>
+        <v>419</v>
       </c>
       <c r="E194" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>414</v>
+        <v>423</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>408</v>
+        <v>419</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>408</v>
+        <v>419</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>3</v>
@@ -5644,7 +5644,7 @@
         <v>419</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>5</v>
@@ -5652,10 +5652,10 @@
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>3</v>
@@ -5664,18 +5664,18 @@
         <v>419</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>11</v>
+        <v>325</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>3</v>
@@ -5684,90 +5684,10 @@
         <v>419</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>15</v>
+        <v>336</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>20</v>
-      </c>
-    </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A200" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="B200" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="C200" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D200" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="E200" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F200" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A201" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="B201" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="C201" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D201" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="E201" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F201" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A202" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="B202" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="C202" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D202" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="E202" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F202" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A203" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="B203" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="C203" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D203" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="E203" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F203" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
   </sheetData>
